--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_power.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_power.xlsx
@@ -647,10 +647,10 @@
         <v>0.1256642700844014</v>
       </c>
       <c r="X2">
-        <v>0.0850085301941815</v>
+        <v>0.08499021942402613</v>
       </c>
       <c r="Y2">
-        <v>0.04065573989021989</v>
+        <v>0.04067405066037527</v>
       </c>
       <c r="Z2">
         <v>0.4196724735955542</v>
@@ -659,10 +659,10 @@
         <v>0.05716857478281649</v>
       </c>
       <c r="AB2">
-        <v>0.07555883313618135</v>
+        <v>0.07554815433015752</v>
       </c>
       <c r="AC2">
-        <v>-0.01839025835336486</v>
+        <v>-0.01837957954734103</v>
       </c>
       <c r="AD2">
         <v>418.5</v>
@@ -781,10 +781,10 @@
         <v>0.1256642700844014</v>
       </c>
       <c r="X3">
-        <v>0.0850085301941815</v>
+        <v>0.08499021942402613</v>
       </c>
       <c r="Y3">
-        <v>0.04065573989021989</v>
+        <v>0.04067405066037527</v>
       </c>
       <c r="Z3">
         <v>0.4196724735955542</v>
@@ -793,10 +793,10 @@
         <v>0.05716857478281649</v>
       </c>
       <c r="AB3">
-        <v>0.07555883313618135</v>
+        <v>0.07554815433015752</v>
       </c>
       <c r="AC3">
-        <v>-0.01839025835336486</v>
+        <v>-0.01837957954734103</v>
       </c>
       <c r="AD3">
         <v>418.5</v>
@@ -1151,13 +1151,13 @@
         <v>587.8</v>
       </c>
       <c r="L2">
-        <v>1310.42564142239</v>
+        <v>1310.56699417379</v>
       </c>
       <c r="M2">
         <v>1003.68083286172</v>
       </c>
       <c r="N2">
-        <v>1306.21564142239</v>
+        <v>1306.35699417379</v>
       </c>
       <c r="O2">
         <v>420.090832861724</v>
@@ -1166,16 +1166,16 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.07555883313618129</v>
+        <v>0.0755481543301575</v>
       </c>
       <c r="R2">
-        <v>0.0686663395843206</v>
+        <v>0.0686556607782967</v>
       </c>
       <c r="S2">
         <v>0.0623366166625341</v>
       </c>
       <c r="T2">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.0850085301941815</v>
+        <v>0.0849902194240261</v>
       </c>
       <c r="X2">
-        <v>0.0686663395843206</v>
+        <v>0.0686556607782967</v>
       </c>
       <c r="Y2">
         <v>0.7638903212913229</v>
@@ -1230,7 +1230,7 @@
         <v>587.8</v>
       </c>
       <c r="AK2">
-        <v>0.05132743418963756</v>
+        <v>0.05130346377183673</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.06866633958432057</v>
+        <v>0.06865566077829674</v>
       </c>
       <c r="C2">
-        <v>1310.425641422394</v>
+        <v>1310.566994173794</v>
       </c>
       <c r="D2">
-        <v>1306.215641422394</v>
+        <v>1306.356994173794</v>
       </c>
       <c r="E2">
         <v>-420.0908328617245</v>
@@ -1469,19 +1469,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.06866633958432057</v>
+        <v>0.06865566077829674</v>
       </c>
       <c r="T2">
         <v>0.4454993697880389</v>
       </c>
       <c r="U2">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V2">
         <v>0</v>
       </c>
       <c r="W2">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1500,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.06878470575094592</v>
+        <v>0.0687600269449221</v>
       </c>
       <c r="C3">
-        <v>1293.620010553295</v>
+        <v>1294.549962512255</v>
       </c>
       <c r="D3">
-        <v>1299.488918881912</v>
+        <v>1300.418870840873</v>
       </c>
       <c r="E3">
         <v>-410.0119245331073</v>
@@ -1533,37 +1533,37 @@
         <v>68.72</v>
       </c>
       <c r="M3">
-        <v>0.5809141757133344</v>
+        <v>0.5668037040532702</v>
       </c>
       <c r="N3">
-        <v>68.13908582428667</v>
+        <v>68.15319629594673</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>68.13908582428667</v>
+        <v>68.15319629594673</v>
       </c>
       <c r="Q3">
-        <v>112.7390858242867</v>
+        <v>112.7531962959467</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.06889731271143493</v>
+        <v>0.06888652603868359</v>
       </c>
       <c r="T3">
         <v>0.4499993634222615</v>
       </c>
       <c r="U3">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V3">
         <v>0</v>
       </c>
       <c r="W3">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>118.2963041237807</v>
+        <v>121.2412683766468</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1582,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.06890307191757125</v>
+        <v>0.06886439311154742</v>
       </c>
       <c r="C4">
-        <v>1276.883306999482</v>
+        <v>1278.586670757614</v>
       </c>
       <c r="D4">
-        <v>1292.831123656717</v>
+        <v>1294.534487414849</v>
       </c>
       <c r="E4">
         <v>-399.93301620449</v>
@@ -1615,37 +1615,37 @@
         <v>68.72</v>
       </c>
       <c r="M4">
-        <v>1.161828351426669</v>
+        <v>1.13360740810654</v>
       </c>
       <c r="N4">
-        <v>67.55817164857334</v>
+        <v>67.58639259189346</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>67.55817164857334</v>
+        <v>67.58639259189346</v>
       </c>
       <c r="Q4">
-        <v>112.1581716485733</v>
+        <v>112.1863925918935</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.06913299957583732</v>
+        <v>0.06912210283499667</v>
       </c>
       <c r="T4">
         <v>0.4545911936612642</v>
       </c>
       <c r="U4">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V4">
         <v>0</v>
       </c>
       <c r="W4">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>59.14815206189037</v>
+        <v>60.62063418832338</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1664,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.0690214380841966</v>
+        <v>0.06896875927817277</v>
       </c>
       <c r="C5">
-        <v>1260.214476735525</v>
+        <v>1262.676392678306</v>
       </c>
       <c r="D5">
-        <v>1286.241201721377</v>
+        <v>1288.703117664157</v>
       </c>
       <c r="E5">
         <v>-389.8541078758728</v>
@@ -1697,37 +1697,37 @@
         <v>68.72</v>
       </c>
       <c r="M5">
-        <v>1.742742527140003</v>
+        <v>1.700411112159811</v>
       </c>
       <c r="N5">
-        <v>66.97725747285999</v>
+        <v>67.01958888784019</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>66.97725747285999</v>
+        <v>67.01958888784019</v>
       </c>
       <c r="Q5">
-        <v>111.57725747286</v>
+        <v>111.6195888878402</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.06937354596321708</v>
+        <v>0.06936253688484201</v>
       </c>
       <c r="T5">
         <v>0.4592777008124112</v>
       </c>
       <c r="U5">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V5">
         <v>0</v>
       </c>
       <c r="W5">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>39.43210137459357</v>
+        <v>40.41375612554891</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1746,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.06913980425082193</v>
+        <v>0.0690731254447981</v>
       </c>
       <c r="C6">
-        <v>1243.612487117657</v>
+        <v>1246.818415069641</v>
       </c>
       <c r="D6">
-        <v>1279.718120432126</v>
+        <v>1282.924048384109</v>
       </c>
       <c r="E6">
         <v>-379.7751995472555</v>
@@ -1779,37 +1779,37 @@
         <v>68.72</v>
       </c>
       <c r="M6">
-        <v>2.323656702853337</v>
+        <v>2.267214816213081</v>
       </c>
       <c r="N6">
-        <v>66.39634329714666</v>
+        <v>66.45278518378692</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>66.39634329714666</v>
+        <v>66.45278518378692</v>
       </c>
       <c r="Q6">
-        <v>110.9963432971467</v>
+        <v>111.0527851837869</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.06961910373366727</v>
+        <v>0.06960797997739245</v>
       </c>
       <c r="T6">
         <v>0.4640618435292072</v>
       </c>
       <c r="U6">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V6">
         <v>0</v>
       </c>
       <c r="W6">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>29.57407603094518</v>
+        <v>30.31031709416169</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1828,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.06925817041744728</v>
+        <v>0.06917749161142345</v>
       </c>
       <c r="C7">
-        <v>1227.076326344327</v>
+        <v>1231.012037463015</v>
       </c>
       <c r="D7">
-        <v>1273.260867987413</v>
+        <v>1277.196579106102</v>
       </c>
       <c r="E7">
         <v>-369.6962912186383</v>
@@ -1861,37 +1861,37 @@
         <v>68.72</v>
       </c>
       <c r="M7">
-        <v>2.904570878566672</v>
+        <v>2.834018520266352</v>
       </c>
       <c r="N7">
-        <v>65.81542912143333</v>
+        <v>65.88598147973364</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>65.81542912143333</v>
+        <v>65.88598147973364</v>
       </c>
       <c r="Q7">
-        <v>110.4154291214333</v>
+        <v>110.4859814797337</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.06986983114139007</v>
+        <v>0.06985859029294395</v>
       </c>
       <c r="T7">
         <v>0.4689467050400409</v>
       </c>
       <c r="U7">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V7">
         <v>0</v>
       </c>
       <c r="W7">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>23.65926082475614</v>
+        <v>24.24825367532934</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +1910,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.06937653658407261</v>
+        <v>0.06928185777804879</v>
       </c>
       <c r="C8">
-        <v>1210.605002933016</v>
+        <v>1215.256571842883</v>
       </c>
       <c r="D8">
-        <v>1266.868452904719</v>
+        <v>1271.520021814586</v>
       </c>
       <c r="E8">
         <v>-359.617382890021</v>
@@ -1943,37 +1943,37 @@
         <v>68.72</v>
       </c>
       <c r="M8">
-        <v>3.485485054280006</v>
+        <v>3.400822224319621</v>
       </c>
       <c r="N8">
-        <v>65.23451494571999</v>
+        <v>65.31917777568037</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>65.23451494571999</v>
+        <v>65.31917777568037</v>
       </c>
       <c r="Q8">
-        <v>109.83451494572</v>
+        <v>109.9191777756804</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.07012589317480912</v>
+        <v>0.07011453274286888</v>
       </c>
       <c r="T8">
         <v>0.4739354997745094</v>
       </c>
       <c r="U8">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V8">
         <v>0</v>
       </c>
       <c r="W8">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.71605068729679</v>
+        <v>20.20687806277446</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.06949490275069796</v>
+        <v>0.06938622394467413</v>
       </c>
       <c r="C9">
-        <v>1194.197545212715</v>
+        <v>1199.551342371236</v>
       </c>
       <c r="D9">
-        <v>1260.539903513036</v>
+        <v>1265.893700671557</v>
       </c>
       <c r="E9">
         <v>-349.5384745614037</v>
@@ -2025,37 +2025,37 @@
         <v>68.72</v>
       </c>
       <c r="M9">
-        <v>4.066399229993341</v>
+        <v>3.967625928372892</v>
       </c>
       <c r="N9">
-        <v>64.65360077000666</v>
+        <v>64.7523740716271</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>64.65360077000666</v>
+        <v>64.7523740716271</v>
       </c>
       <c r="Q9">
-        <v>109.2536007700067</v>
+        <v>109.3523740716271</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.07038746191862427</v>
+        <v>0.07037597933150187</v>
       </c>
       <c r="T9">
         <v>0.4790315804172461</v>
       </c>
       <c r="U9">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V9">
         <v>0</v>
       </c>
       <c r="W9">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.89947201768296</v>
+        <v>17.32018119666382</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2074,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.06961326891732331</v>
+        <v>0.06949059011129946</v>
       </c>
       <c r="C10">
-        <v>1177.853000831562</v>
+        <v>1183.895685119373</v>
       </c>
       <c r="D10">
-        <v>1254.2742674605</v>
+        <v>1260.316951748311</v>
       </c>
       <c r="E10">
         <v>-339.4595662327865</v>
@@ -2107,37 +2107,37 @@
         <v>68.72</v>
       </c>
       <c r="M10">
-        <v>4.647313405706675</v>
+        <v>4.534429632426161</v>
       </c>
       <c r="N10">
-        <v>64.07268659429333</v>
+        <v>64.18557036757383</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>64.07268659429333</v>
+        <v>64.18557036757383</v>
       </c>
       <c r="Q10">
-        <v>108.6726865942933</v>
+        <v>108.7855703675738</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.07065471693947889</v>
+        <v>0.07064310954162689</v>
       </c>
       <c r="T10">
         <v>0.4842384454217813</v>
       </c>
       <c r="U10">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V10">
         <v>0</v>
       </c>
       <c r="W10">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.78703801547259</v>
+        <v>15.15515854708084</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.06973163508394865</v>
+        <v>0.06959495627792482</v>
       </c>
       <c r="C11">
-        <v>1161.570436279067</v>
+        <v>1168.288947806722</v>
       </c>
       <c r="D11">
-        <v>1248.070611236622</v>
+        <v>1254.789122764277</v>
       </c>
       <c r="E11">
         <v>-329.3806579041693</v>
@@ -2189,37 +2189,37 @@
         <v>68.72</v>
       </c>
       <c r="M11">
-        <v>5.228227581420009</v>
+        <v>5.101233336479432</v>
       </c>
       <c r="N11">
-        <v>63.49177241857999</v>
+        <v>63.61876666352057</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>63.49177241857999</v>
+        <v>63.61876666352057</v>
       </c>
       <c r="Q11">
-        <v>108.09177241858</v>
+        <v>108.2187666635206</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.07092784569705558</v>
+        <v>0.07091611074538104</v>
       </c>
       <c r="T11">
         <v>0.489559747019823</v>
       </c>
       <c r="U11">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V11">
         <v>0</v>
       </c>
       <c r="W11">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>13.14403379153119</v>
+        <v>13.47125204184964</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.069960001250574</v>
+        <v>0.06984932244455017</v>
       </c>
       <c r="C12">
-        <v>1139.694463115484</v>
+        <v>1144.938318421653</v>
       </c>
       <c r="D12">
-        <v>1236.273546401657</v>
+        <v>1241.517401707825</v>
       </c>
       <c r="E12">
         <v>-319.301749575552</v>
@@ -2271,37 +2271,37 @@
         <v>68.72</v>
       </c>
       <c r="M12">
-        <v>5.920009748748134</v>
+        <v>5.819220665461962</v>
       </c>
       <c r="N12">
-        <v>62.79999025125186</v>
+        <v>62.90077933453804</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>62.79999025125186</v>
+        <v>62.90077933453804</v>
       </c>
       <c r="Q12">
-        <v>107.3999902512519</v>
+        <v>107.500779334538</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.07120704398257842</v>
+        <v>0.07119517864255194</v>
       </c>
       <c r="T12">
         <v>0.4949992997644877</v>
       </c>
       <c r="U12">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V12">
         <v>0</v>
       </c>
       <c r="W12">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.60808899251083</v>
+        <v>11.8091414556359</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2320,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.07008936741719932</v>
+        <v>0.0699686886111755</v>
       </c>
       <c r="C13">
-        <v>1123.031111196746</v>
+        <v>1128.727709055191</v>
       </c>
       <c r="D13">
-        <v>1229.689102811536</v>
+        <v>1235.38570066998</v>
       </c>
       <c r="E13">
         <v>-309.2228412469348</v>
@@ -2353,37 +2353,37 @@
         <v>68.72</v>
       </c>
       <c r="M13">
-        <v>6.512010723622947</v>
+        <v>6.401142732008156</v>
       </c>
       <c r="N13">
-        <v>62.20798927637705</v>
+        <v>62.31885726799185</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>62.20798927637705</v>
+        <v>62.31885726799185</v>
       </c>
       <c r="Q13">
-        <v>106.807989276377</v>
+        <v>106.9188572679919</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.07149251638687705</v>
+        <v>0.07148051772842332</v>
       </c>
       <c r="T13">
         <v>0.500561089649482</v>
       </c>
       <c r="U13">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V13">
         <v>0</v>
       </c>
       <c r="W13">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.55280817500984</v>
+        <v>10.73558314148719</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.07048273358382466</v>
+        <v>0.07008805477780083</v>
       </c>
       <c r="C14">
-        <v>1093.354775100609</v>
+        <v>1112.577369451331</v>
       </c>
       <c r="D14">
-        <v>1210.091675044016</v>
+        <v>1229.314269394738</v>
       </c>
       <c r="E14">
         <v>-299.1439329183175</v>
@@ -2435,45 +2435,45 @@
         <v>68.72</v>
       </c>
       <c r="M14">
-        <v>7.370094878373255</v>
+        <v>6.983064798554353</v>
       </c>
       <c r="N14">
-        <v>61.34990512162675</v>
+        <v>61.73693520144565</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>61.34990512162675</v>
+        <v>61.73693520144565</v>
       </c>
       <c r="Q14">
-        <v>105.9499051216268</v>
+        <v>106.3369352014456</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.07178447680036429</v>
+        <v>0.07177234179351902</v>
       </c>
       <c r="T14">
         <v>0.5062492838500441</v>
       </c>
       <c r="U14">
-        <v>0.0609366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V14">
         <v>0</v>
       </c>
       <c r="W14">
-        <v>0.0609366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>9.324167617115947</v>
+        <v>9.840951213029921</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2484,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.07063409975045</v>
+        <v>0.07042842094442617</v>
       </c>
       <c r="C15">
-        <v>1075.900244544602</v>
+        <v>1085.509268579844</v>
       </c>
       <c r="D15">
-        <v>1202.716052816626</v>
+        <v>1212.325076851868</v>
       </c>
       <c r="E15">
         <v>-289.0650245897003</v>
@@ -2517,37 +2517,37 @@
         <v>68.72</v>
       </c>
       <c r="M15">
-        <v>7.984269451571027</v>
+        <v>7.787730739162991</v>
       </c>
       <c r="N15">
-        <v>60.73573054842898</v>
+        <v>60.93226926083701</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>60.73573054842898</v>
+        <v>60.93226926083701</v>
       </c>
       <c r="Q15">
-        <v>105.335730548429</v>
+        <v>105.532269260837</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.07208314894749492</v>
+        <v>0.07207087445781235</v>
       </c>
       <c r="T15">
         <v>0.5120682411356768</v>
       </c>
       <c r="U15">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V15">
         <v>0</v>
       </c>
       <c r="W15">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.606923954260875</v>
+        <v>8.824136619724205</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2566,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.07078546591707535</v>
+        <v>0.07056478711105152</v>
       </c>
       <c r="C16">
-        <v>1058.535079515475</v>
+        <v>1068.754747709405</v>
       </c>
       <c r="D16">
-        <v>1195.429796116117</v>
+        <v>1205.649464310047</v>
       </c>
       <c r="E16">
         <v>-278.9861162610831</v>
@@ -2599,37 +2599,37 @@
         <v>68.72</v>
       </c>
       <c r="M16">
-        <v>8.598444024768799</v>
+        <v>8.386786949867837</v>
       </c>
       <c r="N16">
-        <v>60.1215559752312</v>
+        <v>60.33321305013216</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>60.1215559752312</v>
+        <v>60.33321305013216</v>
       </c>
       <c r="Q16">
-        <v>104.7215559752312</v>
+        <v>104.9332130501322</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.07238876695851229</v>
+        <v>0.07237634974220553</v>
       </c>
       <c r="T16">
         <v>0.5180225230093476</v>
       </c>
       <c r="U16">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V16">
         <v>0</v>
       </c>
       <c r="W16">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.992143671813667</v>
+        <v>8.193841146886761</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2648,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.07116183208370069</v>
+        <v>0.07070115327767686</v>
       </c>
       <c r="C17">
-        <v>1030.716154284724</v>
+        <v>1052.073342142668</v>
       </c>
       <c r="D17">
-        <v>1177.689779213983</v>
+        <v>1199.046967071927</v>
       </c>
       <c r="E17">
         <v>-268.9072079324658</v>
@@ -2681,45 +2681,45 @@
         <v>68.72</v>
       </c>
       <c r="M17">
-        <v>9.439394035360456</v>
+        <v>8.98584316057268</v>
       </c>
       <c r="N17">
-        <v>59.28060596463954</v>
+        <v>59.73415683942732</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>59.28060596463954</v>
+        <v>59.73415683942732</v>
       </c>
       <c r="Q17">
-        <v>103.8806059646395</v>
+        <v>104.3341568394273</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.07270157598155362</v>
+        <v>0.07268901268034911</v>
       </c>
       <c r="T17">
         <v>0.524116905632987</v>
       </c>
       <c r="U17">
-        <v>0.0624366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V17">
         <v>0</v>
       </c>
       <c r="W17">
-        <v>0.0624366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>7.280128336900795</v>
+        <v>7.647585070427646</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2730,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.07132819825032603</v>
+        <v>0.0709655194443022</v>
       </c>
       <c r="C18">
-        <v>1012.962292474454</v>
+        <v>1029.398331794773</v>
       </c>
       <c r="D18">
-        <v>1170.01482573233</v>
+        <v>1186.450865052649</v>
       </c>
       <c r="E18">
         <v>-258.8282996038486</v>
@@ -2763,37 +2763,37 @@
         <v>68.72</v>
       </c>
       <c r="M18">
-        <v>10.06868697105115</v>
+        <v>9.713909397883826</v>
       </c>
       <c r="N18">
-        <v>58.65131302894885</v>
+        <v>59.00609060211617</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>58.65131302894885</v>
+        <v>59.00609060211617</v>
       </c>
       <c r="Q18">
-        <v>103.2513130289489</v>
+        <v>103.6060906021162</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.07302183283847688</v>
+        <v>0.07300911997416279</v>
       </c>
       <c r="T18">
         <v>0.5303563926048082</v>
       </c>
       <c r="U18">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V18">
         <v>0</v>
       </c>
       <c r="W18">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.825120315844495</v>
+        <v>7.074391698050081</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2812,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.07149456441695137</v>
+        <v>0.07110988561092754</v>
       </c>
       <c r="C19">
-        <v>995.3078176449512</v>
+        <v>1012.55197433936</v>
       </c>
       <c r="D19">
-        <v>1162.439259231444</v>
+        <v>1179.683415925854</v>
       </c>
       <c r="E19">
         <v>-248.7493912752313</v>
@@ -2845,37 +2845,37 @@
         <v>68.72</v>
       </c>
       <c r="M19">
-        <v>10.69797990674185</v>
+        <v>10.32102873525157</v>
       </c>
       <c r="N19">
-        <v>58.02202009325815</v>
+        <v>58.39897126474843</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>58.02202009325815</v>
+        <v>58.39897126474843</v>
       </c>
       <c r="Q19">
-        <v>102.6220200932582</v>
+        <v>102.9989712647484</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.07334980672809707</v>
+        <v>0.07333694069674307</v>
       </c>
       <c r="T19">
         <v>0.5367462286602879</v>
       </c>
       <c r="U19">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V19">
         <v>0</v>
       </c>
       <c r="W19">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.423642650206582</v>
+        <v>6.658251009929486</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +2894,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.07191293058357671</v>
+        <v>0.07125425177755289</v>
       </c>
       <c r="C20">
-        <v>966.6049844656575</v>
+        <v>995.7823813236807</v>
       </c>
       <c r="D20">
-        <v>1143.815334380768</v>
+        <v>1172.992731238791</v>
       </c>
       <c r="E20">
         <v>-238.6704829466141</v>
@@ -2927,45 +2927,45 @@
         <v>68.72</v>
       </c>
       <c r="M20">
-        <v>11.5812613323137</v>
+        <v>10.9281480726193</v>
       </c>
       <c r="N20">
-        <v>57.1387386676863</v>
+        <v>57.79185192738069</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>57.1387386676863</v>
+        <v>57.79185192738069</v>
       </c>
       <c r="Q20">
-        <v>101.7387386676863</v>
+        <v>102.3918519273807</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.07368577998087875</v>
+        <v>0.07367275704670334</v>
       </c>
       <c r="T20">
         <v>0.5432919143756572</v>
       </c>
       <c r="U20">
-        <v>0.0638366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V20">
         <v>0</v>
       </c>
       <c r="W20">
-        <v>0.0638366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>5.933723281786193</v>
+        <v>6.288348176044516</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +2976,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.07209329675020205</v>
+        <v>0.07158861794417823</v>
       </c>
       <c r="C21">
-        <v>948.6797573908773</v>
+        <v>970.4948610456881</v>
       </c>
       <c r="D21">
-        <v>1135.969015634605</v>
+        <v>1157.784119289416</v>
       </c>
       <c r="E21">
         <v>-228.5915746179969</v>
@@ -3009,37 +3009,37 @@
         <v>68.72</v>
       </c>
       <c r="M21">
-        <v>12.22466473966446</v>
+        <v>11.72676666823077</v>
       </c>
       <c r="N21">
-        <v>56.49533526033554</v>
+        <v>56.99323333176923</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>56.49533526033554</v>
+        <v>56.99323333176923</v>
       </c>
       <c r="Q21">
-        <v>101.0953352603355</v>
+        <v>101.5932333317692</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.07403004886953157</v>
+        <v>0.07401686515839104</v>
       </c>
       <c r="T21">
         <v>0.5499992219605419</v>
       </c>
       <c r="U21">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V21">
         <v>0</v>
       </c>
       <c r="W21">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.621422056429025</v>
+        <v>5.860097838065695</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3058,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.07227366291682741</v>
+        <v>0.07174298411080357</v>
       </c>
       <c r="C22">
-        <v>930.8614449080673</v>
+        <v>953.5268957176496</v>
       </c>
       <c r="D22">
-        <v>1128.229611480412</v>
+        <v>1150.895062289994</v>
       </c>
       <c r="E22">
         <v>-218.5126662893796</v>
@@ -3091,37 +3091,37 @@
         <v>68.72</v>
       </c>
       <c r="M22">
-        <v>12.86806814701523</v>
+        <v>12.34396491392713</v>
       </c>
       <c r="N22">
-        <v>55.85193185298478</v>
+        <v>56.37603508607287</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>55.85193185298478</v>
+        <v>56.37603508607287</v>
       </c>
       <c r="Q22">
-        <v>100.4519318529848</v>
+        <v>100.9760350860729</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.07438292448040072</v>
+        <v>0.07436957597287093</v>
       </c>
       <c r="T22">
         <v>0.5568742122350486</v>
       </c>
       <c r="U22">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V22">
         <v>0</v>
       </c>
       <c r="W22">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.340350953607573</v>
+        <v>5.567092946162409</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3140,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.07245402908345273</v>
+        <v>0.07189735027742891</v>
       </c>
       <c r="C23">
-        <v>913.1478765639316</v>
+        <v>936.6404281132774</v>
       </c>
       <c r="D23">
-        <v>1120.594951464894</v>
+        <v>1144.087503014239</v>
       </c>
       <c r="E23">
         <v>-208.4337579607624</v>
@@ -3173,37 +3173,37 @@
         <v>68.72</v>
       </c>
       <c r="M23">
-        <v>13.51147155436599</v>
+        <v>12.96116315962349</v>
       </c>
       <c r="N23">
-        <v>55.20852844563402</v>
+        <v>55.75883684037652</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>55.20852844563402</v>
+        <v>55.75883684037652</v>
       </c>
       <c r="Q23">
-        <v>99.80852844563401</v>
+        <v>100.3588368403765</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.0747447336510387</v>
+        <v>0.07473121617505918</v>
       </c>
       <c r="T23">
         <v>0.5639232528962518</v>
       </c>
       <c r="U23">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V23">
         <v>0</v>
       </c>
       <c r="W23">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.086048527245309</v>
+        <v>5.301993282059438</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3222,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.07263439525007807</v>
+        <v>0.07205171644405425</v>
       </c>
       <c r="C24">
-        <v>895.5369402595826</v>
+        <v>919.8340205561568</v>
       </c>
       <c r="D24">
-        <v>1113.062923489162</v>
+        <v>1137.360003785736</v>
       </c>
       <c r="E24">
         <v>-198.3548496321451</v>
@@ -3255,37 +3255,37 @@
         <v>68.72</v>
       </c>
       <c r="M24">
-        <v>14.15487496171675</v>
+        <v>13.57836140531984</v>
       </c>
       <c r="N24">
-        <v>54.56512503828325</v>
+        <v>55.14163859468016</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>54.56512503828325</v>
+        <v>55.14163859468016</v>
       </c>
       <c r="Q24">
-        <v>99.16512503828325</v>
+        <v>99.74163859468015</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.07511581997989816</v>
+        <v>0.07510212920294454</v>
       </c>
       <c r="T24">
         <v>0.5711530381897933</v>
       </c>
       <c r="U24">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V24">
         <v>0</v>
       </c>
       <c r="W24">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.854864503279612</v>
+        <v>5.060993587420374</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3304,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.07281476141670341</v>
+        <v>0.07220608261067959</v>
       </c>
       <c r="C25">
-        <v>878.0265803025084</v>
+        <v>903.1062689876721</v>
       </c>
       <c r="D25">
-        <v>1105.631471860705</v>
+        <v>1130.711160545869</v>
       </c>
       <c r="E25">
         <v>-188.2759413035279</v>
@@ -3337,37 +3337,37 @@
         <v>68.72</v>
       </c>
       <c r="M25">
-        <v>14.79827836906751</v>
+        <v>14.1955596510162</v>
       </c>
       <c r="N25">
-        <v>53.92172163093249</v>
+        <v>54.5244403489838</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>53.92172163093249</v>
+        <v>54.5244403489838</v>
       </c>
       <c r="Q25">
-        <v>98.52172163093249</v>
+        <v>99.1244403489838</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.07549654491470204</v>
+        <v>0.07548267633545032</v>
       </c>
       <c r="T25">
         <v>0.5785706101143362</v>
       </c>
       <c r="U25">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V25">
         <v>0</v>
       </c>
       <c r="W25">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.643783437919629</v>
+        <v>4.840950387967313</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3386,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.07361912758332875</v>
+        <v>0.07236044877730492</v>
       </c>
       <c r="C26">
-        <v>835.9792881323403</v>
+        <v>886.455801990096</v>
       </c>
       <c r="D26">
-        <v>1073.663088019154</v>
+        <v>1124.13960187691</v>
       </c>
       <c r="E26">
         <v>-178.1970329749106</v>
@@ -3419,45 +3419,45 @@
         <v>68.72</v>
       </c>
       <c r="M26">
-        <v>16.07060565612398</v>
+        <v>14.81275789671255</v>
       </c>
       <c r="N26">
-        <v>52.64939434387601</v>
+        <v>53.90724210328744</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>52.64939434387601</v>
+        <v>53.90724210328744</v>
       </c>
       <c r="Q26">
-        <v>97.24939434387602</v>
+        <v>98.50724210328744</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.0758872889267376</v>
+        <v>0.07587323786617993</v>
       </c>
       <c r="T26">
         <v>0.5861833813000512</v>
       </c>
       <c r="U26">
-        <v>0.06643661666253409</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V26">
         <v>0</v>
       </c>
       <c r="W26">
-        <v>0.06643661666253409</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.27613006444552</v>
+        <v>4.639244121802008</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3468,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.07382549374995409</v>
+        <v>0.07313981494393026</v>
       </c>
       <c r="C27">
-        <v>817.9944446684324</v>
+        <v>844.3314546538145</v>
       </c>
       <c r="D27">
-        <v>1065.757152883863</v>
+        <v>1092.094162869246</v>
       </c>
       <c r="E27">
         <v>-168.1181246462934</v>
@@ -3501,37 +3501,37 @@
         <v>68.72</v>
       </c>
       <c r="M27">
-        <v>16.74021422512915</v>
+        <v>16.05988791294749</v>
       </c>
       <c r="N27">
-        <v>51.97978577487085</v>
+        <v>52.66011208705251</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>51.97978577487085</v>
+        <v>52.66011208705251</v>
       </c>
       <c r="Q27">
-        <v>96.57978577487086</v>
+        <v>97.26011208705251</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.0762884527790941</v>
+        <v>0.07627421437106233</v>
       </c>
       <c r="T27">
         <v>0.5939991597173852</v>
       </c>
       <c r="U27">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V27">
         <v>0</v>
       </c>
       <c r="W27">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.1050848618677</v>
+        <v>4.278983786966402</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3550,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.07473385991657944</v>
+        <v>0.0733191811105556</v>
       </c>
       <c r="C28">
-        <v>774.4565459973642</v>
+        <v>827.1344295905162</v>
       </c>
       <c r="D28">
-        <v>1032.298162541412</v>
+        <v>1084.976046134565</v>
       </c>
       <c r="E28">
         <v>-158.0392163176761</v>
@@ -3583,45 +3583,45 @@
         <v>68.72</v>
       </c>
       <c r="M28">
-        <v>18.11736215880325</v>
+        <v>16.70228342946539</v>
       </c>
       <c r="N28">
-        <v>50.60263784119675</v>
+        <v>52.01771657053461</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>50.60263784119675</v>
+        <v>52.01771657053461</v>
       </c>
       <c r="Q28">
-        <v>95.20263784119675</v>
+        <v>96.61771657053461</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.0767004588977305</v>
+        <v>0.07668602807877939</v>
       </c>
       <c r="T28">
         <v>0.6020261753892417</v>
       </c>
       <c r="U28">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V28">
         <v>0</v>
       </c>
       <c r="W28">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>3.793046658649966</v>
+        <v>4.114407487467695</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3632,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.07496722608320477</v>
+        <v>0.07444354727718094</v>
       </c>
       <c r="C29">
-        <v>756.1182487121334</v>
+        <v>774.4661608706151</v>
       </c>
       <c r="D29">
-        <v>1024.038773584799</v>
+        <v>1042.386685743281</v>
       </c>
       <c r="E29">
         <v>-147.9603079890589</v>
@@ -3665,37 +3665,37 @@
         <v>68.72</v>
       </c>
       <c r="M29">
-        <v>18.81418378029568</v>
+        <v>18.29713578303762</v>
       </c>
       <c r="N29">
-        <v>49.90581621970432</v>
+        <v>50.42286421696238</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>49.90581621970432</v>
+        <v>50.42286421696238</v>
       </c>
       <c r="Q29">
-        <v>94.50581621970431</v>
+        <v>95.02286421696238</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.07712375285523367</v>
+        <v>0.07710912435383116</v>
       </c>
       <c r="T29">
         <v>0.6102731092986835</v>
       </c>
       <c r="U29">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V29">
         <v>0</v>
       </c>
       <c r="W29">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.652563449070338</v>
+        <v>3.755779091048062</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3714,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.07520059224983011</v>
+        <v>0.07465791344380629</v>
       </c>
       <c r="C30">
-        <v>737.9110686454333</v>
+        <v>756.6440579967924</v>
       </c>
       <c r="D30">
-        <v>1015.910501846716</v>
+        <v>1034.643491198075</v>
       </c>
       <c r="E30">
         <v>-137.8813996604416</v>
@@ -3747,37 +3747,37 @@
         <v>68.72</v>
       </c>
       <c r="M30">
-        <v>19.51100540178811</v>
+        <v>18.97480747870568</v>
       </c>
       <c r="N30">
-        <v>49.20899459821189</v>
+        <v>49.74519252129432</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>49.20899459821189</v>
+        <v>49.74519252129432</v>
       </c>
       <c r="Q30">
-        <v>93.80899459821188</v>
+        <v>94.34519252129432</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.07755880497822301</v>
+        <v>0.07754397330318992</v>
       </c>
       <c r="T30">
         <v>0.6187491247056095</v>
       </c>
       <c r="U30">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V30">
         <v>0</v>
       </c>
       <c r="W30">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.522114754460683</v>
+        <v>3.621644123510631</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3796,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.07679695841645545</v>
+        <v>0.07568427961043162</v>
       </c>
       <c r="C31">
-        <v>675.5120219445777</v>
+        <v>711.0306449811649</v>
       </c>
       <c r="D31">
-        <v>963.5903634744777</v>
+        <v>999.1089865110649</v>
       </c>
       <c r="E31">
         <v>-127.8024913318244</v>
@@ -3829,37 +3829,37 @@
         <v>68.72</v>
       </c>
       <c r="M31">
-        <v>21.58158222847108</v>
+        <v>20.47088653065746</v>
       </c>
       <c r="N31">
-        <v>47.13841777152892</v>
+        <v>48.24911346934255</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>47.13841777152892</v>
+        <v>48.24911346934255</v>
       </c>
       <c r="Q31">
-        <v>91.73841777152893</v>
+        <v>92.84911346934254</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.07800611209059236</v>
+        <v>0.07799107151872781</v>
       </c>
       <c r="T31">
         <v>0.6274639011099139</v>
       </c>
       <c r="U31">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V31">
         <v>0</v>
       </c>
       <c r="W31">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.184196565038799</v>
+        <v>3.356962576930123</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +3878,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.07707732458308079</v>
+        <v>0.07592664577705698</v>
       </c>
       <c r="C32">
-        <v>656.7956057726393</v>
+        <v>692.9139943531362</v>
       </c>
       <c r="D32">
-        <v>954.9528556311566</v>
+        <v>991.0712442116535</v>
       </c>
       <c r="E32">
         <v>-117.7235830032072</v>
@@ -3911,37 +3911,37 @@
         <v>68.72</v>
       </c>
       <c r="M32">
-        <v>22.32577471910801</v>
+        <v>21.17677916964564</v>
       </c>
       <c r="N32">
-        <v>46.39422528089199</v>
+        <v>47.54322083035436</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>46.39422528089199</v>
+        <v>47.54322083035436</v>
       </c>
       <c r="Q32">
-        <v>90.99422528089198</v>
+        <v>92.14322083035435</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.07846619940617225</v>
+        <v>0.07845094396899535</v>
       </c>
       <c r="T32">
         <v>0.6364276711257698</v>
       </c>
       <c r="U32">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V32">
         <v>0</v>
       </c>
       <c r="W32">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.078056679537506</v>
+        <v>3.245063824365786</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08024069074970613</v>
+        <v>0.07616901194368231</v>
       </c>
       <c r="C33">
-        <v>559.0045903849723</v>
+        <v>674.925637447212</v>
       </c>
       <c r="D33">
-        <v>867.2407485721068</v>
+        <v>983.1617956343465</v>
       </c>
       <c r="E33">
         <v>-107.6446746745899</v>
@@ -3993,45 +3993,45 @@
         <v>68.72</v>
       </c>
       <c r="M33">
-        <v>25.9757164808853</v>
+        <v>21.88267180863383</v>
       </c>
       <c r="N33">
-        <v>42.7442835191147</v>
+        <v>46.83732819136617</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>42.7442835191147</v>
+        <v>46.83732819136617</v>
       </c>
       <c r="Q33">
-        <v>87.3442835191147</v>
+        <v>91.43732819136616</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.07893962258597184</v>
+        <v>0.07892414605550253</v>
       </c>
       <c r="T33">
         <v>0.6456512605623752</v>
       </c>
       <c r="U33">
-        <v>0.08313661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V33">
         <v>0</v>
       </c>
       <c r="W33">
-        <v>0.08313661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>2.645547815805922</v>
+        <v>3.140384346160438</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4042,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08061405691633149</v>
+        <v>0.07641137811030765</v>
       </c>
       <c r="C34">
-        <v>539.6248885690043</v>
+        <v>657.0625269594586</v>
       </c>
       <c r="D34">
-        <v>857.9399550847561</v>
+        <v>975.3775934752103</v>
       </c>
       <c r="E34">
         <v>-97.56576634597269</v>
@@ -4075,45 +4075,45 @@
         <v>68.72</v>
       </c>
       <c r="M34">
-        <v>26.81364281897837</v>
+        <v>22.58856444762202</v>
       </c>
       <c r="N34">
-        <v>41.90635718102163</v>
+        <v>46.13143555237798</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>41.90635718102163</v>
+        <v>46.13143555237798</v>
       </c>
       <c r="Q34">
-        <v>86.50635718102163</v>
+        <v>90.73143555237797</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.07942696997694203</v>
+        <v>0.0794112658504364</v>
       </c>
       <c r="T34">
         <v>0.6551461320412337</v>
       </c>
       <c r="U34">
-        <v>0.08313661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V34">
         <v>0</v>
       </c>
       <c r="W34">
-        <v>0.08313661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>2.562874446561988</v>
+        <v>3.042247335342924</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4124,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.08253842308295682</v>
+        <v>0.07922774427693299</v>
       </c>
       <c r="C35">
-        <v>484.6069087175522</v>
+        <v>564.8057596885727</v>
       </c>
       <c r="D35">
-        <v>813.0008835619212</v>
+        <v>893.1997345329418</v>
       </c>
       <c r="E35">
         <v>-87.48685801735542</v>
@@ -4157,45 +4157,45 @@
         <v>68.72</v>
       </c>
       <c r="M35">
-        <v>29.21480783883998</v>
+        <v>25.88876809039629</v>
       </c>
       <c r="N35">
-        <v>39.50519216116002</v>
+        <v>42.8312319096037</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>39.50519216116002</v>
+        <v>42.8312319096037</v>
       </c>
       <c r="Q35">
-        <v>84.10519216116003</v>
+        <v>87.4312319096037</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.07992886505122473</v>
+        <v>0.07991292653477126</v>
       </c>
       <c r="T35">
         <v>0.6649244325194611</v>
       </c>
       <c r="U35">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V35">
         <v>0</v>
       </c>
       <c r="W35">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>2.352231798993365</v>
+        <v>2.65443298653876</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4206,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08295878924958217</v>
+        <v>0.07954811044355833</v>
       </c>
       <c r="C36">
-        <v>465.3307667925851</v>
+        <v>546.2478292392454</v>
       </c>
       <c r="D36">
-        <v>803.8036499655714</v>
+        <v>884.7207124122318</v>
       </c>
       <c r="E36">
         <v>-77.40794968873814</v>
@@ -4239,45 +4239,45 @@
         <v>68.72</v>
       </c>
       <c r="M36">
-        <v>30.10010504607756</v>
+        <v>26.6732762143477</v>
       </c>
       <c r="N36">
-        <v>38.61989495392244</v>
+        <v>42.0467237856523</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>38.61989495392244</v>
+        <v>42.0467237856523</v>
       </c>
       <c r="Q36">
-        <v>83.21989495392245</v>
+        <v>86.64672378565231</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.08044596906715239</v>
+        <v>0.08042978905802536</v>
       </c>
       <c r="T36">
         <v>0.6749990451333923</v>
       </c>
       <c r="U36">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V36">
         <v>0</v>
       </c>
       <c r="W36">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.283048510787677</v>
+        <v>2.57636142811115</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4288,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.0833791554162075</v>
+        <v>0.07986847661018368</v>
       </c>
       <c r="C37">
-        <v>446.2603881844163</v>
+        <v>527.849365375092</v>
       </c>
       <c r="D37">
-        <v>794.8121796860198</v>
+        <v>876.4011568766955</v>
       </c>
       <c r="E37">
         <v>-67.32904136012093</v>
@@ -4321,45 +4321,45 @@
         <v>68.72</v>
       </c>
       <c r="M37">
-        <v>30.98540225331513</v>
+        <v>27.4577843382991</v>
       </c>
       <c r="N37">
-        <v>37.73459774668487</v>
+        <v>41.2622156617009</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>37.73459774668487</v>
+        <v>41.2622156617009</v>
       </c>
       <c r="Q37">
-        <v>82.33459774668486</v>
+        <v>85.8622156617009</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.0809789839758778</v>
+        <v>0.08096255504353345</v>
       </c>
       <c r="T37">
         <v>0.6853836458277521</v>
       </c>
       <c r="U37">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V37">
         <v>0</v>
       </c>
       <c r="W37">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>2.2178185533366</v>
+        <v>2.502751101593689</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4370,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08379952158283285</v>
+        <v>0.08159284277680903</v>
       </c>
       <c r="C38">
-        <v>427.3889441804894</v>
+        <v>475.5487058228289</v>
       </c>
       <c r="D38">
-        <v>786.0196440107102</v>
+        <v>834.1794056530497</v>
       </c>
       <c r="E38">
         <v>-57.25013303150371</v>
@@ -4403,37 +4403,37 @@
         <v>68.72</v>
       </c>
       <c r="M38">
-        <v>31.8706994605527</v>
+        <v>29.65737119158836</v>
       </c>
       <c r="N38">
-        <v>36.8493005394473</v>
+        <v>39.06262880841165</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
       <c r="P38">
-        <v>36.8493005394473</v>
+        <v>39.06262880841165</v>
       </c>
       <c r="Q38">
-        <v>81.44930053944731</v>
+        <v>83.66262880841165</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.0815286556005009</v>
+        <v>0.08151196996608867</v>
       </c>
       <c r="T38">
         <v>0.6960927652938108</v>
       </c>
       <c r="U38">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V38">
         <v>0</v>
       </c>
       <c r="W38">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.156212482410584</v>
+        <v>2.317130522326634</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4452,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08421988774945818</v>
+        <v>0.08195220894343436</v>
       </c>
       <c r="C39">
-        <v>408.7099049301037</v>
+        <v>457.1777493995469</v>
       </c>
       <c r="D39">
-        <v>777.4195130889417</v>
+        <v>825.8873575583849</v>
       </c>
       <c r="E39">
         <v>-47.17122470288643</v>
@@ -4485,37 +4485,37 @@
         <v>68.72</v>
       </c>
       <c r="M39">
-        <v>32.75599666779028</v>
+        <v>30.48118705802137</v>
       </c>
       <c r="N39">
-        <v>35.96400333220972</v>
+        <v>38.23881294197863</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
       <c r="P39">
-        <v>35.96400333220972</v>
+        <v>38.23881294197863</v>
       </c>
       <c r="Q39">
-        <v>80.56400333220972</v>
+        <v>82.83881294197863</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.08209577711796917</v>
+        <v>0.08207882663221705</v>
       </c>
       <c r="T39">
         <v>0.707141856806411</v>
       </c>
       <c r="U39">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V39">
         <v>0</v>
       </c>
       <c r="W39">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.09793646937246</v>
+        <v>2.254505373074563</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4534,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08464025391608351</v>
+        <v>0.0823115751100597</v>
       </c>
       <c r="C40">
-        <v>390.2170232715747</v>
+        <v>438.9700223920469</v>
       </c>
       <c r="D40">
-        <v>769.0055397590299</v>
+        <v>817.7585388795021</v>
       </c>
       <c r="E40">
         <v>-37.09231637426922</v>
@@ -4567,37 +4567,37 @@
         <v>68.72</v>
       </c>
       <c r="M40">
-        <v>33.64129387502785</v>
+        <v>31.30500292445438</v>
       </c>
       <c r="N40">
-        <v>35.07870612497215</v>
+        <v>37.41499707554562</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
       <c r="P40">
-        <v>35.07870612497215</v>
+        <v>37.41499707554562</v>
       </c>
       <c r="Q40">
-        <v>79.67870612497215</v>
+        <v>82.01499707554562</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.0826811928779364</v>
+        <v>0.08266396899725281</v>
       </c>
       <c r="T40">
         <v>0.7185473706258692</v>
       </c>
       <c r="U40">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V40">
         <v>0</v>
       </c>
       <c r="W40">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.04272761491529</v>
+        <v>2.195176284309443</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4616,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.09141762008270887</v>
+        <v>0.08267094127668505</v>
       </c>
       <c r="C41">
-        <v>265.8876977212611</v>
+        <v>420.9207520068442</v>
       </c>
       <c r="D41">
-        <v>654.7551225373336</v>
+        <v>809.7881768229167</v>
       </c>
       <c r="E41">
         <v>-27.01340804565194</v>
@@ -4649,45 +4649,45 @@
         <v>68.72</v>
       </c>
       <c r="M41">
-        <v>40.93375310676741</v>
+        <v>32.12881879088739</v>
       </c>
       <c r="N41">
-        <v>27.78624689323259</v>
+        <v>36.59118120911261</v>
       </c>
       <c r="O41">
         <v>0</v>
       </c>
       <c r="P41">
-        <v>27.78624689323259</v>
+        <v>36.59118120911261</v>
       </c>
       <c r="Q41">
-        <v>72.3862468932326</v>
+        <v>81.19118120911261</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.08328580259724684</v>
+        <v>0.08326829635786352</v>
       </c>
       <c r="T41">
         <v>0.7303268357180965</v>
       </c>
       <c r="U41">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V41">
         <v>0</v>
       </c>
       <c r="W41">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y41">
-        <v>1.67881014527932</v>
+        <v>2.138889712916893</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4698,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.09200098624933421</v>
+        <v>0.08303030744331039</v>
       </c>
       <c r="C42">
-        <v>247.5413904273585</v>
+        <v>403.0253497283318</v>
       </c>
       <c r="D42">
-        <v>646.4877235720483</v>
+        <v>801.9716828730216</v>
       </c>
       <c r="E42">
         <v>-16.93449971703467</v>
@@ -4731,45 +4731,45 @@
         <v>68.72</v>
       </c>
       <c r="M42">
-        <v>41.98333651976145</v>
+        <v>32.9526346573204</v>
       </c>
       <c r="N42">
-        <v>26.73666348023855</v>
+        <v>35.7673653426796</v>
       </c>
       <c r="O42">
         <v>0</v>
       </c>
       <c r="P42">
-        <v>26.73666348023855</v>
+        <v>35.7673653426796</v>
       </c>
       <c r="Q42">
-        <v>71.33666348023854</v>
+        <v>80.36736534267959</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.08391056597386762</v>
+        <v>0.08389276796382791</v>
       </c>
       <c r="T42">
         <v>0.7424989496467315</v>
       </c>
       <c r="U42">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V42">
         <v>0</v>
       </c>
       <c r="W42">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y42">
-        <v>1.636839891647337</v>
+        <v>2.08541747009397</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4780,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.09258435241595955</v>
+        <v>0.08338967360993574</v>
       </c>
       <c r="C43">
-        <v>229.4012597969462</v>
+        <v>385.279402510077</v>
       </c>
       <c r="D43">
-        <v>638.4265012702532</v>
+        <v>794.304643983384</v>
       </c>
       <c r="E43">
         <v>-6.855591388417452</v>
@@ -4813,45 +4813,45 @@
         <v>68.72</v>
       </c>
       <c r="M43">
-        <v>43.03291993275549</v>
+        <v>33.77645052375341</v>
       </c>
       <c r="N43">
-        <v>25.68708006724451</v>
+        <v>34.94354947624659</v>
       </c>
       <c r="O43">
         <v>0</v>
       </c>
       <c r="P43">
-        <v>25.68708006724451</v>
+        <v>34.94354947624659</v>
       </c>
       <c r="Q43">
-        <v>70.28708006724452</v>
+        <v>79.5435494762466</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.08455650777003487</v>
+        <v>0.08453840809880805</v>
       </c>
       <c r="T43">
         <v>0.7550836776068456</v>
       </c>
       <c r="U43">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V43">
         <v>0</v>
       </c>
       <c r="W43">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y43">
-        <v>1.596916967460816</v>
+        <v>2.034553629359971</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4862,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.09316771858258491</v>
+        <v>0.08971303977656107</v>
       </c>
       <c r="C44">
-        <v>211.4596882060331</v>
+        <v>260.8226433810056</v>
       </c>
       <c r="D44">
-        <v>630.5638380079573</v>
+        <v>679.9267931829298</v>
       </c>
       <c r="E44">
         <v>3.223316940199766</v>
@@ -4895,37 +4895,37 @@
         <v>68.72</v>
       </c>
       <c r="M44">
-        <v>44.08250334574952</v>
+        <v>40.61132731737374</v>
       </c>
       <c r="N44">
-        <v>24.63749665425048</v>
+        <v>28.10867268262626</v>
       </c>
       <c r="O44">
         <v>0</v>
       </c>
       <c r="P44">
-        <v>24.63749665425048</v>
+        <v>28.10867268262626</v>
       </c>
       <c r="Q44">
-        <v>69.23749665425048</v>
+        <v>72.70867268262626</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.08522472342124238</v>
+        <v>0.08520631168671852</v>
       </c>
       <c r="T44">
         <v>0.7681023617035153</v>
       </c>
       <c r="U44">
-        <v>0.1041366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V44">
         <v>0</v>
       </c>
       <c r="W44">
-        <v>0.1041366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.558895134902225</v>
+        <v>1.69213873417531</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +4944,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.09375108474921023</v>
+        <v>0.09021440594318642</v>
       </c>
       <c r="C45">
-        <v>193.7094287304053</v>
+        <v>243.0684710779013</v>
       </c>
       <c r="D45">
-        <v>622.8924868609467</v>
+        <v>672.2515292084428</v>
       </c>
       <c r="E45">
         <v>13.30222526881704</v>
@@ -4977,37 +4977,37 @@
         <v>68.72</v>
       </c>
       <c r="M45">
-        <v>45.13208675874356</v>
+        <v>41.57826368207312</v>
       </c>
       <c r="N45">
-        <v>23.58791324125644</v>
+        <v>27.14173631792688</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>23.58791324125644</v>
+        <v>27.14173631792688</v>
       </c>
       <c r="Q45">
-        <v>68.18791324125644</v>
+        <v>71.74173631792688</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.08591638523565012</v>
+        <v>0.08589765048823991</v>
       </c>
       <c r="T45">
         <v>0.7815778417334015</v>
       </c>
       <c r="U45">
-        <v>0.1041366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V45">
         <v>0</v>
       </c>
       <c r="W45">
-        <v>0.1041366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.522641759671941</v>
+        <v>1.652786670589838</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5026,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1231104509158356</v>
+        <v>0.09071577210981176</v>
       </c>
       <c r="C46">
-        <v>-52.91872213334409</v>
+        <v>225.4856469447589</v>
       </c>
       <c r="D46">
-        <v>386.3432443258147</v>
+        <v>664.7476134039176</v>
       </c>
       <c r="E46">
         <v>23.38113359743426</v>
@@ -5059,45 +5059,45 @@
         <v>68.72</v>
       </c>
       <c r="M46">
-        <v>75.18473677816658</v>
+        <v>42.54520004677249</v>
       </c>
       <c r="N46">
-        <v>-6.464736778166582</v>
+        <v>26.17479995322751</v>
       </c>
       <c r="O46">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P46">
-        <v>-6.464736778166582</v>
+        <v>26.17479995322751</v>
       </c>
       <c r="Q46">
-        <v>38.13526322183342</v>
+        <v>70.7747999532275</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.0866327492577153</v>
+        <v>0.08661367996124419</v>
       </c>
       <c r="T46">
         <v>0.7955345889072123</v>
       </c>
       <c r="U46">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V46">
         <v>0</v>
       </c>
       <c r="W46">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>0.9140153034353121</v>
+        <v>1.615223337167341</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5108,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1243478170824609</v>
+        <v>0.0912171382764371</v>
       </c>
       <c r="C47">
-        <v>-69.08370741469395</v>
+        <v>208.0684963720553</v>
       </c>
       <c r="D47">
-        <v>380.2571673730821</v>
+        <v>657.4093711598313</v>
       </c>
       <c r="E47">
         <v>33.46004192605153</v>
@@ -5141,45 +5141,45 @@
         <v>68.72</v>
       </c>
       <c r="M47">
-        <v>76.89348079585218</v>
+        <v>43.51213641147187</v>
       </c>
       <c r="N47">
-        <v>-8.173480795852186</v>
+        <v>25.20786358852813</v>
       </c>
       <c r="O47">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P47">
-        <v>-8.173480795852186</v>
+        <v>25.20786358852813</v>
       </c>
       <c r="Q47">
-        <v>36.42651920414782</v>
+        <v>69.80786358852814</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.08737516288058286</v>
+        <v>0.08735574686963045</v>
       </c>
       <c r="T47">
         <v>0.8099988541600707</v>
       </c>
       <c r="U47">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V47">
         <v>0</v>
       </c>
       <c r="W47">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y47">
-        <v>0.8937038522478608</v>
+        <v>1.579329485230289</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5190,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1255851832490863</v>
+        <v>0.09171850444306244</v>
       </c>
       <c r="C48">
-        <v>-85.0599181541524</v>
+        <v>190.8115925856225</v>
       </c>
       <c r="D48">
-        <v>374.3598649622409</v>
+        <v>650.2313757020157</v>
       </c>
       <c r="E48">
         <v>43.53895025466875</v>
@@ -5223,45 +5223,45 @@
         <v>68.72</v>
       </c>
       <c r="M48">
-        <v>78.60222481353779</v>
+        <v>44.47907277617124</v>
       </c>
       <c r="N48">
-        <v>-9.882224813537789</v>
+        <v>24.24092722382876</v>
       </c>
       <c r="O48">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P48">
-        <v>-9.882224813537789</v>
+        <v>24.24092722382876</v>
       </c>
       <c r="Q48">
-        <v>34.71777518646221</v>
+        <v>68.84092722382876</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.08814507330429736</v>
+        <v>0.08812529773758657</v>
       </c>
       <c r="T48">
         <v>0.8249988329408128</v>
       </c>
       <c r="U48">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V48">
         <v>0</v>
       </c>
       <c r="W48">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.8742755076337768</v>
+        <v>1.54499623555137</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5272,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1268225494157116</v>
+        <v>0.09221987060968778</v>
       </c>
       <c r="C49">
-        <v>-100.8560031747795</v>
+        <v>173.7097432626974</v>
       </c>
       <c r="D49">
-        <v>368.642688270231</v>
+        <v>643.2084347077079</v>
       </c>
       <c r="E49">
         <v>53.61785858328602</v>
@@ -5305,45 +5305,45 @@
         <v>68.72</v>
       </c>
       <c r="M49">
-        <v>80.31096883122341</v>
+        <v>45.44600914087062</v>
       </c>
       <c r="N49">
-        <v>-11.59096883122341</v>
+        <v>23.27399085912938</v>
       </c>
       <c r="O49">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>-11.59096883122341</v>
+        <v>23.27399085912938</v>
       </c>
       <c r="Q49">
-        <v>33.00903116877659</v>
+        <v>67.87399085912938</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.08894403695154826</v>
+        <v>0.08892388826093725</v>
       </c>
       <c r="T49">
         <v>0.8405648486566771</v>
       </c>
       <c r="U49">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V49">
         <v>0</v>
       </c>
       <c r="W49">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y49">
-        <v>0.8556739010883772</v>
+        <v>1.51212397522049</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5354,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.128059915582337</v>
+        <v>0.1199852367763131</v>
       </c>
       <c r="C50">
-        <v>-116.4800909119851</v>
+        <v>-77.10328531912478</v>
       </c>
       <c r="D50">
-        <v>363.0975088616427</v>
+        <v>402.474314454503</v>
       </c>
       <c r="E50">
         <v>63.69676691190324</v>
@@ -5387,37 +5387,37 @@
         <v>68.72</v>
       </c>
       <c r="M50">
-        <v>82.01971284890899</v>
+        <v>73.89208117271205</v>
       </c>
       <c r="N50">
-        <v>-13.299712848909</v>
+        <v>-5.172081172712055</v>
       </c>
       <c r="O50">
         <v>-0</v>
       </c>
       <c r="P50">
-        <v>-13.299712848909</v>
+        <v>-5.172081172712055</v>
       </c>
       <c r="Q50">
-        <v>31.30028715109101</v>
+        <v>39.42791882728795</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.08977372996984725</v>
+        <v>0.08975319380441682</v>
       </c>
       <c r="T50">
         <v>0.8567295572846901</v>
       </c>
       <c r="U50">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V50">
         <v>0</v>
       </c>
       <c r="W50">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8378473614823695</v>
+        <v>0.9300049329964998</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5436,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1292972817489623</v>
+        <v>0.1210546029429385</v>
       </c>
       <c r="C51">
-        <v>-131.9398279722744</v>
+        <v>-92.90134434394218</v>
       </c>
       <c r="D51">
-        <v>357.7166801299705</v>
+        <v>396.7551637583028</v>
       </c>
       <c r="E51">
         <v>73.77567524052046</v>
@@ -5469,37 +5469,37 @@
         <v>68.72</v>
       </c>
       <c r="M51">
-        <v>83.7284568665946</v>
+        <v>75.43149953047688</v>
       </c>
       <c r="N51">
-        <v>-15.0084568665946</v>
+        <v>-6.711499530476885</v>
       </c>
       <c r="O51">
         <v>-0</v>
       </c>
       <c r="P51">
-        <v>-15.0084568665946</v>
+        <v>-6.711499530476885</v>
       </c>
       <c r="Q51">
-        <v>29.5915431334054</v>
+        <v>37.88850046952312</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.09063595996925602</v>
+        <v>0.09061502113391519</v>
       </c>
       <c r="T51">
         <v>0.8735281760549782</v>
       </c>
       <c r="U51">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V51">
         <v>0</v>
       </c>
       <c r="W51">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8207484357378313</v>
+        <v>0.9110252404863672</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5518,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1305346479155876</v>
+        <v>0.1221239691095638</v>
       </c>
       <c r="C52">
-        <v>-147.2424143135897</v>
+        <v>-108.5391426714269</v>
       </c>
       <c r="D52">
-        <v>352.4930021172725</v>
+        <v>391.1962737594353</v>
       </c>
       <c r="E52">
         <v>83.85458356913773</v>
@@ -5551,37 +5551,37 @@
         <v>68.72</v>
       </c>
       <c r="M52">
-        <v>85.4372008842802</v>
+        <v>76.97091788824171</v>
       </c>
       <c r="N52">
-        <v>-16.7172008842802</v>
+        <v>-8.250917888241716</v>
       </c>
       <c r="O52">
         <v>-0</v>
       </c>
       <c r="P52">
-        <v>-16.7172008842802</v>
+        <v>-8.250917888241716</v>
       </c>
       <c r="Q52">
-        <v>27.8827991157198</v>
+        <v>36.34908211175829</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.09153267916864115</v>
+        <v>0.0915113215565935</v>
       </c>
       <c r="T52">
         <v>0.8909987395760778</v>
       </c>
       <c r="U52">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V52">
         <v>0</v>
       </c>
       <c r="W52">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8043334670230747</v>
+        <v>0.8928047356766399</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5600,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.158394014082213</v>
+        <v>0.1231933352761891</v>
       </c>
       <c r="C53">
-        <v>-244.5393838971124</v>
+        <v>-124.0233234072271</v>
       </c>
       <c r="D53">
-        <v>265.2749408623671</v>
+        <v>385.7910013522524</v>
       </c>
       <c r="E53">
         <v>93.93349189775495</v>
@@ -5633,45 +5633,45 @@
         <v>68.72</v>
       </c>
       <c r="M53">
-        <v>113.9780146544106</v>
+        <v>78.51033624600655</v>
       </c>
       <c r="N53">
-        <v>-45.25801465441063</v>
+        <v>-9.790336246006547</v>
       </c>
       <c r="O53">
         <v>-0</v>
       </c>
       <c r="P53">
-        <v>-45.25801465441063</v>
+        <v>-9.790336246006547</v>
       </c>
       <c r="Q53">
-        <v>-0.6580146544106285</v>
+        <v>34.80966375399345</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.09246599915167464</v>
+        <v>0.09244420566999337</v>
       </c>
       <c r="T53">
         <v>0.9091823873225283</v>
       </c>
       <c r="U53">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V53">
         <v>0</v>
       </c>
       <c r="W53">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y53">
-        <v>0.6029232936576749</v>
+        <v>0.875298760467294</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5682,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1601533802488383</v>
+        <v>0.1242627014428145</v>
       </c>
       <c r="C54">
-        <v>-258.6996386169881</v>
+        <v>-139.3601675021179</v>
       </c>
       <c r="D54">
-        <v>261.1935944711087</v>
+        <v>380.5330655859789</v>
       </c>
       <c r="E54">
         <v>104.0124002263723</v>
@@ -5715,45 +5715,45 @@
         <v>68.72</v>
       </c>
       <c r="M54">
-        <v>116.2128776868501</v>
+        <v>80.04975460377139</v>
       </c>
       <c r="N54">
-        <v>-47.49287768685008</v>
+        <v>-11.32975460377139</v>
       </c>
       <c r="O54">
         <v>-0</v>
       </c>
       <c r="P54">
-        <v>-47.49287768685008</v>
+        <v>-11.32975460377139</v>
       </c>
       <c r="Q54">
-        <v>-2.892877686850078</v>
+        <v>33.27024539622861</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.09343820746733453</v>
+        <v>0.09341595995478488</v>
       </c>
       <c r="T54">
         <v>0.9281236870584144</v>
       </c>
       <c r="U54">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V54">
         <v>0</v>
       </c>
       <c r="W54">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.5913286149334888</v>
+        <v>0.858466091996769</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5764,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1619127464154637</v>
+        <v>0.1253320676094398</v>
       </c>
       <c r="C55">
-        <v>-272.7362103997747</v>
+        <v>-154.5556180991718</v>
       </c>
       <c r="D55">
-        <v>257.2359310169393</v>
+        <v>375.4165233175422</v>
       </c>
       <c r="E55">
         <v>114.0913085549895</v>
@@ -5797,45 +5797,45 @@
         <v>68.72</v>
       </c>
       <c r="M55">
-        <v>118.4477407192895</v>
+        <v>81.58917296153622</v>
       </c>
       <c r="N55">
-        <v>-49.7277407192895</v>
+        <v>-12.86917296153622</v>
       </c>
       <c r="O55">
         <v>-0</v>
       </c>
       <c r="P55">
-        <v>-49.7277407192895</v>
+        <v>-12.86917296153622</v>
       </c>
       <c r="Q55">
-        <v>-5.127740719289498</v>
+        <v>31.73082703846378</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.09445178634961823</v>
+        <v>0.09442906548573776</v>
       </c>
       <c r="T55">
         <v>0.9478709995490189</v>
       </c>
       <c r="U55">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V55">
         <v>0</v>
       </c>
       <c r="W55">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.5801714712554984</v>
+        <v>0.8422686185628678</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5846,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.163672112582089</v>
+        <v>0.1264014337760652</v>
       </c>
       <c r="C56">
-        <v>-286.6546375421096</v>
+        <v>-169.6153029427982</v>
       </c>
       <c r="D56">
-        <v>253.3964122032216</v>
+        <v>370.4357468025331</v>
       </c>
       <c r="E56">
         <v>124.1702168836067</v>
@@ -5879,45 +5879,45 @@
         <v>68.72</v>
       </c>
       <c r="M56">
-        <v>120.6826037517289</v>
+        <v>83.12859131930105</v>
       </c>
       <c r="N56">
-        <v>-51.96260375172892</v>
+        <v>-14.40859131930105</v>
       </c>
       <c r="O56">
         <v>-0</v>
       </c>
       <c r="P56">
-        <v>-51.96260375172892</v>
+        <v>-14.40859131930105</v>
       </c>
       <c r="Q56">
-        <v>-7.362603751728919</v>
+        <v>30.19140868069895</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.09550943387895777</v>
+        <v>0.09548621908325379</v>
       </c>
       <c r="T56">
         <v>0.9684768908435627</v>
       </c>
       <c r="U56">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V56">
         <v>0</v>
       </c>
       <c r="W56">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.5694275551211374</v>
+        <v>0.8266710515524444</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +5928,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1654314787487143</v>
+        <v>0.1274707999426905</v>
       </c>
       <c r="C57">
-        <v>-300.4601325437131</v>
+        <v>-184.544555027289</v>
       </c>
       <c r="D57">
-        <v>249.6698255302354</v>
+        <v>365.5854030466596</v>
       </c>
       <c r="E57">
         <v>134.249125212224</v>
@@ -5961,45 +5961,45 @@
         <v>68.72</v>
       </c>
       <c r="M57">
-        <v>122.9174667841684</v>
+        <v>84.66800967706591</v>
       </c>
       <c r="N57">
-        <v>-54.19746678416836</v>
+        <v>-15.94800967706591</v>
       </c>
       <c r="O57">
         <v>-0</v>
       </c>
       <c r="P57">
-        <v>-54.19746678416836</v>
+        <v>-15.94800967706591</v>
       </c>
       <c r="Q57">
-        <v>-9.597466784168354</v>
+        <v>28.65199032293409</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.09661408796515683</v>
+        <v>0.09659035728510389</v>
       </c>
       <c r="T57">
         <v>0.9899985995289754</v>
       </c>
       <c r="U57">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V57">
         <v>0</v>
       </c>
       <c r="W57">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.5590743268462075</v>
+        <v>0.8116406687969451</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6010,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1671908449153397</v>
+        <v>0.1587801661093158</v>
       </c>
       <c r="C58">
-        <v>-314.1576057169157</v>
+        <v>-295.9354692002432</v>
       </c>
       <c r="D58">
-        <v>246.0512606856501</v>
+        <v>264.2733972023225</v>
       </c>
       <c r="E58">
         <v>144.3280335408413</v>
@@ -6043,37 +6043,37 @@
         <v>68.72</v>
       </c>
       <c r="M58">
-        <v>125.1523298166078</v>
+        <v>116.6860468205693</v>
       </c>
       <c r="N58">
-        <v>-56.43232981660778</v>
+        <v>-47.96604682056928</v>
       </c>
       <c r="O58">
         <v>-0</v>
       </c>
       <c r="P58">
-        <v>-56.43232981660778</v>
+        <v>-47.96604682056928</v>
       </c>
       <c r="Q58">
-        <v>-11.83232981660777</v>
+        <v>-3.366046820569274</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.09776895360072857</v>
+        <v>0.09774468358703806</v>
       </c>
       <c r="T58">
         <v>1.012498567700088</v>
       </c>
       <c r="U58">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V58">
         <v>0</v>
       </c>
       <c r="W58">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5490908567239539</v>
+        <v>0.5889307408423243</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6092,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.168950211081965</v>
+        <v>0.1603895322759412</v>
       </c>
       <c r="C59">
-        <v>-327.7516867724211</v>
+        <v>-309.7259963455982</v>
       </c>
       <c r="D59">
-        <v>242.5360879587619</v>
+        <v>260.5617783855848</v>
       </c>
       <c r="E59">
         <v>154.4069418694585</v>
@@ -6125,37 +6125,37 @@
         <v>68.72</v>
       </c>
       <c r="M59">
-        <v>127.3871928490472</v>
+        <v>118.7697262280794</v>
       </c>
       <c r="N59">
-        <v>-58.6671928490472</v>
+        <v>-50.04972622807944</v>
       </c>
       <c r="O59">
         <v>-0</v>
       </c>
       <c r="P59">
-        <v>-58.6671928490472</v>
+        <v>-50.04972622807944</v>
       </c>
       <c r="Q59">
-        <v>-14.0671928490472</v>
+        <v>-5.449726228079435</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.0989775339170246</v>
+        <v>0.09895269948441106</v>
       </c>
       <c r="T59">
         <v>1.036045046018695</v>
       </c>
       <c r="U59">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V59">
         <v>0</v>
       </c>
       <c r="W59">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5394576837989722</v>
+        <v>0.5785986225819326</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6174,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1707095772485903</v>
+        <v>0.1619988984425665</v>
       </c>
       <c r="C60">
-        <v>-341.2467445808421</v>
+        <v>-323.4137109199713</v>
       </c>
       <c r="D60">
-        <v>239.119938478958</v>
+        <v>256.9529721398289</v>
       </c>
       <c r="E60">
         <v>164.4858501980757</v>
@@ -6207,37 +6207,37 @@
         <v>68.72</v>
       </c>
       <c r="M60">
-        <v>129.6220558814866</v>
+        <v>120.8534056355896</v>
       </c>
       <c r="N60">
-        <v>-60.9020558814866</v>
+        <v>-52.1334056355896</v>
       </c>
       <c r="O60">
         <v>-0</v>
       </c>
       <c r="P60">
-        <v>-60.9020558814866</v>
+        <v>-52.1334056355896</v>
       </c>
       <c r="Q60">
-        <v>-16.3020558814866</v>
+        <v>-7.533405635589595</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1002436656769537</v>
+        <v>0.1002182399483256</v>
       </c>
       <c r="T60">
         <v>1.060712785209616</v>
       </c>
       <c r="U60">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V60">
         <v>0</v>
       </c>
       <c r="W60">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5301566892507141</v>
+        <v>0.5686227842615545</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6256,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1724689434152157</v>
+        <v>0.1636082646091918</v>
       </c>
       <c r="C61">
-        <v>-354.6469052873716</v>
+        <v>-337.0028264581376</v>
       </c>
       <c r="D61">
-        <v>235.7986861010457</v>
+        <v>253.4427649302798</v>
       </c>
       <c r="E61">
         <v>174.5647585266929</v>
@@ -6289,37 +6289,37 @@
         <v>68.72</v>
       </c>
       <c r="M61">
-        <v>131.856918913926</v>
+        <v>122.9370850430998</v>
       </c>
       <c r="N61">
-        <v>-63.13691891392602</v>
+        <v>-54.21708504309976</v>
       </c>
       <c r="O61">
         <v>-0</v>
       </c>
       <c r="P61">
-        <v>-63.13691891392602</v>
+        <v>-54.21708504309976</v>
       </c>
       <c r="Q61">
-        <v>-18.53691891392602</v>
+        <v>-9.617085043099756</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1015715599617575</v>
+        <v>0.1015455140934067</v>
       </c>
       <c r="T61">
         <v>1.086583828751314</v>
       </c>
       <c r="U61">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V61">
         <v>0</v>
       </c>
       <c r="W61">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5211709826532445</v>
+        <v>0.5589851099520367</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6338,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.174228309581841</v>
+        <v>0.1652176307758172</v>
       </c>
       <c r="C62">
-        <v>-367.9560689375115</v>
+        <v>-350.4973293552025</v>
       </c>
       <c r="D62">
-        <v>232.5684307795231</v>
+        <v>250.0271703618321</v>
       </c>
       <c r="E62">
         <v>184.6436668553101</v>
@@ -6371,37 +6371,37 @@
         <v>68.72</v>
       </c>
       <c r="M62">
-        <v>134.0917819463654</v>
+        <v>125.0207644506099</v>
       </c>
       <c r="N62">
-        <v>-65.37178194636545</v>
+        <v>-56.30076445060992</v>
       </c>
       <c r="O62">
         <v>-0</v>
       </c>
       <c r="P62">
-        <v>-65.37178194636545</v>
+        <v>-56.30076445060992</v>
       </c>
       <c r="Q62">
-        <v>-20.77178194636544</v>
+        <v>-11.70076445060992</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1029658489608014</v>
+        <v>0.1029391519457419</v>
       </c>
       <c r="T62">
         <v>1.113748424470097</v>
       </c>
       <c r="U62">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V62">
         <v>0</v>
       </c>
       <c r="W62">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5124847996090237</v>
+        <v>0.5496686914528361</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6420,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1759876757484664</v>
+        <v>0.1668269969424425</v>
       </c>
       <c r="C63">
-        <v>-381.1779247547159</v>
+        <v>-363.9009939686409</v>
       </c>
       <c r="D63">
-        <v>229.425483290936</v>
+        <v>246.702414077011</v>
       </c>
       <c r="E63">
         <v>194.7225751839275</v>
@@ -6453,37 +6453,37 @@
         <v>68.72</v>
       </c>
       <c r="M63">
-        <v>136.3266449788049</v>
+        <v>127.1044438581201</v>
       </c>
       <c r="N63">
-        <v>-67.60664497880489</v>
+        <v>-58.38444385812011</v>
       </c>
       <c r="O63">
         <v>-0</v>
       </c>
       <c r="P63">
-        <v>-67.60664497880489</v>
+        <v>-58.38444385812011</v>
       </c>
       <c r="Q63">
-        <v>-23.00664497880489</v>
+        <v>-13.78444385812011</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1044316399597963</v>
+        <v>0.1044042584058891</v>
       </c>
       <c r="T63">
         <v>1.142306076379587</v>
       </c>
       <c r="U63">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V63">
         <v>0</v>
       </c>
       <c r="W63">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5040834094514987</v>
+        <v>0.5406577292978714</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6502,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1963470419150917</v>
+        <v>0.1684363631090679</v>
       </c>
       <c r="C64">
-        <v>-422.28339702545</v>
+        <v>-377.2173965312256</v>
       </c>
       <c r="D64">
-        <v>198.3989193488191</v>
+        <v>243.4649198430436</v>
       </c>
       <c r="E64">
         <v>204.8014835125447</v>
@@ -6535,45 +6535,45 @@
         <v>68.72</v>
       </c>
       <c r="M64">
-        <v>157.3082775024724</v>
+        <v>129.1881232656303</v>
       </c>
       <c r="N64">
-        <v>-88.58827750247238</v>
+        <v>-60.46812326563025</v>
       </c>
       <c r="O64">
         <v>-0</v>
       </c>
       <c r="P64">
-        <v>-88.58827750247238</v>
+        <v>-60.46812326563025</v>
       </c>
       <c r="Q64">
-        <v>-43.98827750247238</v>
+        <v>-15.86812326563025</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1059745778534752</v>
+        <v>0.1059464757323599</v>
       </c>
       <c r="T64">
         <v>1.172366762600102</v>
       </c>
       <c r="U64">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V64">
         <v>0</v>
       </c>
       <c r="W64">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.4368492306383556</v>
+        <v>0.5319374433414543</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6584,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1984064080817171</v>
+        <v>0.1700457292756932</v>
       </c>
       <c r="C65">
-        <v>-435.0396242631343</v>
+        <v>-390.4499279826634</v>
       </c>
       <c r="D65">
-        <v>195.721600439752</v>
+        <v>240.3112967202229</v>
       </c>
       <c r="E65">
         <v>214.8803918411619</v>
@@ -6617,45 +6617,45 @@
         <v>68.72</v>
       </c>
       <c r="M65">
-        <v>159.8455077847703</v>
+        <v>131.2718026731404</v>
       </c>
       <c r="N65">
-        <v>-91.12550778477032</v>
+        <v>-62.55180267314043</v>
       </c>
       <c r="O65">
         <v>-0</v>
       </c>
       <c r="P65">
-        <v>-91.12550778477032</v>
+        <v>-62.55180267314043</v>
       </c>
       <c r="Q65">
-        <v>-46.52550778477032</v>
+        <v>-17.95180267314043</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.107600917795461</v>
+        <v>0.1075720561575588</v>
       </c>
       <c r="T65">
         <v>1.204052350778483</v>
       </c>
       <c r="U65">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V65">
         <v>0</v>
       </c>
       <c r="W65">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.4299151158663181</v>
+        <v>0.5234939918598438</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.2004657742483424</v>
+        <v>0.1716550954423186</v>
       </c>
       <c r="C66">
-        <v>-447.7245547966139</v>
+        <v>-403.6018058167278</v>
       </c>
       <c r="D66">
-        <v>193.1155782348897</v>
+        <v>237.2383272147758</v>
       </c>
       <c r="E66">
         <v>224.9593001697791</v>
@@ -6699,45 +6699,45 @@
         <v>68.72</v>
       </c>
       <c r="M66">
-        <v>162.3827380670683</v>
+        <v>133.3554820806506</v>
       </c>
       <c r="N66">
-        <v>-93.66273806706826</v>
+        <v>-64.63548208065058</v>
       </c>
       <c r="O66">
         <v>-0</v>
       </c>
       <c r="P66">
-        <v>-93.66273806706826</v>
+        <v>-64.63548208065058</v>
       </c>
       <c r="Q66">
-        <v>-49.06273806706826</v>
+        <v>-20.03548208065057</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.109317609956446</v>
+        <v>0.1092879466063798</v>
       </c>
       <c r="T66">
         <v>1.237498249411219</v>
       </c>
       <c r="U66">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V66">
         <v>0</v>
       </c>
       <c r="W66">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.423197692180907</v>
+        <v>0.5153143982370338</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6748,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.2025251404149678</v>
+        <v>0.1732644616089439</v>
       </c>
       <c r="C67">
-        <v>-460.3409991389954</v>
+        <v>-416.6760850308992</v>
       </c>
       <c r="D67">
-        <v>190.5780422211256</v>
+        <v>234.2429563292217</v>
       </c>
       <c r="E67">
         <v>235.0382084983964</v>
@@ -6781,45 +6781,45 @@
         <v>68.72</v>
       </c>
       <c r="M67">
-        <v>164.9199683493662</v>
+        <v>135.4391614881608</v>
       </c>
       <c r="N67">
-        <v>-96.19996834936623</v>
+        <v>-66.71916148816078</v>
       </c>
       <c r="O67">
         <v>-0</v>
       </c>
       <c r="P67">
-        <v>-96.19996834936623</v>
+        <v>-66.71916148816078</v>
       </c>
       <c r="Q67">
-        <v>-51.59996834936623</v>
+        <v>-22.11916148816078</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1111323988123445</v>
+        <v>0.1111018879379907</v>
       </c>
       <c r="T67">
         <v>1.27285534225154</v>
       </c>
       <c r="U67">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V67">
         <v>0</v>
       </c>
       <c r="W67">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.4166869584550468</v>
+        <v>0.5073864844180024</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6830,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.2045845065815931</v>
+        <v>0.1979738277755692</v>
       </c>
       <c r="C68">
-        <v>-472.8916219988424</v>
+        <v>-464.7904102541212</v>
       </c>
       <c r="D68">
-        <v>188.1063276898958</v>
+        <v>196.2075394346169</v>
       </c>
       <c r="E68">
         <v>245.1171168270137</v>
@@ -6863,37 +6863,37 @@
         <v>68.72</v>
       </c>
       <c r="M68">
-        <v>167.4571986316641</v>
+        <v>160.8051191347768</v>
       </c>
       <c r="N68">
-        <v>-98.73719863166414</v>
+        <v>-92.08511913477676</v>
       </c>
       <c r="O68">
         <v>-0</v>
       </c>
       <c r="P68">
-        <v>-98.73719863166414</v>
+        <v>-92.08511913477676</v>
       </c>
       <c r="Q68">
-        <v>-54.13719863166414</v>
+        <v>-47.48511913477676</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.113053939953884</v>
+        <v>0.1130225317008728</v>
       </c>
       <c r="T68">
         <v>1.310292264082467</v>
       </c>
       <c r="U68">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V68">
         <v>0</v>
       </c>
       <c r="W68">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4103735196905764</v>
+        <v>0.4273495792282782</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +6912,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.2066438727482184</v>
+        <v>0.1999331939421946</v>
       </c>
       <c r="C69">
-        <v>-485.3789516142257</v>
+        <v>-477.3635406550403</v>
       </c>
       <c r="D69">
-        <v>185.6979064031297</v>
+        <v>193.7133173623151</v>
       </c>
       <c r="E69">
         <v>255.1960251556309</v>
@@ -6945,37 +6945,37 @@
         <v>68.72</v>
       </c>
       <c r="M69">
-        <v>169.9944289139621</v>
+        <v>163.2415603337885</v>
       </c>
       <c r="N69">
-        <v>-101.2744289139621</v>
+        <v>-94.52156033378853</v>
       </c>
       <c r="O69">
         <v>-0</v>
       </c>
       <c r="P69">
-        <v>-101.2744289139621</v>
+        <v>-94.52156033378853</v>
       </c>
       <c r="Q69">
-        <v>-56.67442891396208</v>
+        <v>-49.92156033378853</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1150919381343048</v>
+        <v>0.1150595781160507</v>
       </c>
       <c r="T69">
         <v>1.349998090266785</v>
       </c>
       <c r="U69">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V69">
         <v>0</v>
       </c>
       <c r="W69">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.404248541784747</v>
+        <v>0.420971227299498</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +6994,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.2087032389148438</v>
+        <v>0.2018925601088199</v>
       </c>
       <c r="C70">
-        <v>-497.8053883787857</v>
+        <v>-489.8740531536441</v>
       </c>
       <c r="D70">
-        <v>183.350377967187</v>
+        <v>191.2817131923286</v>
       </c>
       <c r="E70">
         <v>265.2749334842482</v>
@@ -7027,37 +7027,37 @@
         <v>68.72</v>
       </c>
       <c r="M70">
-        <v>172.5316591962601</v>
+        <v>165.6780015328003</v>
       </c>
       <c r="N70">
-        <v>-103.8116591962601</v>
+        <v>-96.95800153280032</v>
       </c>
       <c r="O70">
         <v>-0</v>
       </c>
       <c r="P70">
-        <v>-103.8116591962601</v>
+        <v>-96.95800153280032</v>
       </c>
       <c r="Q70">
-        <v>-59.21165919626005</v>
+        <v>-52.35800153280032</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1172573112010018</v>
+        <v>0.1172239399321773</v>
       </c>
       <c r="T70">
         <v>1.392185530587622</v>
       </c>
       <c r="U70">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V70">
         <v>0</v>
       </c>
       <c r="W70">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3983037102879123</v>
+        <v>0.4147804739568582</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7076,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2107626050814691</v>
+        <v>0.2038519262754453</v>
       </c>
       <c r="C71">
-        <v>-510.1732128216769</v>
+        <v>-502.3242765681023</v>
       </c>
       <c r="D71">
-        <v>181.061461852913</v>
+        <v>188.9103981064877</v>
       </c>
       <c r="E71">
         <v>275.3538418128654</v>
@@ -7109,37 +7109,37 @@
         <v>68.72</v>
       </c>
       <c r="M71">
-        <v>175.068889478558</v>
+        <v>168.1144427318121</v>
       </c>
       <c r="N71">
-        <v>-106.348889478558</v>
+        <v>-99.39444273181209</v>
       </c>
       <c r="O71">
         <v>-0</v>
       </c>
       <c r="P71">
-        <v>-106.348889478558</v>
+        <v>-99.39444273181209</v>
       </c>
       <c r="Q71">
-        <v>-61.74888947855799</v>
+        <v>-54.79444273181209</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1195623857558728</v>
+        <v>0.1195279379945056</v>
       </c>
       <c r="T71">
         <v>1.437094741251739</v>
       </c>
       <c r="U71">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V71">
         <v>0</v>
       </c>
       <c r="W71">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3925311927475079</v>
+        <v>0.4087691627400921</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7158,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2128219712480944</v>
+        <v>0.2058112924420706</v>
       </c>
       <c r="C72">
-        <v>-522.4845929971611</v>
+        <v>-514.7164256494468</v>
       </c>
       <c r="D72">
-        <v>178.8289900060459</v>
+        <v>186.5971573537603</v>
       </c>
       <c r="E72">
         <v>285.4327501414826</v>
@@ -7191,37 +7191,37 @@
         <v>68.72</v>
       </c>
       <c r="M72">
-        <v>177.6061197608559</v>
+        <v>170.5508839308238</v>
       </c>
       <c r="N72">
-        <v>-108.8861197608559</v>
+        <v>-101.8308839308238</v>
       </c>
       <c r="O72">
         <v>-0</v>
       </c>
       <c r="P72">
-        <v>-108.8861197608559</v>
+        <v>-101.8308839308238</v>
       </c>
       <c r="Q72">
-        <v>-64.28611976085594</v>
+        <v>-57.23088393082383</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1220211319477353</v>
+        <v>0.1219855359276558</v>
       </c>
       <c r="T72">
         <v>1.484997899293463</v>
       </c>
       <c r="U72">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V72">
         <v>0</v>
       </c>
       <c r="W72">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3869236042796863</v>
+        <v>0.4029296032723766</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7240,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2148813374147198</v>
+        <v>0.207770658608696</v>
       </c>
       <c r="C73">
-        <v>-534.7415913341804</v>
+        <v>-527.0526079809482</v>
       </c>
       <c r="D73">
-        <v>176.650899997644</v>
+        <v>184.3398833508762</v>
       </c>
       <c r="E73">
         <v>295.5116584700999</v>
@@ -7273,37 +7273,37 @@
         <v>68.72</v>
       </c>
       <c r="M73">
-        <v>180.1433500431538</v>
+        <v>172.9873251298356</v>
       </c>
       <c r="N73">
-        <v>-111.4233500431538</v>
+        <v>-104.2673251298356</v>
       </c>
       <c r="O73">
         <v>-0</v>
       </c>
       <c r="P73">
-        <v>-111.4233500431538</v>
+        <v>-104.2673251298356</v>
       </c>
       <c r="Q73">
-        <v>-66.82335004315385</v>
+        <v>-59.6673251298356</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1246494468424847</v>
+        <v>0.1246126233734371</v>
       </c>
       <c r="T73">
         <v>1.536204723407031</v>
       </c>
       <c r="U73">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V73">
         <v>0</v>
       </c>
       <c r="W73">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.381473976050395</v>
+        <v>0.3972545384375544</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7322,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2169407035813451</v>
+        <v>0.2097300247753213</v>
       </c>
       <c r="C74">
-        <v>-546.9461709913961</v>
+        <v>-539.3348303827036</v>
       </c>
       <c r="D74">
-        <v>174.5252286690454</v>
+        <v>182.136569277738</v>
       </c>
       <c r="E74">
         <v>305.5905667987171</v>
@@ -7355,37 +7355,37 @@
         <v>68.72</v>
       </c>
       <c r="M74">
-        <v>182.6805803254518</v>
+        <v>175.4237663288474</v>
       </c>
       <c r="N74">
-        <v>-113.9605803254518</v>
+        <v>-106.7037663288474</v>
       </c>
       <c r="O74">
         <v>-0</v>
       </c>
       <c r="P74">
-        <v>-113.9605803254518</v>
+        <v>-106.7037663288474</v>
       </c>
       <c r="Q74">
-        <v>-69.36058032545179</v>
+        <v>-62.10376632884736</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1274654985154306</v>
+        <v>0.1274273599224884</v>
       </c>
       <c r="T74">
         <v>1.591069177814425</v>
       </c>
       <c r="U74">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V74">
         <v>0</v>
       </c>
       <c r="W74">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3761757263830284</v>
+        <v>0.3917371142925884</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7404,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2190000697479705</v>
+        <v>0.2116893909419466</v>
       </c>
       <c r="C75">
-        <v>-559.1002017588586</v>
+        <v>-551.5650048623486</v>
       </c>
       <c r="D75">
-        <v>172.4501062302002</v>
+        <v>179.9853031267102</v>
       </c>
       <c r="E75">
         <v>315.6694751273343</v>
@@ -7437,37 +7437,37 @@
         <v>68.72</v>
       </c>
       <c r="M75">
-        <v>185.2178106077497</v>
+        <v>177.8602075278591</v>
       </c>
       <c r="N75">
-        <v>-116.4978106077497</v>
+        <v>-109.1402075278591</v>
       </c>
       <c r="O75">
         <v>-0</v>
       </c>
       <c r="P75">
-        <v>-116.4978106077497</v>
+        <v>-109.1402075278591</v>
       </c>
       <c r="Q75">
-        <v>-71.89781060774973</v>
+        <v>-64.54020752785914</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1304901466085947</v>
+        <v>0.1304505954751731</v>
       </c>
       <c r="T75">
         <v>1.649997665881625</v>
       </c>
       <c r="U75">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V75">
         <v>0</v>
       </c>
       <c r="W75">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3710226342407952</v>
+        <v>0.3863708524529639</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7486,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2210594359145958</v>
+        <v>0.213648757108572</v>
       </c>
       <c r="C76">
-        <v>-571.2054655435925</v>
+        <v>-563.7449541489765</v>
       </c>
       <c r="D76">
-        <v>170.4237507740836</v>
+        <v>177.8842621686996</v>
       </c>
       <c r="E76">
         <v>325.7483834559516</v>
@@ -7519,37 +7519,37 @@
         <v>68.72</v>
       </c>
       <c r="M76">
-        <v>187.7550408900477</v>
+        <v>180.2966487268709</v>
       </c>
       <c r="N76">
-        <v>-119.0350408900477</v>
+        <v>-111.5766487268709</v>
       </c>
       <c r="O76">
         <v>-0</v>
       </c>
       <c r="P76">
-        <v>-119.0350408900477</v>
+        <v>-111.5766487268709</v>
       </c>
       <c r="Q76">
-        <v>-74.4350408900477</v>
+        <v>-66.97664872687093</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1337474599396945</v>
+        <v>0.1337063876088336</v>
       </c>
       <c r="T76">
         <v>1.71345911456938</v>
       </c>
       <c r="U76">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V76">
         <v>0</v>
       </c>
       <c r="W76">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3660088148591627</v>
+        <v>0.381149624717113</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7568,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2231188020812211</v>
+        <v>0.2156081232751973</v>
       </c>
       <c r="C77">
-        <v>-583.2636614729277</v>
+        <v>-575.8764168439334</v>
       </c>
       <c r="D77">
-        <v>168.4444631733656</v>
+        <v>175.8317078023599</v>
       </c>
       <c r="E77">
         <v>335.8272917845688</v>
@@ -7601,37 +7601,37 @@
         <v>68.72</v>
       </c>
       <c r="M77">
-        <v>190.2922711723456</v>
+        <v>182.7330899258827</v>
       </c>
       <c r="N77">
-        <v>-121.5722711723456</v>
+        <v>-114.0130899258827</v>
       </c>
       <c r="O77">
         <v>-0</v>
       </c>
       <c r="P77">
-        <v>-121.5722711723456</v>
+        <v>-114.0130899258827</v>
       </c>
       <c r="Q77">
-        <v>-76.97227117234561</v>
+        <v>-69.4130899258827</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1372653583372823</v>
+        <v>0.137222643113187</v>
       </c>
       <c r="T77">
         <v>1.781997479152156</v>
       </c>
       <c r="U77">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V77">
         <v>0</v>
       </c>
       <c r="W77">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3611286973277072</v>
+        <v>0.3760676297208848</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7650,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2251781682478465</v>
+        <v>0.2175674894418227</v>
       </c>
       <c r="C78">
-        <v>-595.2764106462974</v>
+        <v>-587.9610522190799</v>
       </c>
       <c r="D78">
-        <v>166.5106223286131</v>
+        <v>173.8259807558306</v>
       </c>
       <c r="E78">
         <v>345.9062001131861</v>
@@ -7683,37 +7683,37 @@
         <v>68.72</v>
       </c>
       <c r="M78">
-        <v>192.8295014546435</v>
+        <v>185.1695311248944</v>
       </c>
       <c r="N78">
-        <v>-124.1095014546435</v>
+        <v>-116.4495311248944</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>-124.1095014546435</v>
+        <v>-116.4495311248944</v>
       </c>
       <c r="Q78">
-        <v>-79.50950145464356</v>
+        <v>-71.84953112489444</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1410764149346691</v>
+        <v>0.1410319199095698</v>
       </c>
       <c r="T78">
         <v>1.856247374116829</v>
       </c>
       <c r="U78">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V78">
         <v>0</v>
       </c>
       <c r="W78">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3563770039418164</v>
+        <v>0.3711193714350838</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7732,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2272375344144718</v>
+        <v>0.219526855608448</v>
       </c>
       <c r="C79">
-        <v>-607.2452605634284</v>
+        <v>-600.0004446903509</v>
       </c>
       <c r="D79">
-        <v>164.6206807400995</v>
+        <v>171.8654966131769</v>
       </c>
       <c r="E79">
         <v>355.9851084418034</v>
@@ -7765,37 +7765,37 @@
         <v>68.72</v>
       </c>
       <c r="M79">
-        <v>195.3667317369415</v>
+        <v>187.6059723239062</v>
       </c>
       <c r="N79">
-        <v>-126.6467317369415</v>
+        <v>-118.8859723239062</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>-126.6467317369415</v>
+        <v>-118.8859723239062</v>
       </c>
       <c r="Q79">
-        <v>-82.04673173694152</v>
+        <v>-74.28597232390624</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1452188677579155</v>
+        <v>0.1451724381665076</v>
       </c>
       <c r="T79">
         <v>1.936953781687125</v>
       </c>
       <c r="U79">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V79">
         <v>0</v>
       </c>
       <c r="W79">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3517487311633513</v>
+        <v>0.3662996393385242</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7814,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2292969005810972</v>
+        <v>0.2214862217750734</v>
       </c>
       <c r="C80">
-        <v>-619.1716892543484</v>
+        <v>-611.9961079919634</v>
       </c>
       <c r="D80">
-        <v>162.7731603777967</v>
+        <v>169.9487416401817</v>
       </c>
       <c r="E80">
         <v>366.0640167704206</v>
@@ -7847,37 +7847,37 @@
         <v>68.72</v>
       </c>
       <c r="M80">
-        <v>197.9039620192395</v>
+        <v>190.042413522918</v>
       </c>
       <c r="N80">
-        <v>-129.1839620192395</v>
+        <v>-121.322413522918</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-129.1839620192395</v>
+        <v>-121.322413522918</v>
       </c>
       <c r="Q80">
-        <v>-84.58396201923946</v>
+        <v>-76.722413522918</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1497379072014572</v>
+        <v>0.1496893671740761</v>
       </c>
       <c r="T80">
         <v>2.024997135400177</v>
       </c>
       <c r="U80">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V80">
         <v>0</v>
       </c>
       <c r="W80">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3472391320458723</v>
+        <v>0.3616034901162354</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +7896,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2313562667477225</v>
+        <v>0.2234455879416987</v>
       </c>
       <c r="C81">
-        <v>-631.0571091343779</v>
+        <v>-623.9494890743853</v>
       </c>
       <c r="D81">
-        <v>160.9666488263844</v>
+        <v>168.074268886377</v>
       </c>
       <c r="E81">
         <v>376.1429250990378</v>
@@ -7929,37 +7929,37 @@
         <v>68.72</v>
       </c>
       <c r="M81">
-        <v>200.4411923015374</v>
+        <v>192.4788547219298</v>
       </c>
       <c r="N81">
-        <v>-131.7211923015374</v>
+        <v>-123.7588547219298</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-131.7211923015374</v>
+        <v>-123.7588547219298</v>
       </c>
       <c r="Q81">
-        <v>-87.12119230153741</v>
+        <v>-79.15885472192977</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1546873313539075</v>
+        <v>0.1546364798966512</v>
       </c>
       <c r="T81">
         <v>2.121425570419233</v>
       </c>
       <c r="U81">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V81">
         <v>0</v>
       </c>
       <c r="W81">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3428436999946588</v>
+        <v>0.3570262307476755</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +7978,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2334156329143479</v>
+        <v>0.225404954108324</v>
       </c>
       <c r="C82">
-        <v>-642.9028706052354</v>
+        <v>-635.8619717471581</v>
       </c>
       <c r="D82">
-        <v>159.1997956841442</v>
+        <v>166.2406945422215</v>
       </c>
       <c r="E82">
         <v>386.2218334276552</v>
@@ -8011,37 +8011,37 @@
         <v>68.72</v>
       </c>
       <c r="M82">
-        <v>202.9784225838353</v>
+        <v>194.9152959209416</v>
       </c>
       <c r="N82">
-        <v>-134.2584225838353</v>
+        <v>-126.1952959209416</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-134.2584225838353</v>
+        <v>-126.1952959209416</v>
       </c>
       <c r="Q82">
-        <v>-89.65842258383535</v>
+        <v>-81.59529592094157</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1601316979216029</v>
+        <v>0.1600783038914838</v>
       </c>
       <c r="T82">
         <v>2.227496848940195</v>
       </c>
       <c r="U82">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V82">
         <v>0</v>
       </c>
       <c r="W82">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3385581537447255</v>
+        <v>0.3525634028633294</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8060,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2354749990809732</v>
+        <v>0.2273643202749494</v>
       </c>
       <c r="C83">
-        <v>-654.7102654215506</v>
+        <v>-647.7348800858493</v>
       </c>
       <c r="D83">
-        <v>157.4713091964462</v>
+        <v>164.4466945321475</v>
       </c>
       <c r="E83">
         <v>396.3007417562724</v>
@@ -8093,37 +8093,37 @@
         <v>68.72</v>
       </c>
       <c r="M83">
-        <v>205.5156528661333</v>
+        <v>197.3517371199533</v>
       </c>
       <c r="N83">
-        <v>-136.7956528661333</v>
+        <v>-128.6317371199533</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-136.7956528661333</v>
+        <v>-128.6317371199533</v>
       </c>
       <c r="Q83">
-        <v>-92.19565286613329</v>
+        <v>-84.03173711995331</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1661491557069504</v>
+        <v>0.1660929514647198</v>
       </c>
       <c r="T83">
         <v>2.344733525200205</v>
       </c>
       <c r="U83">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V83">
         <v>0</v>
       </c>
       <c r="W83">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3343784234515808</v>
+        <v>0.3482107682600786</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8142,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2375343652475986</v>
+        <v>0.2293236864415747</v>
       </c>
       <c r="C84">
-        <v>-666.4805298404262</v>
+        <v>-659.5694816207614</v>
       </c>
       <c r="D84">
-        <v>155.7799531061878</v>
+        <v>162.6910013258527</v>
       </c>
       <c r="E84">
         <v>406.3796500848896</v>
@@ -8175,37 +8175,37 @@
         <v>68.72</v>
       </c>
       <c r="M84">
-        <v>208.0528831484312</v>
+        <v>199.7881783189651</v>
       </c>
       <c r="N84">
-        <v>-139.3328831484312</v>
+        <v>-131.0681783189651</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-139.3328831484312</v>
+        <v>-131.0681783189651</v>
       </c>
       <c r="Q84">
-        <v>-94.73288314843123</v>
+        <v>-86.46817831896507</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1728352199128921</v>
+        <v>0.1727758932127597</v>
       </c>
       <c r="T84">
         <v>2.474996498822439</v>
       </c>
       <c r="U84">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V84">
         <v>0</v>
       </c>
       <c r="W84">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3303006377997323</v>
+        <v>0.343964295476419</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8224,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2395937314142239</v>
+        <v>0.2312830526082001</v>
       </c>
       <c r="C85">
-        <v>-678.2148475701849</v>
+        <v>-671.3669903235359</v>
       </c>
       <c r="D85">
-        <v>154.1245437050465</v>
+        <v>160.9724009516954</v>
       </c>
       <c r="E85">
         <v>416.4585584135069</v>
@@ -8257,37 +8257,37 @@
         <v>68.72</v>
       </c>
       <c r="M85">
-        <v>210.5901134307292</v>
+        <v>202.2246195179769</v>
       </c>
       <c r="N85">
-        <v>-141.8701134307292</v>
+        <v>-133.5046195179769</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-141.8701134307292</v>
+        <v>-133.5046195179769</v>
       </c>
       <c r="Q85">
-        <v>-97.2701134307292</v>
+        <v>-88.90461951797687</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.1803078799077681</v>
+        <v>0.1802450634017456</v>
       </c>
       <c r="T85">
         <v>2.620584528164936</v>
       </c>
       <c r="U85">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V85">
         <v>0</v>
       </c>
       <c r="W85">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.326321112043109</v>
+        <v>0.3398201473381489</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8306,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2416530975808492</v>
+        <v>0.2332424187748254</v>
       </c>
       <c r="C86">
-        <v>-689.9143525330815</v>
+        <v>-683.12856940644</v>
       </c>
       <c r="D86">
-        <v>152.503947070767</v>
+        <v>159.2897301974086</v>
       </c>
       <c r="E86">
         <v>426.537466742124</v>
@@ -8339,37 +8339,37 @@
         <v>68.72</v>
       </c>
       <c r="M86">
-        <v>213.1273437130271</v>
+        <v>204.6610607169886</v>
       </c>
       <c r="N86">
-        <v>-144.4073437130271</v>
+        <v>-135.9410607169886</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-144.4073437130271</v>
+        <v>-135.9410607169886</v>
       </c>
       <c r="Q86">
-        <v>-99.80734371302711</v>
+        <v>-91.34106071698861</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.1887146224020036</v>
+        <v>0.1886478798643547</v>
       </c>
       <c r="T86">
         <v>2.784371061175243</v>
       </c>
       <c r="U86">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V86">
         <v>0</v>
       </c>
       <c r="W86">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3224363368997386</v>
+        <v>0.3357746693936472</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8388,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2437124637474746</v>
+        <v>0.2352017849414507</v>
       </c>
       <c r="C87">
-        <v>-701.5801314555341</v>
+        <v>-694.855333947902</v>
       </c>
       <c r="D87">
-        <v>150.9170764769316</v>
+        <v>157.6418739845637</v>
       </c>
       <c r="E87">
         <v>436.6163750707412</v>
@@ -8421,37 +8421,37 @@
         <v>68.72</v>
       </c>
       <c r="M87">
-        <v>215.664573995325</v>
+        <v>207.0975019160004</v>
       </c>
       <c r="N87">
-        <v>-146.944573995325</v>
+        <v>-138.3775019160004</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-146.944573995325</v>
+        <v>-138.3775019160004</v>
       </c>
       <c r="Q87">
-        <v>-102.344573995325</v>
+        <v>-93.77750191600038</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.1982422638954705</v>
+        <v>0.1981710718553117</v>
       </c>
       <c r="T87">
         <v>2.969995798586926</v>
       </c>
       <c r="U87">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V87">
         <v>0</v>
       </c>
       <c r="W87">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.31864296823033</v>
+        <v>0.3318243791654866</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8470,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2457718299140999</v>
+        <v>0.2371611511080761</v>
       </c>
       <c r="C88">
-        <v>-713.2132262983025</v>
+        <v>-706.5483533567476</v>
       </c>
       <c r="D88">
-        <v>149.3628899627805</v>
+        <v>156.0277629043354</v>
       </c>
       <c r="E88">
         <v>446.6952833993586</v>
@@ -8503,37 +8503,37 @@
         <v>68.72</v>
       </c>
       <c r="M88">
-        <v>218.201804277623</v>
+        <v>209.5339431150122</v>
       </c>
       <c r="N88">
-        <v>-149.481804277623</v>
+        <v>-140.8139431150122</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-149.481804277623</v>
+        <v>-140.8139431150122</v>
       </c>
       <c r="Q88">
-        <v>-104.881804277623</v>
+        <v>-96.21394311501217</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2091309970308612</v>
+        <v>0.2090547198449768</v>
       </c>
       <c r="T88">
         <v>3.182138355628849</v>
       </c>
       <c r="U88">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V88">
         <v>0</v>
       </c>
       <c r="W88">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.314937817436954</v>
+        <v>0.3279659561519344</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8552,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2478311960807252</v>
+        <v>0.2391205172747014</v>
       </c>
       <c r="C89">
-        <v>-724.8146365380396</v>
+        <v>-718.20865368658</v>
       </c>
       <c r="D89">
-        <v>147.8403880516607</v>
+        <v>154.4463709031203</v>
       </c>
       <c r="E89">
         <v>456.7741917279758</v>
@@ -8585,37 +8585,37 @@
         <v>68.72</v>
       </c>
       <c r="M89">
-        <v>220.7390345599209</v>
+        <v>211.9703843140239</v>
       </c>
       <c r="N89">
-        <v>-152.0190345599209</v>
+        <v>-143.2503843140239</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-152.0190345599209</v>
+        <v>-143.2503843140239</v>
       </c>
       <c r="Q89">
-        <v>-107.4190345599209</v>
+        <v>-98.65038431402391</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.221694919879389</v>
+        <v>0.2216127752176673</v>
       </c>
       <c r="T89">
         <v>3.426918229138761</v>
       </c>
       <c r="U89">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V89">
         <v>0</v>
       </c>
       <c r="W89">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3113178425238856</v>
+        <v>0.3241962325180042</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8634,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2498905622473506</v>
+        <v>0.2410798834413267</v>
       </c>
       <c r="C90">
-        <v>-736.3853213107109</v>
+        <v>-729.8372198108327</v>
       </c>
       <c r="D90">
-        <v>146.3486116076066</v>
+        <v>152.8967131074848</v>
       </c>
       <c r="E90">
         <v>466.853100056593</v>
@@ -8667,37 +8667,37 @@
         <v>68.72</v>
       </c>
       <c r="M90">
-        <v>223.2762648422189</v>
+        <v>214.4068255130357</v>
       </c>
       <c r="N90">
-        <v>-154.5562648422189</v>
+        <v>-145.6868255130357</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-154.5562648422189</v>
+        <v>-145.6868255130357</v>
       </c>
       <c r="Q90">
-        <v>-109.9562648422189</v>
+        <v>-101.0868255130357</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2363528298693381</v>
+        <v>0.2362638398191396</v>
       </c>
       <c r="T90">
         <v>3.712494748233658</v>
       </c>
       <c r="U90">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V90">
         <v>0</v>
       </c>
       <c r="W90">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3077801397679323</v>
+        <v>0.3205121844212087</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8716,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.251949928413976</v>
+        <v>0.2430392496079521</v>
       </c>
       <c r="C91">
-        <v>-747.9262014265416</v>
+        <v>-741.4349974681788</v>
       </c>
       <c r="D91">
-        <v>144.8866398203931</v>
+        <v>151.3778437787558</v>
       </c>
       <c r="E91">
         <v>476.9320083852102</v>
@@ -8749,37 +8749,37 @@
         <v>68.72</v>
       </c>
       <c r="M91">
-        <v>225.8134951245168</v>
+        <v>216.8432667120474</v>
       </c>
       <c r="N91">
-        <v>-157.0934951245168</v>
+        <v>-148.1232667120474</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-157.0934951245168</v>
+        <v>-148.1232667120474</v>
       </c>
       <c r="Q91">
-        <v>-112.4934951245168</v>
+        <v>-103.5232667120474</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2536758144029143</v>
+        <v>0.2535787343481523</v>
       </c>
       <c r="T91">
         <v>4.049994270800354</v>
       </c>
       <c r="U91">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V91">
         <v>0</v>
       </c>
       <c r="W91">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3043219359503151</v>
+        <v>0.316910923922094</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2540092945806013</v>
+        <v>0.2449986157745774</v>
       </c>
       <c r="C92">
-        <v>-759.4381612653865</v>
+        <v>-753.0028951872267</v>
       </c>
       <c r="D92">
-        <v>143.4535883101655</v>
+        <v>149.8888543883253</v>
       </c>
       <c r="E92">
         <v>487.0109167138276</v>
@@ -8831,37 +8831,37 @@
         <v>68.72</v>
       </c>
       <c r="M92">
-        <v>228.3507254068147</v>
+        <v>219.2797079110592</v>
       </c>
       <c r="N92">
-        <v>-159.6307254068147</v>
+        <v>-150.5597079110592</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-159.6307254068147</v>
+        <v>-150.5597079110592</v>
       </c>
       <c r="Q92">
-        <v>-115.0307254068148</v>
+        <v>-105.9597079110592</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.2744633958432058</v>
+        <v>0.2743566077829675</v>
       </c>
       <c r="T92">
         <v>4.45499369788039</v>
       </c>
       <c r="U92">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V92">
         <v>0</v>
       </c>
       <c r="W92">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3009405811064227</v>
+        <v>0.3133896914340707</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +8880,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2560686607472266</v>
+        <v>0.2469579819412028</v>
       </c>
       <c r="C93">
-        <v>-770.9220505607208</v>
+        <v>-764.5417860987302</v>
       </c>
       <c r="D93">
-        <v>142.0486073434485</v>
+        <v>148.4288718054391</v>
       </c>
       <c r="E93">
         <v>497.0898250424448</v>
@@ -8913,37 +8913,37 @@
         <v>68.72</v>
       </c>
       <c r="M93">
-        <v>230.8879556891127</v>
+        <v>221.716149110071</v>
       </c>
       <c r="N93">
-        <v>-162.1679556891127</v>
+        <v>-152.996149110071</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-162.1679556891127</v>
+        <v>-152.996149110071</v>
       </c>
       <c r="Q93">
-        <v>-117.5679556891127</v>
+        <v>-108.396149110071</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.2998704398257842</v>
+        <v>0.2997517864255195</v>
       </c>
       <c r="T93">
         <v>4.949992997644878</v>
       </c>
       <c r="U93">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V93">
         <v>0</v>
       </c>
       <c r="W93">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2976335417536049</v>
+        <v>0.3099458486710589</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +8962,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2581280269138519</v>
+        <v>0.2489173481078281</v>
       </c>
       <c r="C94">
-        <v>-782.3786860798141</v>
+        <v>-776.0525096429122</v>
       </c>
       <c r="D94">
-        <v>140.6708801529724</v>
+        <v>146.9970565898743</v>
       </c>
       <c r="E94">
         <v>507.168733371062</v>
@@ -8995,37 +8995,37 @@
         <v>68.72</v>
       </c>
       <c r="M94">
-        <v>233.4251859714106</v>
+        <v>224.1525903090827</v>
       </c>
       <c r="N94">
-        <v>-164.7051859714106</v>
+        <v>-155.4325903090827</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-164.7051859714106</v>
+        <v>-155.4325903090827</v>
       </c>
       <c r="Q94">
-        <v>-120.1051859714106</v>
+        <v>-110.8325903090827</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3316292448040074</v>
+        <v>0.3314957597287095</v>
       </c>
       <c r="T94">
         <v>5.568742122350489</v>
       </c>
       <c r="U94">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V94">
         <v>0</v>
       </c>
       <c r="W94">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2943983945606309</v>
+        <v>0.3065768720550692</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9044,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2601873930804773</v>
+        <v>0.2508767142744535</v>
       </c>
       <c r="C95">
-        <v>-793.8088532070666</v>
+        <v>-787.5358731789123</v>
       </c>
       <c r="D95">
-        <v>139.3196213543372</v>
+        <v>145.5926013824915</v>
       </c>
       <c r="E95">
         <v>517.2476416996793</v>
@@ -9077,37 +9077,37 @@
         <v>68.72</v>
       </c>
       <c r="M95">
-        <v>235.9624162537086</v>
+        <v>226.5890315080945</v>
       </c>
       <c r="N95">
-        <v>-167.2424162537086</v>
+        <v>-157.8690315080945</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-167.2424162537086</v>
+        <v>-157.8690315080945</v>
       </c>
       <c r="Q95">
-        <v>-122.6424162537086</v>
+        <v>-113.2690315080945</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.3724619940617227</v>
+        <v>0.3723094396899537</v>
       </c>
       <c r="T95">
         <v>6.364276711257703</v>
       </c>
       <c r="U95">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V95">
         <v>0</v>
       </c>
       <c r="W95">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2912328204255703</v>
+        <v>0.3032803465491006</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9126,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2622467592471026</v>
+        <v>0.2528360804410788</v>
       </c>
       <c r="C96">
-        <v>-805.2133074369584</v>
+        <v>-798.9926535028459</v>
       </c>
       <c r="D96">
-        <v>137.9940754530626</v>
+        <v>144.2147293871751</v>
       </c>
       <c r="E96">
         <v>527.3265500282965</v>
@@ -9159,37 +9159,37 @@
         <v>68.72</v>
       </c>
       <c r="M96">
-        <v>238.4996465360065</v>
+        <v>229.0254727071063</v>
       </c>
       <c r="N96">
-        <v>-169.7796465360065</v>
+        <v>-160.3054727071063</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-169.7796465360065</v>
+        <v>-160.3054727071063</v>
       </c>
       <c r="Q96">
-        <v>-125.1796465360065</v>
+        <v>-115.7054727071063</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.4269056597386766</v>
+        <v>0.4267276796382795</v>
       </c>
       <c r="T96">
         <v>7.424989496467322</v>
       </c>
       <c r="U96">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V96">
         <v>0</v>
       </c>
       <c r="W96">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2881345989316814</v>
+        <v>0.3000539598836847</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9208,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.264306125413728</v>
+        <v>0.2547954466077041</v>
       </c>
       <c r="C97">
-        <v>-816.5927757825762</v>
+        <v>-810.4235982804707</v>
       </c>
       <c r="D97">
-        <v>136.6935154360621</v>
+        <v>142.8626929381674</v>
       </c>
       <c r="E97">
         <v>537.4054583569138</v>
@@ -9241,37 +9241,37 @@
         <v>68.72</v>
       </c>
       <c r="M97">
-        <v>241.0368768183044</v>
+        <v>231.4619139061181</v>
       </c>
       <c r="N97">
-        <v>-172.3168768183045</v>
+        <v>-162.7419139061181</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-172.3168768183045</v>
+        <v>-162.7419139061181</v>
       </c>
       <c r="Q97">
-        <v>-127.7168768183045</v>
+        <v>-118.1419139061181</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.5031267916864121</v>
+        <v>0.5029132155659356</v>
       </c>
       <c r="T97">
         <v>8.90998739576079</v>
       </c>
       <c r="U97">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V97">
         <v>0</v>
       </c>
       <c r="W97">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2851016031534531</v>
+        <v>0.296895497148067</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9290,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2663654915803533</v>
+        <v>0.2567548127743295</v>
       </c>
       <c r="C98">
-        <v>-827.9479581052308</v>
+        <v>-821.8294274000134</v>
       </c>
       <c r="D98">
-        <v>135.4172414420247</v>
+        <v>141.535772147242</v>
       </c>
       <c r="E98">
         <v>547.484366685531</v>
@@ -9323,37 +9323,37 @@
         <v>68.72</v>
       </c>
       <c r="M98">
-        <v>243.5741071006024</v>
+        <v>233.8983551051298</v>
       </c>
       <c r="N98">
-        <v>-174.8541071006024</v>
+        <v>-165.1783551051298</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-174.8541071006024</v>
+        <v>-165.1783551051298</v>
       </c>
       <c r="Q98">
-        <v>-130.2541071006024</v>
+        <v>-120.5783551051298</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.6174584896080137</v>
+        <v>0.6171915194574181</v>
       </c>
       <c r="T98">
         <v>11.13748424470096</v>
       </c>
       <c r="U98">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V98">
         <v>0</v>
       </c>
       <c r="W98">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2821317947872714</v>
+        <v>0.2938028357194413</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9372,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2684248577469787</v>
+        <v>0.2587141789409548</v>
       </c>
       <c r="C99">
-        <v>-839.279528370281</v>
+        <v>-833.2108342502975</v>
       </c>
       <c r="D99">
-        <v>134.1645795055917</v>
+        <v>140.2332736255752</v>
       </c>
       <c r="E99">
         <v>557.5632750141482</v>
@@ -9405,37 +9405,37 @@
         <v>68.72</v>
       </c>
       <c r="M99">
-        <v>246.1113373829003</v>
+        <v>236.3347963041416</v>
       </c>
       <c r="N99">
-        <v>-177.3913373829003</v>
+        <v>-167.6147963041416</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-177.3913373829003</v>
+        <v>-167.6147963041416</v>
       </c>
       <c r="Q99">
-        <v>-132.7913373829003</v>
+        <v>-123.0147963041416</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.8080113194773518</v>
+        <v>0.8076553592765576</v>
       </c>
       <c r="T99">
         <v>14.84997899293462</v>
       </c>
       <c r="U99">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V99">
         <v>0</v>
       </c>
       <c r="W99">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2792232195832788</v>
+        <v>0.2907739405058388</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9454,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.270484223913604</v>
+        <v>0.2606735451075802</v>
       </c>
       <c r="C100">
-        <v>-850.5881358338921</v>
+        <v>-844.5684869289439</v>
       </c>
       <c r="D100">
-        <v>132.9348803705978</v>
+        <v>138.954529275546</v>
       </c>
       <c r="E100">
         <v>567.6421833427654</v>
@@ -9487,37 +9487,37 @@
         <v>68.72</v>
       </c>
       <c r="M100">
-        <v>248.6485676651983</v>
+        <v>238.7712375031533</v>
       </c>
       <c r="N100">
-        <v>-179.9285676651983</v>
+        <v>-170.0512375031533</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-179.9285676651983</v>
+        <v>-170.0512375031533</v>
       </c>
       <c r="Q100">
-        <v>-135.3285676651983</v>
+        <v>-125.4512375031534</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.189116979216028</v>
+        <v>1.188583038914836</v>
       </c>
       <c r="T100">
         <v>22.27496848940192</v>
       </c>
       <c r="U100">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V100">
         <v>0</v>
       </c>
       <c r="W100">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2763740030569188</v>
+        <v>0.2878068594802691</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9536,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2725435900802293</v>
+        <v>0.2626329112742055</v>
       </c>
       <c r="C101">
-        <v>-861.8744061651254</v>
+        <v>-855.9030293850649</v>
       </c>
       <c r="D101">
-        <v>131.7275183679818</v>
+        <v>137.6988951480424</v>
       </c>
       <c r="E101">
         <v>577.7210916713827</v>
@@ -9569,37 +9569,37 @@
         <v>68.72</v>
       </c>
       <c r="M101">
-        <v>251.1857979474962</v>
+        <v>241.2076787021651</v>
       </c>
       <c r="N101">
-        <v>-182.4657979474962</v>
+        <v>-172.4876787021651</v>
       </c>
       <c r="O101">
         <v>-0</v>
       </c>
       <c r="P101">
-        <v>-182.4657979474962</v>
+        <v>-172.4876787021651</v>
       </c>
       <c r="Q101">
-        <v>-137.8657979474962</v>
+        <v>-127.8876787021651</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.332433958432055</v>
+        <v>2.331366077829673</v>
       </c>
       <c r="T101">
         <v>44.54993697880385</v>
       </c>
       <c r="U101">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V101">
         <v>0</v>
       </c>
       <c r="W101">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.2735823464603843</v>
+        <v>0.2848997194855188</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_power.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_power.xlsx
@@ -1133,43 +1133,43 @@
         <v>2.0195</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>121.241268376647</v>
       </c>
       <c r="G2">
         <v>4.94282660150282</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.118589343788884</v>
       </c>
       <c r="I2">
         <v>0.416801918585719</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>587.8</v>
       </c>
       <c r="L2">
-        <v>1310.56699417379</v>
+        <v>1294.54996251226</v>
       </c>
       <c r="M2">
         <v>1003.68083286172</v>
       </c>
       <c r="N2">
-        <v>1306.35699417379</v>
+        <v>1300.41887084087</v>
       </c>
       <c r="O2">
         <v>420.090832861724</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>10.0789083286172</v>
       </c>
       <c r="Q2">
         <v>0.0755481543301575</v>
       </c>
       <c r="R2">
-        <v>0.0686556607782967</v>
+        <v>0.0687600269449221</v>
       </c>
       <c r="S2">
         <v>0.0623366166625341</v>
@@ -1191,13 +1191,13 @@
         <v>0.0849902194240261</v>
       </c>
       <c r="X2">
-        <v>0.0686556607782967</v>
+        <v>0.0688865260386836</v>
       </c>
       <c r="Y2">
         <v>0.7638903212913229</v>
       </c>
       <c r="Z2">
-        <v>0.445499369788039</v>
+        <v>0.449999363422262</v>
       </c>
       <c r="AA2">
         <v>418.5</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06865566077829674</v>
+        <v>0.0687600269449221</v>
       </c>
       <c r="C2">
-        <v>1310.566994173794</v>
+        <v>1294.549962512255</v>
       </c>
       <c r="D2">
-        <v>1306.356994173794</v>
+        <v>1300.418870840873</v>
       </c>
       <c r="E2">
-        <v>-420.0908328617245</v>
+        <v>-410.0119245331073</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>10.07890832861724</v>
       </c>
       <c r="G2">
         <v>4.21</v>
@@ -1451,28 +1451,28 @@
         <v>68.72</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.5668037040532702</v>
       </c>
       <c r="N2">
-        <v>68.72</v>
+        <v>68.15319629594673</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>68.72</v>
+        <v>68.15319629594673</v>
       </c>
       <c r="Q2">
-        <v>113.32</v>
+        <v>112.7531962959467</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06865566077829674</v>
+        <v>0.06888652603868359</v>
       </c>
       <c r="T2">
-        <v>0.4454993697880389</v>
+        <v>0.4499993634222615</v>
       </c>
       <c r="U2">
         <v>0.0562366166625341</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>121.2412683766468</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0687600269449221</v>
+        <v>0.06886439311154742</v>
       </c>
       <c r="C3">
-        <v>1294.549962512255</v>
+        <v>1278.586670757614</v>
       </c>
       <c r="D3">
-        <v>1300.418870840873</v>
+        <v>1294.534487414849</v>
       </c>
       <c r="E3">
-        <v>-410.0119245331073</v>
+        <v>-399.93301620449</v>
       </c>
       <c r="F3">
-        <v>10.07890832861724</v>
+        <v>20.15781665723449</v>
       </c>
       <c r="G3">
         <v>4.21</v>
@@ -1533,28 +1533,28 @@
         <v>68.72</v>
       </c>
       <c r="M3">
-        <v>0.5668037040532702</v>
+        <v>1.13360740810654</v>
       </c>
       <c r="N3">
-        <v>68.15319629594673</v>
+        <v>67.58639259189346</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>68.15319629594673</v>
+        <v>67.58639259189346</v>
       </c>
       <c r="Q3">
-        <v>112.7531962959467</v>
+        <v>112.1863925918935</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06888652603868359</v>
+        <v>0.06912210283499667</v>
       </c>
       <c r="T3">
-        <v>0.4499993634222615</v>
+        <v>0.4545911936612642</v>
       </c>
       <c r="U3">
         <v>0.0562366166625341</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>121.2412683766468</v>
+        <v>60.62063418832338</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06886439311154742</v>
+        <v>0.06896875927817277</v>
       </c>
       <c r="C4">
-        <v>1278.586670757614</v>
+        <v>1262.676392678306</v>
       </c>
       <c r="D4">
-        <v>1294.534487414849</v>
+        <v>1288.703117664157</v>
       </c>
       <c r="E4">
-        <v>-399.93301620449</v>
+        <v>-389.8541078758728</v>
       </c>
       <c r="F4">
-        <v>20.15781665723449</v>
+        <v>30.23672498585173</v>
       </c>
       <c r="G4">
         <v>4.21</v>
@@ -1615,28 +1615,28 @@
         <v>68.72</v>
       </c>
       <c r="M4">
-        <v>1.13360740810654</v>
+        <v>1.700411112159811</v>
       </c>
       <c r="N4">
-        <v>67.58639259189346</v>
+        <v>67.01958888784019</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>67.58639259189346</v>
+        <v>67.01958888784019</v>
       </c>
       <c r="Q4">
-        <v>112.1863925918935</v>
+        <v>111.6195888878402</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06912210283499667</v>
+        <v>0.06936253688484201</v>
       </c>
       <c r="T4">
-        <v>0.4545911936612642</v>
+        <v>0.4592777008124112</v>
       </c>
       <c r="U4">
         <v>0.0562366166625341</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>60.62063418832338</v>
+        <v>40.41375612554891</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06896875927817277</v>
+        <v>0.0690731254447981</v>
       </c>
       <c r="C5">
-        <v>1262.676392678306</v>
+        <v>1246.818415069641</v>
       </c>
       <c r="D5">
-        <v>1288.703117664157</v>
+        <v>1282.924048384109</v>
       </c>
       <c r="E5">
-        <v>-389.8541078758728</v>
+        <v>-379.7751995472555</v>
       </c>
       <c r="F5">
-        <v>30.23672498585173</v>
+        <v>40.31563331446898</v>
       </c>
       <c r="G5">
         <v>4.21</v>
@@ -1697,28 +1697,28 @@
         <v>68.72</v>
       </c>
       <c r="M5">
-        <v>1.700411112159811</v>
+        <v>2.267214816213081</v>
       </c>
       <c r="N5">
-        <v>67.01958888784019</v>
+        <v>66.45278518378692</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>67.01958888784019</v>
+        <v>66.45278518378692</v>
       </c>
       <c r="Q5">
-        <v>111.6195888878402</v>
+        <v>111.0527851837869</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06936253688484201</v>
+        <v>0.06960797997739245</v>
       </c>
       <c r="T5">
-        <v>0.4592777008124112</v>
+        <v>0.4640618435292072</v>
       </c>
       <c r="U5">
         <v>0.0562366166625341</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>40.41375612554891</v>
+        <v>30.31031709416169</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0690731254447981</v>
+        <v>0.06917749161142345</v>
       </c>
       <c r="C6">
-        <v>1246.818415069641</v>
+        <v>1231.012037463015</v>
       </c>
       <c r="D6">
-        <v>1282.924048384109</v>
+        <v>1277.196579106102</v>
       </c>
       <c r="E6">
-        <v>-379.7751995472555</v>
+        <v>-369.6962912186383</v>
       </c>
       <c r="F6">
-        <v>40.31563331446898</v>
+        <v>50.39454164308623</v>
       </c>
       <c r="G6">
         <v>4.21</v>
@@ -1779,28 +1779,28 @@
         <v>68.72</v>
       </c>
       <c r="M6">
-        <v>2.267214816213081</v>
+        <v>2.834018520266352</v>
       </c>
       <c r="N6">
-        <v>66.45278518378692</v>
+        <v>65.88598147973364</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>66.45278518378692</v>
+        <v>65.88598147973364</v>
       </c>
       <c r="Q6">
-        <v>111.0527851837869</v>
+        <v>110.4859814797337</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.06960797997739245</v>
+        <v>0.06985859029294395</v>
       </c>
       <c r="T6">
-        <v>0.4640618435292072</v>
+        <v>0.4689467050400409</v>
       </c>
       <c r="U6">
         <v>0.0562366166625341</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>30.31031709416169</v>
+        <v>24.24825367532934</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06917749161142345</v>
+        <v>0.06928185777804879</v>
       </c>
       <c r="C7">
-        <v>1231.012037463015</v>
+        <v>1215.256571842883</v>
       </c>
       <c r="D7">
-        <v>1277.196579106102</v>
+        <v>1271.520021814586</v>
       </c>
       <c r="E7">
-        <v>-369.6962912186383</v>
+        <v>-359.617382890021</v>
       </c>
       <c r="F7">
-        <v>50.39454164308623</v>
+        <v>60.47344997170347</v>
       </c>
       <c r="G7">
         <v>4.21</v>
@@ -1861,28 +1861,28 @@
         <v>68.72</v>
       </c>
       <c r="M7">
-        <v>2.834018520266352</v>
+        <v>3.400822224319622</v>
       </c>
       <c r="N7">
-        <v>65.88598147973364</v>
+        <v>65.31917777568037</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>65.88598147973364</v>
+        <v>65.31917777568037</v>
       </c>
       <c r="Q7">
-        <v>110.4859814797337</v>
+        <v>109.9191777756804</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.06985859029294395</v>
+        <v>0.07011453274286888</v>
       </c>
       <c r="T7">
-        <v>0.4689467050400409</v>
+        <v>0.4739354997745094</v>
       </c>
       <c r="U7">
         <v>0.0562366166625341</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>24.24825367532934</v>
+        <v>20.20687806277446</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06928185777804879</v>
+        <v>0.06938622394467413</v>
       </c>
       <c r="C8">
-        <v>1215.256571842883</v>
+        <v>1199.551342371236</v>
       </c>
       <c r="D8">
-        <v>1271.520021814586</v>
+        <v>1265.893700671557</v>
       </c>
       <c r="E8">
-        <v>-359.617382890021</v>
+        <v>-349.5384745614038</v>
       </c>
       <c r="F8">
-        <v>60.47344997170347</v>
+        <v>70.55235830032071</v>
       </c>
       <c r="G8">
         <v>4.21</v>
@@ -1943,28 +1943,28 @@
         <v>68.72</v>
       </c>
       <c r="M8">
-        <v>3.400822224319621</v>
+        <v>3.967625928372891</v>
       </c>
       <c r="N8">
-        <v>65.31917777568037</v>
+        <v>64.7523740716271</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>65.31917777568037</v>
+        <v>64.7523740716271</v>
       </c>
       <c r="Q8">
-        <v>109.9191777756804</v>
+        <v>109.3523740716271</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07011453274286888</v>
+        <v>0.07037597933150187</v>
       </c>
       <c r="T8">
-        <v>0.4739354997745094</v>
+        <v>0.4790315804172461</v>
       </c>
       <c r="U8">
         <v>0.0562366166625341</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>20.20687806277446</v>
+        <v>17.32018119666382</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06938622394467413</v>
+        <v>0.06949059011129946</v>
       </c>
       <c r="C9">
-        <v>1199.551342371236</v>
+        <v>1183.895685119373</v>
       </c>
       <c r="D9">
-        <v>1265.893700671557</v>
+        <v>1260.316951748311</v>
       </c>
       <c r="E9">
-        <v>-349.5384745614037</v>
+        <v>-339.4595662327865</v>
       </c>
       <c r="F9">
-        <v>70.55235830032072</v>
+        <v>80.63126662893795</v>
       </c>
       <c r="G9">
         <v>4.21</v>
@@ -2025,28 +2025,28 @@
         <v>68.72</v>
       </c>
       <c r="M9">
-        <v>3.967625928372892</v>
+        <v>4.534429632426161</v>
       </c>
       <c r="N9">
-        <v>64.7523740716271</v>
+        <v>64.18557036757383</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>64.7523740716271</v>
+        <v>64.18557036757383</v>
       </c>
       <c r="Q9">
-        <v>109.3523740716271</v>
+        <v>108.7855703675738</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07037597933150187</v>
+        <v>0.07064310954162689</v>
       </c>
       <c r="T9">
-        <v>0.4790315804172461</v>
+        <v>0.4842384454217813</v>
       </c>
       <c r="U9">
         <v>0.0562366166625341</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.32018119666382</v>
+        <v>15.15515854708084</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06949059011129946</v>
+        <v>0.06959495627792482</v>
       </c>
       <c r="C10">
-        <v>1183.895685119373</v>
+        <v>1168.288947806722</v>
       </c>
       <c r="D10">
-        <v>1260.316951748311</v>
+        <v>1254.789122764277</v>
       </c>
       <c r="E10">
-        <v>-339.4595662327865</v>
+        <v>-329.3806579041693</v>
       </c>
       <c r="F10">
-        <v>80.63126662893795</v>
+        <v>90.7101749575552</v>
       </c>
       <c r="G10">
         <v>4.21</v>
@@ -2107,28 +2107,28 @@
         <v>68.72</v>
       </c>
       <c r="M10">
-        <v>4.534429632426161</v>
+        <v>5.101233336479432</v>
       </c>
       <c r="N10">
-        <v>64.18557036757383</v>
+        <v>63.61876666352057</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>64.18557036757383</v>
+        <v>63.61876666352057</v>
       </c>
       <c r="Q10">
-        <v>108.7855703675738</v>
+        <v>108.2187666635206</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07064310954162689</v>
+        <v>0.07091611074538104</v>
       </c>
       <c r="T10">
-        <v>0.4842384454217813</v>
+        <v>0.489559747019823</v>
       </c>
       <c r="U10">
         <v>0.0562366166625341</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.15515854708084</v>
+        <v>13.47125204184964</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06959495627792482</v>
+        <v>0.06984932244455017</v>
       </c>
       <c r="C11">
-        <v>1168.288947806722</v>
+        <v>1144.938318421653</v>
       </c>
       <c r="D11">
-        <v>1254.789122764277</v>
+        <v>1241.517401707825</v>
       </c>
       <c r="E11">
-        <v>-329.3806579041693</v>
+        <v>-319.301749575552</v>
       </c>
       <c r="F11">
-        <v>90.7101749575552</v>
+        <v>100.7890832861724</v>
       </c>
       <c r="G11">
         <v>4.21</v>
@@ -2189,45 +2189,45 @@
         <v>68.72</v>
       </c>
       <c r="M11">
-        <v>5.101233336479432</v>
+        <v>5.819220665461961</v>
       </c>
       <c r="N11">
-        <v>63.61876666352057</v>
+        <v>62.90077933453804</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>63.61876666352057</v>
+        <v>62.90077933453804</v>
       </c>
       <c r="Q11">
-        <v>108.2187666635206</v>
+        <v>107.500779334538</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07091611074538104</v>
+        <v>0.07119517864255194</v>
       </c>
       <c r="T11">
-        <v>0.489559747019823</v>
+        <v>0.4949992997644877</v>
       </c>
       <c r="U11">
-        <v>0.0562366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V11">
         <v>0</v>
       </c>
       <c r="W11">
-        <v>0.0562366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>13.47125204184964</v>
+        <v>11.8091414556359</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06984932244455017</v>
+        <v>0.0699686886111755</v>
       </c>
       <c r="C12">
-        <v>1144.938318421653</v>
+        <v>1128.727709055191</v>
       </c>
       <c r="D12">
-        <v>1241.517401707825</v>
+        <v>1235.38570066998</v>
       </c>
       <c r="E12">
-        <v>-319.301749575552</v>
+        <v>-309.2228412469348</v>
       </c>
       <c r="F12">
-        <v>100.7890832861725</v>
+        <v>110.8679916147897</v>
       </c>
       <c r="G12">
         <v>4.21</v>
@@ -2271,28 +2271,28 @@
         <v>68.72</v>
       </c>
       <c r="M12">
-        <v>5.819220665461962</v>
+        <v>6.401142732008156</v>
       </c>
       <c r="N12">
-        <v>62.90077933453804</v>
+        <v>62.31885726799185</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>62.90077933453804</v>
+        <v>62.31885726799185</v>
       </c>
       <c r="Q12">
-        <v>107.500779334538</v>
+        <v>106.9188572679919</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07119517864255194</v>
+        <v>0.07148051772842332</v>
       </c>
       <c r="T12">
-        <v>0.4949992997644877</v>
+        <v>0.500561089649482</v>
       </c>
       <c r="U12">
         <v>0.05773661666253409</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.8091414556359</v>
+        <v>10.73558314148719</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0699686886111755</v>
+        <v>0.07008805477780083</v>
       </c>
       <c r="C13">
-        <v>1128.727709055191</v>
+        <v>1112.577369451331</v>
       </c>
       <c r="D13">
-        <v>1235.38570066998</v>
+        <v>1229.314269394738</v>
       </c>
       <c r="E13">
-        <v>-309.2228412469348</v>
+        <v>-299.1439329183175</v>
       </c>
       <c r="F13">
-        <v>110.8679916147897</v>
+        <v>120.9468999434069</v>
       </c>
       <c r="G13">
         <v>4.21</v>
@@ -2353,28 +2353,28 @@
         <v>68.72</v>
       </c>
       <c r="M13">
-        <v>6.401142732008156</v>
+        <v>6.983064798554353</v>
       </c>
       <c r="N13">
-        <v>62.31885726799185</v>
+        <v>61.73693520144565</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>62.31885726799185</v>
+        <v>61.73693520144565</v>
       </c>
       <c r="Q13">
-        <v>106.9188572679919</v>
+        <v>106.3369352014456</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07148051772842332</v>
+        <v>0.07177234179351902</v>
       </c>
       <c r="T13">
-        <v>0.500561089649482</v>
+        <v>0.5062492838500441</v>
       </c>
       <c r="U13">
         <v>0.05773661666253409</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.73558314148719</v>
+        <v>9.840951213029921</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07008805477780083</v>
+        <v>0.07042842094442617</v>
       </c>
       <c r="C14">
-        <v>1112.577369451331</v>
+        <v>1085.509268579844</v>
       </c>
       <c r="D14">
-        <v>1229.314269394738</v>
+        <v>1212.325076851868</v>
       </c>
       <c r="E14">
-        <v>-299.1439329183175</v>
+        <v>-289.0650245897003</v>
       </c>
       <c r="F14">
-        <v>120.9468999434069</v>
+        <v>131.0258082720242</v>
       </c>
       <c r="G14">
         <v>4.21</v>
@@ -2435,45 +2435,45 @@
         <v>68.72</v>
       </c>
       <c r="M14">
-        <v>6.983064798554353</v>
+        <v>7.787730739162991</v>
       </c>
       <c r="N14">
-        <v>61.73693520144565</v>
+        <v>60.93226926083701</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>61.73693520144565</v>
+        <v>60.93226926083701</v>
       </c>
       <c r="Q14">
-        <v>106.3369352014456</v>
+        <v>105.532269260837</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07177234179351902</v>
+        <v>0.07207087445781235</v>
       </c>
       <c r="T14">
-        <v>0.5062492838500441</v>
+        <v>0.5120682411356768</v>
       </c>
       <c r="U14">
-        <v>0.05773661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V14">
         <v>0</v>
       </c>
       <c r="W14">
-        <v>0.05773661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>9.840951213029921</v>
+        <v>8.824136619724205</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07042842094442617</v>
+        <v>0.07056478711105152</v>
       </c>
       <c r="C15">
-        <v>1085.509268579844</v>
+        <v>1068.754747709405</v>
       </c>
       <c r="D15">
-        <v>1212.325076851868</v>
+        <v>1205.649464310047</v>
       </c>
       <c r="E15">
-        <v>-289.0650245897003</v>
+        <v>-278.9861162610831</v>
       </c>
       <c r="F15">
-        <v>131.0258082720242</v>
+        <v>141.1047166006414</v>
       </c>
       <c r="G15">
         <v>4.21</v>
@@ -2517,28 +2517,28 @@
         <v>68.72</v>
       </c>
       <c r="M15">
-        <v>7.787730739162991</v>
+        <v>8.386786949867837</v>
       </c>
       <c r="N15">
-        <v>60.93226926083701</v>
+        <v>60.33321305013216</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>60.93226926083701</v>
+        <v>60.33321305013216</v>
       </c>
       <c r="Q15">
-        <v>105.532269260837</v>
+        <v>104.9332130501322</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07207087445781235</v>
+        <v>0.07237634974220553</v>
       </c>
       <c r="T15">
-        <v>0.5120682411356768</v>
+        <v>0.5180225230093476</v>
       </c>
       <c r="U15">
         <v>0.05943661666253409</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.824136619724205</v>
+        <v>8.193841146886761</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07056478711105152</v>
+        <v>0.07070115327767686</v>
       </c>
       <c r="C16">
-        <v>1068.754747709405</v>
+        <v>1052.073342142668</v>
       </c>
       <c r="D16">
-        <v>1205.649464310047</v>
+        <v>1199.046967071927</v>
       </c>
       <c r="E16">
-        <v>-278.9861162610831</v>
+        <v>-268.9072079324658</v>
       </c>
       <c r="F16">
-        <v>141.1047166006414</v>
+        <v>151.1836249292587</v>
       </c>
       <c r="G16">
         <v>4.21</v>
@@ -2599,28 +2599,28 @@
         <v>68.72</v>
       </c>
       <c r="M16">
-        <v>8.386786949867837</v>
+        <v>8.985843160572681</v>
       </c>
       <c r="N16">
-        <v>60.33321305013216</v>
+        <v>59.73415683942731</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>60.33321305013216</v>
+        <v>59.73415683942731</v>
       </c>
       <c r="Q16">
-        <v>104.9332130501322</v>
+        <v>104.3341568394273</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07237634974220553</v>
+        <v>0.07268901268034911</v>
       </c>
       <c r="T16">
-        <v>0.5180225230093476</v>
+        <v>0.524116905632987</v>
       </c>
       <c r="U16">
         <v>0.05943661666253409</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.193841146886761</v>
+        <v>7.647585070427644</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07070115327767686</v>
+        <v>0.0709655194443022</v>
       </c>
       <c r="C17">
-        <v>1052.073342142668</v>
+        <v>1029.398331794773</v>
       </c>
       <c r="D17">
-        <v>1199.046967071927</v>
+        <v>1186.450865052649</v>
       </c>
       <c r="E17">
-        <v>-268.9072079324658</v>
+        <v>-258.8282996038486</v>
       </c>
       <c r="F17">
-        <v>151.1836249292587</v>
+        <v>161.2625332578759</v>
       </c>
       <c r="G17">
         <v>4.21</v>
@@ -2681,45 +2681,45 @@
         <v>68.72</v>
       </c>
       <c r="M17">
-        <v>8.98584316057268</v>
+        <v>9.713909397883826</v>
       </c>
       <c r="N17">
-        <v>59.73415683942732</v>
+        <v>59.00609060211617</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>59.73415683942732</v>
+        <v>59.00609060211617</v>
       </c>
       <c r="Q17">
-        <v>104.3341568394273</v>
+        <v>103.6060906021162</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07268901268034911</v>
+        <v>0.07300911997416279</v>
       </c>
       <c r="T17">
-        <v>0.524116905632987</v>
+        <v>0.5303563926048082</v>
       </c>
       <c r="U17">
-        <v>0.05943661666253409</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V17">
         <v>0</v>
       </c>
       <c r="W17">
-        <v>0.05943661666253409</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y17">
-        <v>7.647585070427646</v>
+        <v>7.074391698050081</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0709655194443022</v>
+        <v>0.07110988561092754</v>
       </c>
       <c r="C18">
-        <v>1029.398331794773</v>
+        <v>1012.55197433936</v>
       </c>
       <c r="D18">
-        <v>1186.450865052649</v>
+        <v>1179.683415925854</v>
       </c>
       <c r="E18">
-        <v>-258.8282996038486</v>
+        <v>-248.7493912752313</v>
       </c>
       <c r="F18">
-        <v>161.2625332578759</v>
+        <v>171.3414415864932</v>
       </c>
       <c r="G18">
         <v>4.21</v>
@@ -2763,28 +2763,28 @@
         <v>68.72</v>
       </c>
       <c r="M18">
-        <v>9.713909397883826</v>
+        <v>10.32102873525157</v>
       </c>
       <c r="N18">
-        <v>59.00609060211617</v>
+        <v>58.39897126474843</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>59.00609060211617</v>
+        <v>58.39897126474843</v>
       </c>
       <c r="Q18">
-        <v>103.6060906021162</v>
+        <v>102.9989712647484</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07300911997416279</v>
+        <v>0.07333694069674307</v>
       </c>
       <c r="T18">
-        <v>0.5303563926048082</v>
+        <v>0.5367462286602879</v>
       </c>
       <c r="U18">
         <v>0.0602366166625341</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.074391698050081</v>
+        <v>6.658251009929486</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07110988561092754</v>
+        <v>0.07125425177755287</v>
       </c>
       <c r="C19">
-        <v>1012.55197433936</v>
+        <v>995.7823813236814</v>
       </c>
       <c r="D19">
-        <v>1179.683415925854</v>
+        <v>1172.992731238792</v>
       </c>
       <c r="E19">
-        <v>-248.7493912752313</v>
+        <v>-238.6704829466141</v>
       </c>
       <c r="F19">
-        <v>171.3414415864932</v>
+        <v>181.4203499151104</v>
       </c>
       <c r="G19">
         <v>4.21</v>
@@ -2845,28 +2845,28 @@
         <v>68.72</v>
       </c>
       <c r="M19">
-        <v>10.32102873525157</v>
+        <v>10.92814807261931</v>
       </c>
       <c r="N19">
-        <v>58.39897126474843</v>
+        <v>57.79185192738069</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>58.39897126474843</v>
+        <v>57.79185192738069</v>
       </c>
       <c r="Q19">
-        <v>102.9989712647484</v>
+        <v>102.3918519273807</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07333694069674307</v>
+        <v>0.07367275704670334</v>
       </c>
       <c r="T19">
-        <v>0.5367462286602879</v>
+        <v>0.5432919143756572</v>
       </c>
       <c r="U19">
         <v>0.0602366166625341</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.658251009929486</v>
+        <v>6.288348176044515</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07125425177755289</v>
+        <v>0.07158861794417823</v>
       </c>
       <c r="C20">
-        <v>995.7823813236807</v>
+        <v>970.4948610456881</v>
       </c>
       <c r="D20">
-        <v>1172.992731238791</v>
+        <v>1157.784119289416</v>
       </c>
       <c r="E20">
-        <v>-238.6704829466141</v>
+        <v>-228.5915746179969</v>
       </c>
       <c r="F20">
-        <v>181.4203499151104</v>
+        <v>191.4992582437276</v>
       </c>
       <c r="G20">
         <v>4.21</v>
@@ -2927,45 +2927,45 @@
         <v>68.72</v>
       </c>
       <c r="M20">
-        <v>10.9281480726193</v>
+        <v>11.72676666823077</v>
       </c>
       <c r="N20">
-        <v>57.79185192738069</v>
+        <v>56.99323333176923</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>57.79185192738069</v>
+        <v>56.99323333176923</v>
       </c>
       <c r="Q20">
-        <v>102.3918519273807</v>
+        <v>101.5932333317692</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07367275704670334</v>
+        <v>0.07401686515839104</v>
       </c>
       <c r="T20">
-        <v>0.5432919143756572</v>
+        <v>0.5499992219605419</v>
       </c>
       <c r="U20">
-        <v>0.0602366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V20">
         <v>0</v>
       </c>
       <c r="W20">
-        <v>0.0602366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y20">
-        <v>6.288348176044516</v>
+        <v>5.860097838065695</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07158861794417823</v>
+        <v>0.07174298411080357</v>
       </c>
       <c r="C21">
-        <v>970.4948610456881</v>
+        <v>953.5268957176496</v>
       </c>
       <c r="D21">
-        <v>1157.784119289416</v>
+        <v>1150.895062289994</v>
       </c>
       <c r="E21">
-        <v>-228.5915746179969</v>
+        <v>-218.5126662893796</v>
       </c>
       <c r="F21">
-        <v>191.4992582437276</v>
+        <v>201.5781665723449</v>
       </c>
       <c r="G21">
         <v>4.21</v>
@@ -3009,28 +3009,28 @@
         <v>68.72</v>
       </c>
       <c r="M21">
-        <v>11.72676666823077</v>
+        <v>12.34396491392713</v>
       </c>
       <c r="N21">
-        <v>56.99323333176923</v>
+        <v>56.37603508607287</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>56.99323333176923</v>
+        <v>56.37603508607287</v>
       </c>
       <c r="Q21">
-        <v>101.5932333317692</v>
+        <v>100.9760350860729</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07401686515839104</v>
+        <v>0.07436957597287093</v>
       </c>
       <c r="T21">
-        <v>0.5499992219605419</v>
+        <v>0.5568742122350486</v>
       </c>
       <c r="U21">
         <v>0.0612366166625341</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.860097838065695</v>
+        <v>5.567092946162409</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07174298411080357</v>
+        <v>0.07189735027742891</v>
       </c>
       <c r="C22">
-        <v>953.5268957176496</v>
+        <v>936.6404281132774</v>
       </c>
       <c r="D22">
-        <v>1150.895062289994</v>
+        <v>1144.087503014239</v>
       </c>
       <c r="E22">
-        <v>-218.5126662893796</v>
+        <v>-208.4337579607623</v>
       </c>
       <c r="F22">
-        <v>201.5781665723449</v>
+        <v>211.6570749009622</v>
       </c>
       <c r="G22">
         <v>4.21</v>
@@ -3091,28 +3091,28 @@
         <v>68.72</v>
       </c>
       <c r="M22">
-        <v>12.34396491392713</v>
+        <v>12.96116315962349</v>
       </c>
       <c r="N22">
-        <v>56.37603508607287</v>
+        <v>55.75883684037651</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>56.37603508607287</v>
+        <v>55.75883684037651</v>
       </c>
       <c r="Q22">
-        <v>100.9760350860729</v>
+        <v>100.3588368403765</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07436957597287093</v>
+        <v>0.07473121617505918</v>
       </c>
       <c r="T22">
-        <v>0.5568742122350486</v>
+        <v>0.5639232528962518</v>
       </c>
       <c r="U22">
         <v>0.0612366166625341</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.567092946162409</v>
+        <v>5.301993282059438</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07189735027742891</v>
+        <v>0.07205171644405425</v>
       </c>
       <c r="C23">
-        <v>936.6404281132774</v>
+        <v>919.8340205561568</v>
       </c>
       <c r="D23">
-        <v>1144.087503014239</v>
+        <v>1137.360003785736</v>
       </c>
       <c r="E23">
-        <v>-208.4337579607624</v>
+        <v>-198.3548496321451</v>
       </c>
       <c r="F23">
-        <v>211.6570749009621</v>
+        <v>221.7359832295794</v>
       </c>
       <c r="G23">
         <v>4.21</v>
@@ -3173,28 +3173,28 @@
         <v>68.72</v>
       </c>
       <c r="M23">
-        <v>12.96116315962349</v>
+        <v>13.57836140531984</v>
       </c>
       <c r="N23">
-        <v>55.75883684037652</v>
+        <v>55.14163859468016</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>55.75883684037652</v>
+        <v>55.14163859468016</v>
       </c>
       <c r="Q23">
-        <v>100.3588368403765</v>
+        <v>99.74163859468015</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07473121617505918</v>
+        <v>0.07510212920294454</v>
       </c>
       <c r="T23">
-        <v>0.5639232528962518</v>
+        <v>0.5711530381897933</v>
       </c>
       <c r="U23">
         <v>0.0612366166625341</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.301993282059438</v>
+        <v>5.060993587420374</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07205171644405425</v>
+        <v>0.07220608261067959</v>
       </c>
       <c r="C24">
-        <v>919.8340205561568</v>
+        <v>903.1062689876721</v>
       </c>
       <c r="D24">
-        <v>1137.360003785736</v>
+        <v>1130.711160545869</v>
       </c>
       <c r="E24">
-        <v>-198.3548496321451</v>
+        <v>-188.2759413035279</v>
       </c>
       <c r="F24">
-        <v>221.7359832295794</v>
+        <v>231.8148915581966</v>
       </c>
       <c r="G24">
         <v>4.21</v>
@@ -3255,28 +3255,28 @@
         <v>68.72</v>
       </c>
       <c r="M24">
-        <v>13.57836140531984</v>
+        <v>14.1955596510162</v>
       </c>
       <c r="N24">
-        <v>55.14163859468016</v>
+        <v>54.5244403489838</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>55.14163859468016</v>
+        <v>54.5244403489838</v>
       </c>
       <c r="Q24">
-        <v>99.74163859468015</v>
+        <v>99.1244403489838</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07510212920294454</v>
+        <v>0.07548267633545032</v>
       </c>
       <c r="T24">
-        <v>0.5711530381897933</v>
+        <v>0.5785706101143362</v>
       </c>
       <c r="U24">
         <v>0.0612366166625341</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.060993587420374</v>
+        <v>4.840950387967313</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07220608261067959</v>
+        <v>0.07236044877730494</v>
       </c>
       <c r="C25">
-        <v>903.1062689876721</v>
+        <v>886.4558019900953</v>
       </c>
       <c r="D25">
-        <v>1130.711160545869</v>
+        <v>1124.139601876909</v>
       </c>
       <c r="E25">
-        <v>-188.2759413035279</v>
+        <v>-178.1970329749106</v>
       </c>
       <c r="F25">
-        <v>231.8148915581966</v>
+        <v>241.8937998868139</v>
       </c>
       <c r="G25">
         <v>4.21</v>
@@ -3337,28 +3337,28 @@
         <v>68.72</v>
       </c>
       <c r="M25">
-        <v>14.1955596510162</v>
+        <v>14.81275789671256</v>
       </c>
       <c r="N25">
-        <v>54.5244403489838</v>
+        <v>53.90724210328744</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>54.5244403489838</v>
+        <v>53.90724210328744</v>
       </c>
       <c r="Q25">
-        <v>99.1244403489838</v>
+        <v>98.50724210328744</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07548267633545032</v>
+        <v>0.07587323786617993</v>
       </c>
       <c r="T25">
-        <v>0.5785706101143362</v>
+        <v>0.5861833813000512</v>
       </c>
       <c r="U25">
         <v>0.0612366166625341</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.840950387967313</v>
+        <v>4.639244121802008</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07236044877730492</v>
+        <v>0.07313981494393026</v>
       </c>
       <c r="C26">
-        <v>886.455801990096</v>
+        <v>844.3314546538145</v>
       </c>
       <c r="D26">
-        <v>1124.13960187691</v>
+        <v>1092.094162869246</v>
       </c>
       <c r="E26">
-        <v>-178.1970329749106</v>
+        <v>-168.1181246462934</v>
       </c>
       <c r="F26">
-        <v>241.8937998868139</v>
+        <v>251.9727082154311</v>
       </c>
       <c r="G26">
         <v>4.21</v>
@@ -3419,45 +3419,45 @@
         <v>68.72</v>
       </c>
       <c r="M26">
-        <v>14.81275789671255</v>
+        <v>16.05988791294749</v>
       </c>
       <c r="N26">
-        <v>53.90724210328744</v>
+        <v>52.66011208705251</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>53.90724210328744</v>
+        <v>52.66011208705251</v>
       </c>
       <c r="Q26">
-        <v>98.50724210328744</v>
+        <v>97.26011208705251</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07587323786617993</v>
+        <v>0.07627421437106233</v>
       </c>
       <c r="T26">
-        <v>0.5861833813000512</v>
+        <v>0.5939991597173852</v>
       </c>
       <c r="U26">
-        <v>0.0612366166625341</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V26">
         <v>0</v>
       </c>
       <c r="W26">
-        <v>0.0612366166625341</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.639244121802008</v>
+        <v>4.278983786966402</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07313981494393026</v>
+        <v>0.0733191811105556</v>
       </c>
       <c r="C27">
-        <v>844.3314546538145</v>
+        <v>827.1344295905162</v>
       </c>
       <c r="D27">
-        <v>1092.094162869246</v>
+        <v>1084.976046134565</v>
       </c>
       <c r="E27">
-        <v>-168.1181246462934</v>
+        <v>-158.0392163176761</v>
       </c>
       <c r="F27">
-        <v>251.9727082154311</v>
+        <v>262.0516165440484</v>
       </c>
       <c r="G27">
         <v>4.21</v>
@@ -3501,28 +3501,28 @@
         <v>68.72</v>
       </c>
       <c r="M27">
-        <v>16.05988791294749</v>
+        <v>16.70228342946539</v>
       </c>
       <c r="N27">
-        <v>52.66011208705251</v>
+        <v>52.01771657053461</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>52.66011208705251</v>
+        <v>52.01771657053461</v>
       </c>
       <c r="Q27">
-        <v>97.26011208705251</v>
+        <v>96.61771657053461</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07627421437106233</v>
+        <v>0.07668602807877939</v>
       </c>
       <c r="T27">
-        <v>0.5939991597173852</v>
+        <v>0.6020261753892417</v>
       </c>
       <c r="U27">
         <v>0.06373661666253409</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.278983786966402</v>
+        <v>4.114407487467695</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0733191811105556</v>
+        <v>0.07444354727718094</v>
       </c>
       <c r="C28">
-        <v>827.1344295905162</v>
+        <v>774.4661608706151</v>
       </c>
       <c r="D28">
-        <v>1084.976046134565</v>
+        <v>1042.386685743281</v>
       </c>
       <c r="E28">
-        <v>-158.0392163176761</v>
+        <v>-147.9603079890589</v>
       </c>
       <c r="F28">
-        <v>262.0516165440484</v>
+        <v>272.1305248726656</v>
       </c>
       <c r="G28">
         <v>4.21</v>
@@ -3583,45 +3583,45 @@
         <v>68.72</v>
       </c>
       <c r="M28">
-        <v>16.70228342946539</v>
+        <v>18.29713578303762</v>
       </c>
       <c r="N28">
-        <v>52.01771657053461</v>
+        <v>50.42286421696238</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>52.01771657053461</v>
+        <v>50.42286421696238</v>
       </c>
       <c r="Q28">
-        <v>96.61771657053461</v>
+        <v>95.02286421696238</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07668602807877939</v>
+        <v>0.07710912435383116</v>
       </c>
       <c r="T28">
-        <v>0.6020261753892417</v>
+        <v>0.6102731092986835</v>
       </c>
       <c r="U28">
-        <v>0.06373661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V28">
         <v>0</v>
       </c>
       <c r="W28">
-        <v>0.06373661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.114407487467695</v>
+        <v>3.755779091048062</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07444354727718094</v>
+        <v>0.07465791344380629</v>
       </c>
       <c r="C29">
-        <v>774.4661608706151</v>
+        <v>756.6440579967924</v>
       </c>
       <c r="D29">
-        <v>1042.386685743281</v>
+        <v>1034.643491198075</v>
       </c>
       <c r="E29">
-        <v>-147.9603079890589</v>
+        <v>-137.8813996604416</v>
       </c>
       <c r="F29">
-        <v>272.1305248726656</v>
+        <v>282.2094332012829</v>
       </c>
       <c r="G29">
         <v>4.21</v>
@@ -3665,28 +3665,28 @@
         <v>68.72</v>
       </c>
       <c r="M29">
-        <v>18.29713578303762</v>
+        <v>18.97480747870568</v>
       </c>
       <c r="N29">
-        <v>50.42286421696238</v>
+        <v>49.74519252129432</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>50.42286421696238</v>
+        <v>49.74519252129432</v>
       </c>
       <c r="Q29">
-        <v>95.02286421696238</v>
+        <v>94.34519252129432</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07710912435383116</v>
+        <v>0.07754397330318992</v>
       </c>
       <c r="T29">
-        <v>0.6102731092986835</v>
+        <v>0.6187491247056095</v>
       </c>
       <c r="U29">
         <v>0.0672366166625341</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.755779091048062</v>
+        <v>3.621644123510631</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07465791344380629</v>
+        <v>0.07568427961043164</v>
       </c>
       <c r="C30">
-        <v>756.6440579967924</v>
+        <v>711.0306449811637</v>
       </c>
       <c r="D30">
-        <v>1034.643491198075</v>
+        <v>999.1089865110639</v>
       </c>
       <c r="E30">
-        <v>-137.8813996604416</v>
+        <v>-127.8024913318243</v>
       </c>
       <c r="F30">
-        <v>282.2094332012829</v>
+        <v>292.2883415299002</v>
       </c>
       <c r="G30">
         <v>4.21</v>
@@ -3747,45 +3747,45 @@
         <v>68.72</v>
       </c>
       <c r="M30">
-        <v>18.97480747870568</v>
+        <v>20.47088653065746</v>
       </c>
       <c r="N30">
-        <v>49.74519252129432</v>
+        <v>48.24911346934254</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>49.74519252129432</v>
+        <v>48.24911346934254</v>
       </c>
       <c r="Q30">
-        <v>94.34519252129432</v>
+        <v>92.84911346934254</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07754397330318992</v>
+        <v>0.07799107151872782</v>
       </c>
       <c r="T30">
-        <v>0.6187491247056095</v>
+        <v>0.627463901109914</v>
       </c>
       <c r="U30">
-        <v>0.0672366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V30">
         <v>0</v>
       </c>
       <c r="W30">
-        <v>0.0672366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.621644123510631</v>
+        <v>3.356962576930123</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07568427961043162</v>
+        <v>0.07592664577705698</v>
       </c>
       <c r="C31">
-        <v>711.0306449811649</v>
+        <v>692.9139943531362</v>
       </c>
       <c r="D31">
-        <v>999.1089865110649</v>
+        <v>991.0712442116535</v>
       </c>
       <c r="E31">
-        <v>-127.8024913318244</v>
+        <v>-117.7235830032072</v>
       </c>
       <c r="F31">
-        <v>292.2883415299001</v>
+        <v>302.3672498585173</v>
       </c>
       <c r="G31">
         <v>4.21</v>
@@ -3829,28 +3829,28 @@
         <v>68.72</v>
       </c>
       <c r="M31">
-        <v>20.47088653065746</v>
+        <v>21.17677916964564</v>
       </c>
       <c r="N31">
-        <v>48.24911346934255</v>
+        <v>47.54322083035436</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>48.24911346934255</v>
+        <v>47.54322083035436</v>
       </c>
       <c r="Q31">
-        <v>92.84911346934254</v>
+        <v>92.14322083035435</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07799107151872781</v>
+        <v>0.07845094396899535</v>
       </c>
       <c r="T31">
-        <v>0.6274639011099139</v>
+        <v>0.6364276711257698</v>
       </c>
       <c r="U31">
         <v>0.07003661666253409</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.356962576930123</v>
+        <v>3.245063824365786</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07592664577705698</v>
+        <v>0.07616901194368231</v>
       </c>
       <c r="C32">
-        <v>692.9139943531362</v>
+        <v>674.925637447212</v>
       </c>
       <c r="D32">
-        <v>991.0712442116535</v>
+        <v>983.1617956343465</v>
       </c>
       <c r="E32">
-        <v>-117.7235830032072</v>
+        <v>-107.6446746745899</v>
       </c>
       <c r="F32">
-        <v>302.3672498585173</v>
+        <v>312.4461581871346</v>
       </c>
       <c r="G32">
         <v>4.21</v>
@@ -3911,28 +3911,28 @@
         <v>68.72</v>
       </c>
       <c r="M32">
-        <v>21.17677916964564</v>
+        <v>21.88267180863383</v>
       </c>
       <c r="N32">
-        <v>47.54322083035436</v>
+        <v>46.83732819136617</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>47.54322083035436</v>
+        <v>46.83732819136617</v>
       </c>
       <c r="Q32">
-        <v>92.14322083035435</v>
+        <v>91.43732819136616</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07845094396899535</v>
+        <v>0.07892414605550253</v>
       </c>
       <c r="T32">
-        <v>0.6364276711257698</v>
+        <v>0.6456512605623752</v>
       </c>
       <c r="U32">
         <v>0.07003661666253409</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.245063824365786</v>
+        <v>3.140384346160438</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07616901194368231</v>
+        <v>0.07641137811030765</v>
       </c>
       <c r="C33">
-        <v>674.925637447212</v>
+        <v>657.0625269594586</v>
       </c>
       <c r="D33">
-        <v>983.1617956343465</v>
+        <v>975.3775934752103</v>
       </c>
       <c r="E33">
-        <v>-107.6446746745899</v>
+        <v>-97.56576634597269</v>
       </c>
       <c r="F33">
-        <v>312.4461581871346</v>
+        <v>322.5250665157518</v>
       </c>
       <c r="G33">
         <v>4.21</v>
@@ -3993,28 +3993,28 @@
         <v>68.72</v>
       </c>
       <c r="M33">
-        <v>21.88267180863383</v>
+        <v>22.58856444762202</v>
       </c>
       <c r="N33">
-        <v>46.83732819136617</v>
+        <v>46.13143555237798</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>46.83732819136617</v>
+        <v>46.13143555237798</v>
       </c>
       <c r="Q33">
-        <v>91.43732819136616</v>
+        <v>90.73143555237797</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07892414605550253</v>
+        <v>0.0794112658504364</v>
       </c>
       <c r="T33">
-        <v>0.6456512605623752</v>
+        <v>0.6551461320412337</v>
       </c>
       <c r="U33">
         <v>0.07003661666253409</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.140384346160438</v>
+        <v>3.042247335342924</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07641137811030765</v>
+        <v>0.07922774427693299</v>
       </c>
       <c r="C34">
-        <v>657.0625269594586</v>
+        <v>564.8057596885727</v>
       </c>
       <c r="D34">
-        <v>975.3775934752103</v>
+        <v>893.1997345329418</v>
       </c>
       <c r="E34">
-        <v>-97.56576634597269</v>
+        <v>-87.48685801735542</v>
       </c>
       <c r="F34">
-        <v>322.5250665157518</v>
+        <v>332.6039748443691</v>
       </c>
       <c r="G34">
         <v>4.21</v>
@@ -4075,45 +4075,45 @@
         <v>68.72</v>
       </c>
       <c r="M34">
-        <v>22.58856444762202</v>
+        <v>25.88876809039629</v>
       </c>
       <c r="N34">
-        <v>46.13143555237798</v>
+        <v>42.8312319096037</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>46.13143555237798</v>
+        <v>42.8312319096037</v>
       </c>
       <c r="Q34">
-        <v>90.73143555237797</v>
+        <v>87.4312319096037</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.0794112658504364</v>
+        <v>0.07991292653477126</v>
       </c>
       <c r="T34">
-        <v>0.6551461320412337</v>
+        <v>0.6649244325194611</v>
       </c>
       <c r="U34">
-        <v>0.07003661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V34">
         <v>0</v>
       </c>
       <c r="W34">
-        <v>0.07003661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>3.042247335342924</v>
+        <v>2.65443298653876</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07922774427693299</v>
+        <v>0.07954811044355833</v>
       </c>
       <c r="C35">
-        <v>564.8057596885727</v>
+        <v>546.2478292392454</v>
       </c>
       <c r="D35">
-        <v>893.1997345329418</v>
+        <v>884.7207124122318</v>
       </c>
       <c r="E35">
-        <v>-87.48685801735542</v>
+        <v>-77.40794968873814</v>
       </c>
       <c r="F35">
-        <v>332.6039748443691</v>
+        <v>342.6828831729864</v>
       </c>
       <c r="G35">
         <v>4.21</v>
@@ -4157,28 +4157,28 @@
         <v>68.72</v>
       </c>
       <c r="M35">
-        <v>25.88876809039629</v>
+        <v>26.6732762143477</v>
       </c>
       <c r="N35">
-        <v>42.8312319096037</v>
+        <v>42.0467237856523</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>42.8312319096037</v>
+        <v>42.0467237856523</v>
       </c>
       <c r="Q35">
-        <v>87.4312319096037</v>
+        <v>86.64672378565231</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07991292653477126</v>
+        <v>0.08042978905802536</v>
       </c>
       <c r="T35">
-        <v>0.6649244325194611</v>
+        <v>0.6749990451333923</v>
       </c>
       <c r="U35">
         <v>0.07783661666253411</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.65443298653876</v>
+        <v>2.57636142811115</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07954811044355833</v>
+        <v>0.07986847661018368</v>
       </c>
       <c r="C36">
-        <v>546.2478292392454</v>
+        <v>527.849365375092</v>
       </c>
       <c r="D36">
-        <v>884.7207124122318</v>
+        <v>876.4011568766955</v>
       </c>
       <c r="E36">
-        <v>-77.40794968873814</v>
+        <v>-67.32904136012093</v>
       </c>
       <c r="F36">
-        <v>342.6828831729864</v>
+        <v>352.7617915016036</v>
       </c>
       <c r="G36">
         <v>4.21</v>
@@ -4239,28 +4239,28 @@
         <v>68.72</v>
       </c>
       <c r="M36">
-        <v>26.6732762143477</v>
+        <v>27.4577843382991</v>
       </c>
       <c r="N36">
-        <v>42.0467237856523</v>
+        <v>41.2622156617009</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>42.0467237856523</v>
+        <v>41.2622156617009</v>
       </c>
       <c r="Q36">
-        <v>86.64672378565231</v>
+        <v>85.8622156617009</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08042978905802536</v>
+        <v>0.08096255504353345</v>
       </c>
       <c r="T36">
-        <v>0.6749990451333923</v>
+        <v>0.6853836458277521</v>
       </c>
       <c r="U36">
         <v>0.07783661666253411</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.57636142811115</v>
+        <v>2.502751101593689</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07986847661018368</v>
+        <v>0.08159284277680902</v>
       </c>
       <c r="C37">
-        <v>527.849365375092</v>
+        <v>475.5487058228292</v>
       </c>
       <c r="D37">
-        <v>876.4011568766955</v>
+        <v>834.17940565305</v>
       </c>
       <c r="E37">
-        <v>-67.32904136012093</v>
+        <v>-57.25013303150365</v>
       </c>
       <c r="F37">
-        <v>352.7617915016036</v>
+        <v>362.8406998302208</v>
       </c>
       <c r="G37">
         <v>4.21</v>
@@ -4321,45 +4321,45 @@
         <v>68.72</v>
       </c>
       <c r="M37">
-        <v>27.4577843382991</v>
+        <v>29.65737119158836</v>
       </c>
       <c r="N37">
-        <v>41.2622156617009</v>
+        <v>39.06262880841164</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>41.2622156617009</v>
+        <v>39.06262880841164</v>
       </c>
       <c r="Q37">
-        <v>85.8622156617009</v>
+        <v>83.66262880841164</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08096255504353345</v>
+        <v>0.08151196996608867</v>
       </c>
       <c r="T37">
-        <v>0.6853836458277521</v>
+        <v>0.6960927652938108</v>
       </c>
       <c r="U37">
-        <v>0.07783661666253411</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V37">
         <v>0</v>
       </c>
       <c r="W37">
-        <v>0.07783661666253411</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y37">
-        <v>2.502751101593689</v>
+        <v>2.317130522326634</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08159284277680903</v>
+        <v>0.08195220894343436</v>
       </c>
       <c r="C38">
-        <v>475.5487058228289</v>
+        <v>457.1777493995469</v>
       </c>
       <c r="D38">
-        <v>834.1794056530497</v>
+        <v>825.8873575583849</v>
       </c>
       <c r="E38">
-        <v>-57.25013303150371</v>
+        <v>-47.17122470288643</v>
       </c>
       <c r="F38">
-        <v>362.8406998302208</v>
+        <v>372.9196081588381</v>
       </c>
       <c r="G38">
         <v>4.21</v>
@@ -4403,28 +4403,28 @@
         <v>68.72</v>
       </c>
       <c r="M38">
-        <v>29.65737119158836</v>
+        <v>30.48118705802137</v>
       </c>
       <c r="N38">
-        <v>39.06262880841165</v>
+        <v>38.23881294197863</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
       <c r="P38">
-        <v>39.06262880841165</v>
+        <v>38.23881294197863</v>
       </c>
       <c r="Q38">
-        <v>83.66262880841165</v>
+        <v>82.83881294197863</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08151196996608867</v>
+        <v>0.08207882663221705</v>
       </c>
       <c r="T38">
-        <v>0.6960927652938108</v>
+        <v>0.707141856806411</v>
       </c>
       <c r="U38">
         <v>0.0817366166625341</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.317130522326634</v>
+        <v>2.254505373074563</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08195220894343436</v>
+        <v>0.0823115751100597</v>
       </c>
       <c r="C39">
-        <v>457.1777493995469</v>
+        <v>438.9700223920469</v>
       </c>
       <c r="D39">
-        <v>825.8873575583849</v>
+        <v>817.7585388795021</v>
       </c>
       <c r="E39">
-        <v>-47.17122470288643</v>
+        <v>-37.09231637426922</v>
       </c>
       <c r="F39">
-        <v>372.9196081588381</v>
+        <v>382.9985164874553</v>
       </c>
       <c r="G39">
         <v>4.21</v>
@@ -4485,28 +4485,28 @@
         <v>68.72</v>
       </c>
       <c r="M39">
-        <v>30.48118705802137</v>
+        <v>31.30500292445438</v>
       </c>
       <c r="N39">
-        <v>38.23881294197863</v>
+        <v>37.41499707554562</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
       <c r="P39">
-        <v>38.23881294197863</v>
+        <v>37.41499707554562</v>
       </c>
       <c r="Q39">
-        <v>82.83881294197863</v>
+        <v>82.01499707554562</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08207882663221705</v>
+        <v>0.08266396899725281</v>
       </c>
       <c r="T39">
-        <v>0.707141856806411</v>
+        <v>0.7185473706258692</v>
       </c>
       <c r="U39">
         <v>0.0817366166625341</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.254505373074563</v>
+        <v>2.195176284309443</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0823115751100597</v>
+        <v>0.08267094127668505</v>
       </c>
       <c r="C40">
-        <v>438.9700223920469</v>
+        <v>420.9207520068442</v>
       </c>
       <c r="D40">
-        <v>817.7585388795021</v>
+        <v>809.7881768229167</v>
       </c>
       <c r="E40">
-        <v>-37.09231637426922</v>
+        <v>-27.01340804565194</v>
       </c>
       <c r="F40">
-        <v>382.9985164874553</v>
+        <v>393.0774248160726</v>
       </c>
       <c r="G40">
         <v>4.21</v>
@@ -4567,28 +4567,28 @@
         <v>68.72</v>
       </c>
       <c r="M40">
-        <v>31.30500292445438</v>
+        <v>32.12881879088739</v>
       </c>
       <c r="N40">
-        <v>37.41499707554562</v>
+        <v>36.59118120911261</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
       <c r="P40">
-        <v>37.41499707554562</v>
+        <v>36.59118120911261</v>
       </c>
       <c r="Q40">
-        <v>82.01499707554562</v>
+        <v>81.19118120911261</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08266396899725281</v>
+        <v>0.08326829635786352</v>
       </c>
       <c r="T40">
-        <v>0.7185473706258692</v>
+        <v>0.7303268357180965</v>
       </c>
       <c r="U40">
         <v>0.0817366166625341</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.195176284309443</v>
+        <v>2.138889712916893</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08267094127668505</v>
+        <v>0.08303030744331039</v>
       </c>
       <c r="C41">
-        <v>420.9207520068442</v>
+        <v>403.0253497283318</v>
       </c>
       <c r="D41">
-        <v>809.7881768229167</v>
+        <v>801.9716828730216</v>
       </c>
       <c r="E41">
-        <v>-27.01340804565194</v>
+        <v>-16.93449971703467</v>
       </c>
       <c r="F41">
-        <v>393.0774248160726</v>
+        <v>403.1563331446898</v>
       </c>
       <c r="G41">
         <v>4.21</v>
@@ -4649,28 +4649,28 @@
         <v>68.72</v>
       </c>
       <c r="M41">
-        <v>32.12881879088739</v>
+        <v>32.9526346573204</v>
       </c>
       <c r="N41">
-        <v>36.59118120911261</v>
+        <v>35.7673653426796</v>
       </c>
       <c r="O41">
         <v>0</v>
       </c>
       <c r="P41">
-        <v>36.59118120911261</v>
+        <v>35.7673653426796</v>
       </c>
       <c r="Q41">
-        <v>81.19118120911261</v>
+        <v>80.36736534267959</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08326829635786352</v>
+        <v>0.08389276796382791</v>
       </c>
       <c r="T41">
-        <v>0.7303268357180965</v>
+        <v>0.7424989496467315</v>
       </c>
       <c r="U41">
         <v>0.0817366166625341</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.138889712916893</v>
+        <v>2.08541747009397</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08303030744331039</v>
+        <v>0.08338967360993574</v>
       </c>
       <c r="C42">
-        <v>403.0253497283318</v>
+        <v>385.279402510077</v>
       </c>
       <c r="D42">
-        <v>801.9716828730216</v>
+        <v>794.304643983384</v>
       </c>
       <c r="E42">
-        <v>-16.93449971703467</v>
+        <v>-6.855591388417452</v>
       </c>
       <c r="F42">
-        <v>403.1563331446898</v>
+        <v>413.235241473307</v>
       </c>
       <c r="G42">
         <v>4.21</v>
@@ -4731,28 +4731,28 @@
         <v>68.72</v>
       </c>
       <c r="M42">
-        <v>32.9526346573204</v>
+        <v>33.77645052375341</v>
       </c>
       <c r="N42">
-        <v>35.7673653426796</v>
+        <v>34.94354947624659</v>
       </c>
       <c r="O42">
         <v>0</v>
       </c>
       <c r="P42">
-        <v>35.7673653426796</v>
+        <v>34.94354947624659</v>
       </c>
       <c r="Q42">
-        <v>80.36736534267959</v>
+        <v>79.5435494762466</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08389276796382791</v>
+        <v>0.08453840809880805</v>
       </c>
       <c r="T42">
-        <v>0.7424989496467315</v>
+        <v>0.7550836776068456</v>
       </c>
       <c r="U42">
         <v>0.0817366166625341</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.08541747009397</v>
+        <v>2.034553629359971</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08338967360993574</v>
+        <v>0.08971303977656107</v>
       </c>
       <c r="C43">
-        <v>385.279402510077</v>
+        <v>260.8226433810055</v>
       </c>
       <c r="D43">
-        <v>794.304643983384</v>
+        <v>679.9267931829298</v>
       </c>
       <c r="E43">
-        <v>-6.855591388417452</v>
+        <v>3.223316940199823</v>
       </c>
       <c r="F43">
-        <v>413.235241473307</v>
+        <v>423.3141498019243</v>
       </c>
       <c r="G43">
         <v>4.21</v>
@@ -4813,45 +4813,45 @@
         <v>68.72</v>
       </c>
       <c r="M43">
-        <v>33.77645052375341</v>
+        <v>40.61132731737375</v>
       </c>
       <c r="N43">
-        <v>34.94354947624659</v>
+        <v>28.10867268262625</v>
       </c>
       <c r="O43">
         <v>0</v>
       </c>
       <c r="P43">
-        <v>34.94354947624659</v>
+        <v>28.10867268262625</v>
       </c>
       <c r="Q43">
-        <v>79.5435494762466</v>
+        <v>72.70867268262626</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08453840809880805</v>
+        <v>0.08520631168671854</v>
       </c>
       <c r="T43">
-        <v>0.7550836776068456</v>
+        <v>0.7681023617035154</v>
       </c>
       <c r="U43">
-        <v>0.0817366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V43">
         <v>0</v>
       </c>
       <c r="W43">
-        <v>0.0817366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.034553629359971</v>
+        <v>1.69213873417531</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08971303977656107</v>
+        <v>0.09021440594318642</v>
       </c>
       <c r="C44">
-        <v>260.8226433810056</v>
+        <v>243.0684710779013</v>
       </c>
       <c r="D44">
-        <v>679.9267931829298</v>
+        <v>672.2515292084428</v>
       </c>
       <c r="E44">
-        <v>3.223316940199766</v>
+        <v>13.30222526881704</v>
       </c>
       <c r="F44">
-        <v>423.3141498019243</v>
+        <v>433.3930581305415</v>
       </c>
       <c r="G44">
         <v>4.21</v>
@@ -4895,28 +4895,28 @@
         <v>68.72</v>
       </c>
       <c r="M44">
-        <v>40.61132731737374</v>
+        <v>41.57826368207312</v>
       </c>
       <c r="N44">
-        <v>28.10867268262626</v>
+        <v>27.14173631792688</v>
       </c>
       <c r="O44">
         <v>0</v>
       </c>
       <c r="P44">
-        <v>28.10867268262626</v>
+        <v>27.14173631792688</v>
       </c>
       <c r="Q44">
-        <v>72.70867268262626</v>
+        <v>71.74173631792688</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08520631168671852</v>
+        <v>0.08589765048823991</v>
       </c>
       <c r="T44">
-        <v>0.7681023617035153</v>
+        <v>0.7815778417334015</v>
       </c>
       <c r="U44">
         <v>0.0959366166625341</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.69213873417531</v>
+        <v>1.652786670589838</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09021440594318642</v>
+        <v>0.09071577210981176</v>
       </c>
       <c r="C45">
-        <v>243.0684710779013</v>
+        <v>225.4856469447589</v>
       </c>
       <c r="D45">
-        <v>672.2515292084428</v>
+        <v>664.7476134039176</v>
       </c>
       <c r="E45">
-        <v>13.30222526881704</v>
+        <v>23.38113359743426</v>
       </c>
       <c r="F45">
-        <v>433.3930581305415</v>
+        <v>443.4719664591588</v>
       </c>
       <c r="G45">
         <v>4.21</v>
@@ -4977,28 +4977,28 @@
         <v>68.72</v>
       </c>
       <c r="M45">
-        <v>41.57826368207312</v>
+        <v>42.54520004677249</v>
       </c>
       <c r="N45">
-        <v>27.14173631792688</v>
+        <v>26.17479995322751</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>27.14173631792688</v>
+        <v>26.17479995322751</v>
       </c>
       <c r="Q45">
-        <v>71.74173631792688</v>
+        <v>70.7747999532275</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08589765048823991</v>
+        <v>0.08661367996124419</v>
       </c>
       <c r="T45">
-        <v>0.7815778417334015</v>
+        <v>0.7955345889072123</v>
       </c>
       <c r="U45">
         <v>0.0959366166625341</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.652786670589838</v>
+        <v>1.615223337167341</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09071577210981176</v>
+        <v>0.0912171382764371</v>
       </c>
       <c r="C46">
-        <v>225.4856469447589</v>
+        <v>208.0684963720553</v>
       </c>
       <c r="D46">
-        <v>664.7476134039176</v>
+        <v>657.4093711598313</v>
       </c>
       <c r="E46">
-        <v>23.38113359743426</v>
+        <v>33.46004192605153</v>
       </c>
       <c r="F46">
-        <v>443.4719664591588</v>
+        <v>453.550874787776</v>
       </c>
       <c r="G46">
         <v>4.21</v>
@@ -5059,28 +5059,28 @@
         <v>68.72</v>
       </c>
       <c r="M46">
-        <v>42.54520004677249</v>
+        <v>43.51213641147187</v>
       </c>
       <c r="N46">
-        <v>26.17479995322751</v>
+        <v>25.20786358852813</v>
       </c>
       <c r="O46">
         <v>0</v>
       </c>
       <c r="P46">
-        <v>26.17479995322751</v>
+        <v>25.20786358852813</v>
       </c>
       <c r="Q46">
-        <v>70.7747999532275</v>
+        <v>69.80786358852814</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08661367996124419</v>
+        <v>0.08735574686963045</v>
       </c>
       <c r="T46">
-        <v>0.7955345889072123</v>
+        <v>0.8099988541600707</v>
       </c>
       <c r="U46">
         <v>0.0959366166625341</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.615223337167341</v>
+        <v>1.579329485230289</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0912171382764371</v>
+        <v>0.09171850444306244</v>
       </c>
       <c r="C47">
-        <v>208.0684963720553</v>
+        <v>190.8115925856225</v>
       </c>
       <c r="D47">
-        <v>657.4093711598313</v>
+        <v>650.2313757020157</v>
       </c>
       <c r="E47">
-        <v>33.46004192605153</v>
+        <v>43.53895025466875</v>
       </c>
       <c r="F47">
-        <v>453.550874787776</v>
+        <v>463.6297831163932</v>
       </c>
       <c r="G47">
         <v>4.21</v>
@@ -5141,28 +5141,28 @@
         <v>68.72</v>
       </c>
       <c r="M47">
-        <v>43.51213641147187</v>
+        <v>44.47907277617124</v>
       </c>
       <c r="N47">
-        <v>25.20786358852813</v>
+        <v>24.24092722382876</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>25.20786358852813</v>
+        <v>24.24092722382876</v>
       </c>
       <c r="Q47">
-        <v>69.80786358852814</v>
+        <v>68.84092722382876</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08735574686963045</v>
+        <v>0.08812529773758657</v>
       </c>
       <c r="T47">
-        <v>0.8099988541600707</v>
+        <v>0.8249988329408128</v>
       </c>
       <c r="U47">
         <v>0.0959366166625341</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.579329485230289</v>
+        <v>1.54499623555137</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09171850444306244</v>
+        <v>0.09221987060968778</v>
       </c>
       <c r="C48">
-        <v>190.8115925856225</v>
+        <v>173.7097432626974</v>
       </c>
       <c r="D48">
-        <v>650.2313757020157</v>
+        <v>643.2084347077079</v>
       </c>
       <c r="E48">
-        <v>43.53895025466875</v>
+        <v>53.61785858328602</v>
       </c>
       <c r="F48">
-        <v>463.6297831163932</v>
+        <v>473.7086914450105</v>
       </c>
       <c r="G48">
         <v>4.21</v>
@@ -5223,28 +5223,28 @@
         <v>68.72</v>
       </c>
       <c r="M48">
-        <v>44.47907277617124</v>
+        <v>45.44600914087062</v>
       </c>
       <c r="N48">
-        <v>24.24092722382876</v>
+        <v>23.27399085912938</v>
       </c>
       <c r="O48">
         <v>0</v>
       </c>
       <c r="P48">
-        <v>24.24092722382876</v>
+        <v>23.27399085912938</v>
       </c>
       <c r="Q48">
-        <v>68.84092722382876</v>
+        <v>67.87399085912938</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08812529773758657</v>
+        <v>0.08892388826093725</v>
       </c>
       <c r="T48">
-        <v>0.8249988329408128</v>
+        <v>0.8405648486566771</v>
       </c>
       <c r="U48">
         <v>0.0959366166625341</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.54499623555137</v>
+        <v>1.51212397522049</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09221987060968778</v>
+        <v>0.1199852367763131</v>
       </c>
       <c r="C49">
-        <v>173.7097432626974</v>
+        <v>-77.10328531912484</v>
       </c>
       <c r="D49">
-        <v>643.2084347077079</v>
+        <v>402.474314454503</v>
       </c>
       <c r="E49">
-        <v>53.61785858328602</v>
+        <v>63.6967669119033</v>
       </c>
       <c r="F49">
-        <v>473.7086914450105</v>
+        <v>483.7875997736278</v>
       </c>
       <c r="G49">
         <v>4.21</v>
@@ -5305,45 +5305,45 @@
         <v>68.72</v>
       </c>
       <c r="M49">
-        <v>45.44600914087062</v>
+        <v>73.89208117271205</v>
       </c>
       <c r="N49">
-        <v>23.27399085912938</v>
+        <v>-5.172081172712055</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P49">
-        <v>23.27399085912938</v>
+        <v>-5.172081172712055</v>
       </c>
       <c r="Q49">
-        <v>67.87399085912938</v>
+        <v>39.42791882728795</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08892388826093725</v>
+        <v>0.08975319380441682</v>
       </c>
       <c r="T49">
-        <v>0.8405648486566771</v>
+        <v>0.8567295572846902</v>
       </c>
       <c r="U49">
-        <v>0.0959366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V49">
         <v>0</v>
       </c>
       <c r="W49">
-        <v>0.0959366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y49">
-        <v>1.51212397522049</v>
+        <v>0.9300049329964998</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1199852367763131</v>
+        <v>0.1210546029429385</v>
       </c>
       <c r="C50">
-        <v>-77.10328531912478</v>
+        <v>-92.90134434394218</v>
       </c>
       <c r="D50">
-        <v>402.474314454503</v>
+        <v>396.7551637583028</v>
       </c>
       <c r="E50">
-        <v>63.69676691190324</v>
+        <v>73.77567524052046</v>
       </c>
       <c r="F50">
-        <v>483.7875997736277</v>
+        <v>493.8665081022449</v>
       </c>
       <c r="G50">
         <v>4.21</v>
@@ -5387,28 +5387,28 @@
         <v>68.72</v>
       </c>
       <c r="M50">
-        <v>73.89208117271205</v>
+        <v>75.43149953047688</v>
       </c>
       <c r="N50">
-        <v>-5.172081172712055</v>
+        <v>-6.711499530476885</v>
       </c>
       <c r="O50">
         <v>-0</v>
       </c>
       <c r="P50">
-        <v>-5.172081172712055</v>
+        <v>-6.711499530476885</v>
       </c>
       <c r="Q50">
-        <v>39.42791882728795</v>
+        <v>37.88850046952312</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08975319380441682</v>
+        <v>0.09061502113391519</v>
       </c>
       <c r="T50">
-        <v>0.8567295572846901</v>
+        <v>0.8735281760549782</v>
       </c>
       <c r="U50">
         <v>0.1527366166625341</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.9300049329964998</v>
+        <v>0.9110252404863672</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1210546029429385</v>
+        <v>0.1221239691095638</v>
       </c>
       <c r="C51">
-        <v>-92.90134434394218</v>
+        <v>-108.5391426714269</v>
       </c>
       <c r="D51">
-        <v>396.7551637583028</v>
+        <v>391.1962737594353</v>
       </c>
       <c r="E51">
-        <v>73.77567524052046</v>
+        <v>83.85458356913773</v>
       </c>
       <c r="F51">
-        <v>493.8665081022449</v>
+        <v>503.9454164308622</v>
       </c>
       <c r="G51">
         <v>4.21</v>
@@ -5469,28 +5469,28 @@
         <v>68.72</v>
       </c>
       <c r="M51">
-        <v>75.43149953047688</v>
+        <v>76.97091788824171</v>
       </c>
       <c r="N51">
-        <v>-6.711499530476885</v>
+        <v>-8.250917888241716</v>
       </c>
       <c r="O51">
         <v>-0</v>
       </c>
       <c r="P51">
-        <v>-6.711499530476885</v>
+        <v>-8.250917888241716</v>
       </c>
       <c r="Q51">
-        <v>37.88850046952312</v>
+        <v>36.34908211175829</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09061502113391519</v>
+        <v>0.0915113215565935</v>
       </c>
       <c r="T51">
-        <v>0.8735281760549782</v>
+        <v>0.8909987395760778</v>
       </c>
       <c r="U51">
         <v>0.1527366166625341</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.9110252404863672</v>
+        <v>0.8928047356766399</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1221239691095638</v>
+        <v>0.1231933352761891</v>
       </c>
       <c r="C52">
-        <v>-108.5391426714269</v>
+        <v>-124.0233234072271</v>
       </c>
       <c r="D52">
-        <v>391.1962737594353</v>
+        <v>385.7910013522524</v>
       </c>
       <c r="E52">
-        <v>83.85458356913773</v>
+        <v>93.93349189775495</v>
       </c>
       <c r="F52">
-        <v>503.9454164308622</v>
+        <v>514.0243247594794</v>
       </c>
       <c r="G52">
         <v>4.21</v>
@@ -5551,28 +5551,28 @@
         <v>68.72</v>
       </c>
       <c r="M52">
-        <v>76.97091788824171</v>
+        <v>78.51033624600655</v>
       </c>
       <c r="N52">
-        <v>-8.250917888241716</v>
+        <v>-9.790336246006547</v>
       </c>
       <c r="O52">
         <v>-0</v>
       </c>
       <c r="P52">
-        <v>-8.250917888241716</v>
+        <v>-9.790336246006547</v>
       </c>
       <c r="Q52">
-        <v>36.34908211175829</v>
+        <v>34.80966375399345</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.0915113215565935</v>
+        <v>0.09244420566999337</v>
       </c>
       <c r="T52">
-        <v>0.8909987395760778</v>
+        <v>0.9091823873225283</v>
       </c>
       <c r="U52">
         <v>0.1527366166625341</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8928047356766399</v>
+        <v>0.875298760467294</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1231933352761891</v>
+        <v>0.1242627014428145</v>
       </c>
       <c r="C53">
-        <v>-124.0233234072271</v>
+        <v>-139.3601675021179</v>
       </c>
       <c r="D53">
-        <v>385.7910013522524</v>
+        <v>380.5330655859789</v>
       </c>
       <c r="E53">
-        <v>93.93349189775495</v>
+        <v>104.0124002263723</v>
       </c>
       <c r="F53">
-        <v>514.0243247594794</v>
+        <v>524.1032330880968</v>
       </c>
       <c r="G53">
         <v>4.21</v>
@@ -5633,28 +5633,28 @@
         <v>68.72</v>
       </c>
       <c r="M53">
-        <v>78.51033624600655</v>
+        <v>80.04975460377139</v>
       </c>
       <c r="N53">
-        <v>-9.790336246006547</v>
+        <v>-11.32975460377139</v>
       </c>
       <c r="O53">
         <v>-0</v>
       </c>
       <c r="P53">
-        <v>-9.790336246006547</v>
+        <v>-11.32975460377139</v>
       </c>
       <c r="Q53">
-        <v>34.80966375399345</v>
+        <v>33.27024539622861</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09244420566999337</v>
+        <v>0.09341595995478488</v>
       </c>
       <c r="T53">
-        <v>0.9091823873225283</v>
+        <v>0.9281236870584144</v>
       </c>
       <c r="U53">
         <v>0.1527366166625341</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.875298760467294</v>
+        <v>0.858466091996769</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1242627014428145</v>
+        <v>0.1253320676094398</v>
       </c>
       <c r="C54">
-        <v>-139.3601675021179</v>
+        <v>-154.5556180991718</v>
       </c>
       <c r="D54">
-        <v>380.5330655859789</v>
+        <v>375.4165233175422</v>
       </c>
       <c r="E54">
-        <v>104.0124002263723</v>
+        <v>114.0913085549895</v>
       </c>
       <c r="F54">
-        <v>524.1032330880968</v>
+        <v>534.182141416714</v>
       </c>
       <c r="G54">
         <v>4.21</v>
@@ -5715,28 +5715,28 @@
         <v>68.72</v>
       </c>
       <c r="M54">
-        <v>80.04975460377139</v>
+        <v>81.58917296153622</v>
       </c>
       <c r="N54">
-        <v>-11.32975460377139</v>
+        <v>-12.86917296153622</v>
       </c>
       <c r="O54">
         <v>-0</v>
       </c>
       <c r="P54">
-        <v>-11.32975460377139</v>
+        <v>-12.86917296153622</v>
       </c>
       <c r="Q54">
-        <v>33.27024539622861</v>
+        <v>31.73082703846378</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09341595995478488</v>
+        <v>0.09442906548573776</v>
       </c>
       <c r="T54">
-        <v>0.9281236870584144</v>
+        <v>0.9478709995490189</v>
       </c>
       <c r="U54">
         <v>0.1527366166625341</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.858466091996769</v>
+        <v>0.8422686185628678</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1253320676094398</v>
+        <v>0.1264014337760652</v>
       </c>
       <c r="C55">
-        <v>-154.5556180991718</v>
+        <v>-169.6153029427982</v>
       </c>
       <c r="D55">
-        <v>375.4165233175422</v>
+        <v>370.4357468025331</v>
       </c>
       <c r="E55">
-        <v>114.0913085549895</v>
+        <v>124.1702168836067</v>
       </c>
       <c r="F55">
-        <v>534.182141416714</v>
+        <v>544.2610497453312</v>
       </c>
       <c r="G55">
         <v>4.21</v>
@@ -5797,28 +5797,28 @@
         <v>68.72</v>
       </c>
       <c r="M55">
-        <v>81.58917296153622</v>
+        <v>83.12859131930105</v>
       </c>
       <c r="N55">
-        <v>-12.86917296153622</v>
+        <v>-14.40859131930105</v>
       </c>
       <c r="O55">
         <v>-0</v>
       </c>
       <c r="P55">
-        <v>-12.86917296153622</v>
+        <v>-14.40859131930105</v>
       </c>
       <c r="Q55">
-        <v>31.73082703846378</v>
+        <v>30.19140868069895</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09442906548573776</v>
+        <v>0.09548621908325379</v>
       </c>
       <c r="T55">
-        <v>0.9478709995490189</v>
+        <v>0.9684768908435627</v>
       </c>
       <c r="U55">
         <v>0.1527366166625341</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8422686185628678</v>
+        <v>0.8266710515524444</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1264014337760652</v>
+        <v>0.1274707999426905</v>
       </c>
       <c r="C56">
-        <v>-169.6153029427982</v>
+        <v>-184.544555027289</v>
       </c>
       <c r="D56">
-        <v>370.4357468025331</v>
+        <v>365.5854030466596</v>
       </c>
       <c r="E56">
-        <v>124.1702168836067</v>
+        <v>134.249125212224</v>
       </c>
       <c r="F56">
-        <v>544.2610497453312</v>
+        <v>554.3399580739485</v>
       </c>
       <c r="G56">
         <v>4.21</v>
@@ -5879,28 +5879,28 @@
         <v>68.72</v>
       </c>
       <c r="M56">
-        <v>83.12859131930105</v>
+        <v>84.66800967706591</v>
       </c>
       <c r="N56">
-        <v>-14.40859131930105</v>
+        <v>-15.94800967706591</v>
       </c>
       <c r="O56">
         <v>-0</v>
       </c>
       <c r="P56">
-        <v>-14.40859131930105</v>
+        <v>-15.94800967706591</v>
       </c>
       <c r="Q56">
-        <v>30.19140868069895</v>
+        <v>28.65199032293409</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09548621908325379</v>
+        <v>0.09659035728510389</v>
       </c>
       <c r="T56">
-        <v>0.9684768908435627</v>
+        <v>0.9899985995289754</v>
       </c>
       <c r="U56">
         <v>0.1527366166625341</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8266710515524444</v>
+        <v>0.8116406687969451</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1274707999426905</v>
+        <v>0.1587801661093158</v>
       </c>
       <c r="C57">
-        <v>-184.544555027289</v>
+        <v>-295.9354692002432</v>
       </c>
       <c r="D57">
-        <v>365.5854030466596</v>
+        <v>264.2733972023225</v>
       </c>
       <c r="E57">
-        <v>134.249125212224</v>
+        <v>144.3280335408413</v>
       </c>
       <c r="F57">
-        <v>554.3399580739485</v>
+        <v>564.4188664025658</v>
       </c>
       <c r="G57">
         <v>4.21</v>
@@ -5961,45 +5961,45 @@
         <v>68.72</v>
       </c>
       <c r="M57">
-        <v>84.66800967706591</v>
+        <v>116.6860468205693</v>
       </c>
       <c r="N57">
-        <v>-15.94800967706591</v>
+        <v>-47.96604682056928</v>
       </c>
       <c r="O57">
         <v>-0</v>
       </c>
       <c r="P57">
-        <v>-15.94800967706591</v>
+        <v>-47.96604682056928</v>
       </c>
       <c r="Q57">
-        <v>28.65199032293409</v>
+        <v>-3.366046820569274</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09659035728510389</v>
+        <v>0.09774468358703806</v>
       </c>
       <c r="T57">
-        <v>0.9899985995289754</v>
+        <v>1.012498567700088</v>
       </c>
       <c r="U57">
-        <v>0.1527366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V57">
         <v>0</v>
       </c>
       <c r="W57">
-        <v>0.1527366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.8116406687969451</v>
+        <v>0.5889307408423243</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1587801661093158</v>
+        <v>0.1603895322759412</v>
       </c>
       <c r="C58">
-        <v>-295.9354692002432</v>
+        <v>-309.7259963455982</v>
       </c>
       <c r="D58">
-        <v>264.2733972023225</v>
+        <v>260.5617783855848</v>
       </c>
       <c r="E58">
-        <v>144.3280335408413</v>
+        <v>154.4069418694585</v>
       </c>
       <c r="F58">
-        <v>564.4188664025658</v>
+        <v>574.497774731183</v>
       </c>
       <c r="G58">
         <v>4.21</v>
@@ -6043,28 +6043,28 @@
         <v>68.72</v>
       </c>
       <c r="M58">
-        <v>116.6860468205693</v>
+        <v>118.7697262280794</v>
       </c>
       <c r="N58">
-        <v>-47.96604682056928</v>
+        <v>-50.04972622807944</v>
       </c>
       <c r="O58">
         <v>-0</v>
       </c>
       <c r="P58">
-        <v>-47.96604682056928</v>
+        <v>-50.04972622807944</v>
       </c>
       <c r="Q58">
-        <v>-3.366046820569274</v>
+        <v>-5.449726228079435</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09774468358703806</v>
+        <v>0.09895269948441106</v>
       </c>
       <c r="T58">
-        <v>1.012498567700088</v>
+        <v>1.036045046018695</v>
       </c>
       <c r="U58">
         <v>0.2067366166625341</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5889307408423243</v>
+        <v>0.5785986225819326</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1603895322759412</v>
+        <v>0.1619988984425665</v>
       </c>
       <c r="C59">
-        <v>-309.7259963455982</v>
+        <v>-323.4137109199714</v>
       </c>
       <c r="D59">
-        <v>260.5617783855848</v>
+        <v>256.9529721398289</v>
       </c>
       <c r="E59">
-        <v>154.4069418694585</v>
+        <v>164.4858501980758</v>
       </c>
       <c r="F59">
-        <v>574.497774731183</v>
+        <v>584.5766830598003</v>
       </c>
       <c r="G59">
         <v>4.21</v>
@@ -6125,28 +6125,28 @@
         <v>68.72</v>
       </c>
       <c r="M59">
-        <v>118.7697262280794</v>
+        <v>120.8534056355896</v>
       </c>
       <c r="N59">
-        <v>-50.04972622807944</v>
+        <v>-52.13340563558963</v>
       </c>
       <c r="O59">
         <v>-0</v>
       </c>
       <c r="P59">
-        <v>-50.04972622807944</v>
+        <v>-52.13340563558963</v>
       </c>
       <c r="Q59">
-        <v>-5.449726228079435</v>
+        <v>-7.533405635589624</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09895269948441106</v>
+        <v>0.1002182399483256</v>
       </c>
       <c r="T59">
-        <v>1.036045046018695</v>
+        <v>1.060712785209617</v>
       </c>
       <c r="U59">
         <v>0.2067366166625341</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5785986225819326</v>
+        <v>0.5686227842615543</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1619988984425665</v>
+        <v>0.1636082646091918</v>
       </c>
       <c r="C60">
-        <v>-323.4137109199713</v>
+        <v>-337.0028264581376</v>
       </c>
       <c r="D60">
-        <v>256.9529721398289</v>
+        <v>253.4427649302798</v>
       </c>
       <c r="E60">
-        <v>164.4858501980757</v>
+        <v>174.5647585266929</v>
       </c>
       <c r="F60">
-        <v>584.5766830598002</v>
+        <v>594.6555913884174</v>
       </c>
       <c r="G60">
         <v>4.21</v>
@@ -6207,28 +6207,28 @@
         <v>68.72</v>
       </c>
       <c r="M60">
-        <v>120.8534056355896</v>
+        <v>122.9370850430998</v>
       </c>
       <c r="N60">
-        <v>-52.1334056355896</v>
+        <v>-54.21708504309976</v>
       </c>
       <c r="O60">
         <v>-0</v>
       </c>
       <c r="P60">
-        <v>-52.1334056355896</v>
+        <v>-54.21708504309976</v>
       </c>
       <c r="Q60">
-        <v>-7.533405635589595</v>
+        <v>-9.617085043099756</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1002182399483256</v>
+        <v>0.1015455140934067</v>
       </c>
       <c r="T60">
-        <v>1.060712785209616</v>
+        <v>1.086583828751314</v>
       </c>
       <c r="U60">
         <v>0.2067366166625341</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5686227842615545</v>
+        <v>0.5589851099520367</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1636082646091918</v>
+        <v>0.1652176307758172</v>
       </c>
       <c r="C61">
-        <v>-337.0028264581376</v>
+        <v>-350.4973293552025</v>
       </c>
       <c r="D61">
-        <v>253.4427649302798</v>
+        <v>250.0271703618321</v>
       </c>
       <c r="E61">
-        <v>174.5647585266929</v>
+        <v>184.6436668553101</v>
       </c>
       <c r="F61">
-        <v>594.6555913884174</v>
+        <v>604.7344997170346</v>
       </c>
       <c r="G61">
         <v>4.21</v>
@@ -6289,28 +6289,28 @@
         <v>68.72</v>
       </c>
       <c r="M61">
-        <v>122.9370850430998</v>
+        <v>125.0207644506099</v>
       </c>
       <c r="N61">
-        <v>-54.21708504309976</v>
+        <v>-56.30076445060992</v>
       </c>
       <c r="O61">
         <v>-0</v>
       </c>
       <c r="P61">
-        <v>-54.21708504309976</v>
+        <v>-56.30076445060992</v>
       </c>
       <c r="Q61">
-        <v>-9.617085043099756</v>
+        <v>-11.70076445060992</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1015455140934067</v>
+        <v>0.1029391519457419</v>
       </c>
       <c r="T61">
-        <v>1.086583828751314</v>
+        <v>1.113748424470097</v>
       </c>
       <c r="U61">
         <v>0.2067366166625341</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5589851099520367</v>
+        <v>0.5496686914528361</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1652176307758172</v>
+        <v>0.1668269969424425</v>
       </c>
       <c r="C62">
-        <v>-350.4973293552025</v>
+        <v>-363.9009939686409</v>
       </c>
       <c r="D62">
-        <v>250.0271703618321</v>
+        <v>246.702414077011</v>
       </c>
       <c r="E62">
-        <v>184.6436668553101</v>
+        <v>194.7225751839275</v>
       </c>
       <c r="F62">
-        <v>604.7344997170346</v>
+        <v>614.813408045652</v>
       </c>
       <c r="G62">
         <v>4.21</v>
@@ -6371,28 +6371,28 @@
         <v>68.72</v>
       </c>
       <c r="M62">
-        <v>125.0207644506099</v>
+        <v>127.1044438581201</v>
       </c>
       <c r="N62">
-        <v>-56.30076445060992</v>
+        <v>-58.38444385812011</v>
       </c>
       <c r="O62">
         <v>-0</v>
       </c>
       <c r="P62">
-        <v>-56.30076445060992</v>
+        <v>-58.38444385812011</v>
       </c>
       <c r="Q62">
-        <v>-11.70076445060992</v>
+        <v>-13.78444385812011</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1029391519457419</v>
+        <v>0.1044042584058891</v>
       </c>
       <c r="T62">
-        <v>1.113748424470097</v>
+        <v>1.142306076379587</v>
       </c>
       <c r="U62">
         <v>0.2067366166625341</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5496686914528361</v>
+        <v>0.5406577292978714</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1668269969424425</v>
+        <v>0.1684363631090679</v>
       </c>
       <c r="C63">
-        <v>-363.9009939686409</v>
+        <v>-377.2173965312256</v>
       </c>
       <c r="D63">
-        <v>246.702414077011</v>
+        <v>243.4649198430436</v>
       </c>
       <c r="E63">
-        <v>194.7225751839275</v>
+        <v>204.8014835125447</v>
       </c>
       <c r="F63">
-        <v>614.813408045652</v>
+        <v>624.8923163742692</v>
       </c>
       <c r="G63">
         <v>4.21</v>
@@ -6453,28 +6453,28 @@
         <v>68.72</v>
       </c>
       <c r="M63">
-        <v>127.1044438581201</v>
+        <v>129.1881232656303</v>
       </c>
       <c r="N63">
-        <v>-58.38444385812011</v>
+        <v>-60.46812326563025</v>
       </c>
       <c r="O63">
         <v>-0</v>
       </c>
       <c r="P63">
-        <v>-58.38444385812011</v>
+        <v>-60.46812326563025</v>
       </c>
       <c r="Q63">
-        <v>-13.78444385812011</v>
+        <v>-15.86812326563025</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1044042584058891</v>
+        <v>0.1059464757323599</v>
       </c>
       <c r="T63">
-        <v>1.142306076379587</v>
+        <v>1.172366762600102</v>
       </c>
       <c r="U63">
         <v>0.2067366166625341</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5406577292978714</v>
+        <v>0.5319374433414543</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1684363631090679</v>
+        <v>0.1700457292756932</v>
       </c>
       <c r="C64">
-        <v>-377.2173965312256</v>
+        <v>-390.4499279826634</v>
       </c>
       <c r="D64">
-        <v>243.4649198430436</v>
+        <v>240.3112967202229</v>
       </c>
       <c r="E64">
-        <v>204.8014835125447</v>
+        <v>214.8803918411619</v>
       </c>
       <c r="F64">
-        <v>624.8923163742692</v>
+        <v>634.9712247028864</v>
       </c>
       <c r="G64">
         <v>4.21</v>
@@ -6535,28 +6535,28 @@
         <v>68.72</v>
       </c>
       <c r="M64">
-        <v>129.1881232656303</v>
+        <v>131.2718026731404</v>
       </c>
       <c r="N64">
-        <v>-60.46812326563025</v>
+        <v>-62.55180267314043</v>
       </c>
       <c r="O64">
         <v>-0</v>
       </c>
       <c r="P64">
-        <v>-60.46812326563025</v>
+        <v>-62.55180267314043</v>
       </c>
       <c r="Q64">
-        <v>-15.86812326563025</v>
+        <v>-17.95180267314043</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1059464757323599</v>
+        <v>0.1075720561575588</v>
       </c>
       <c r="T64">
-        <v>1.172366762600102</v>
+        <v>1.204052350778483</v>
       </c>
       <c r="U64">
         <v>0.2067366166625341</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5319374433414543</v>
+        <v>0.5234939918598438</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1700457292756932</v>
+        <v>0.1716550954423186</v>
       </c>
       <c r="C65">
-        <v>-390.4499279826634</v>
+        <v>-403.6018058167278</v>
       </c>
       <c r="D65">
-        <v>240.3112967202229</v>
+        <v>237.2383272147758</v>
       </c>
       <c r="E65">
-        <v>214.8803918411619</v>
+        <v>224.9593001697791</v>
       </c>
       <c r="F65">
-        <v>634.9712247028864</v>
+        <v>645.0501330315036</v>
       </c>
       <c r="G65">
         <v>4.21</v>
@@ -6617,28 +6617,28 @@
         <v>68.72</v>
       </c>
       <c r="M65">
-        <v>131.2718026731404</v>
+        <v>133.3554820806506</v>
       </c>
       <c r="N65">
-        <v>-62.55180267314043</v>
+        <v>-64.63548208065058</v>
       </c>
       <c r="O65">
         <v>-0</v>
       </c>
       <c r="P65">
-        <v>-62.55180267314043</v>
+        <v>-64.63548208065058</v>
       </c>
       <c r="Q65">
-        <v>-17.95180267314043</v>
+        <v>-20.03548208065057</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1075720561575588</v>
+        <v>0.1092879466063798</v>
       </c>
       <c r="T65">
-        <v>1.204052350778483</v>
+        <v>1.237498249411219</v>
       </c>
       <c r="U65">
         <v>0.2067366166625341</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5234939918598438</v>
+        <v>0.5153143982370338</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1716550954423186</v>
+        <v>0.1732644616089439</v>
       </c>
       <c r="C66">
-        <v>-403.6018058167278</v>
+        <v>-416.6760850308992</v>
       </c>
       <c r="D66">
-        <v>237.2383272147758</v>
+        <v>234.2429563292217</v>
       </c>
       <c r="E66">
-        <v>224.9593001697791</v>
+        <v>235.0382084983964</v>
       </c>
       <c r="F66">
-        <v>645.0501330315036</v>
+        <v>655.1290413601209</v>
       </c>
       <c r="G66">
         <v>4.21</v>
@@ -6699,28 +6699,28 @@
         <v>68.72</v>
       </c>
       <c r="M66">
-        <v>133.3554820806506</v>
+        <v>135.4391614881608</v>
       </c>
       <c r="N66">
-        <v>-64.63548208065058</v>
+        <v>-66.71916148816078</v>
       </c>
       <c r="O66">
         <v>-0</v>
       </c>
       <c r="P66">
-        <v>-64.63548208065058</v>
+        <v>-66.71916148816078</v>
       </c>
       <c r="Q66">
-        <v>-20.03548208065057</v>
+        <v>-22.11916148816078</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1092879466063798</v>
+        <v>0.1111018879379907</v>
       </c>
       <c r="T66">
-        <v>1.237498249411219</v>
+        <v>1.27285534225154</v>
       </c>
       <c r="U66">
         <v>0.2067366166625341</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5153143982370338</v>
+        <v>0.5073864844180024</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1732644616089439</v>
+        <v>0.1979738277755692</v>
       </c>
       <c r="C67">
-        <v>-416.6760850308992</v>
+        <v>-464.7904102541212</v>
       </c>
       <c r="D67">
-        <v>234.2429563292217</v>
+        <v>196.2075394346169</v>
       </c>
       <c r="E67">
-        <v>235.0382084983964</v>
+        <v>245.1171168270137</v>
       </c>
       <c r="F67">
-        <v>655.1290413601209</v>
+        <v>665.2079496887382</v>
       </c>
       <c r="G67">
         <v>4.21</v>
@@ -6781,45 +6781,45 @@
         <v>68.72</v>
       </c>
       <c r="M67">
-        <v>135.4391614881608</v>
+        <v>160.8051191347768</v>
       </c>
       <c r="N67">
-        <v>-66.71916148816078</v>
+        <v>-92.08511913477676</v>
       </c>
       <c r="O67">
         <v>-0</v>
       </c>
       <c r="P67">
-        <v>-66.71916148816078</v>
+        <v>-92.08511913477676</v>
       </c>
       <c r="Q67">
-        <v>-22.11916148816078</v>
+        <v>-47.48511913477676</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1111018879379907</v>
+        <v>0.1130225317008728</v>
       </c>
       <c r="T67">
-        <v>1.27285534225154</v>
+        <v>1.310292264082467</v>
       </c>
       <c r="U67">
-        <v>0.2067366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V67">
         <v>0</v>
       </c>
       <c r="W67">
-        <v>0.2067366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.5073864844180024</v>
+        <v>0.4273495792282782</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1979738277755692</v>
+        <v>0.1999331939421946</v>
       </c>
       <c r="C68">
-        <v>-464.7904102541212</v>
+        <v>-477.3635406550403</v>
       </c>
       <c r="D68">
-        <v>196.2075394346169</v>
+        <v>193.7133173623151</v>
       </c>
       <c r="E68">
-        <v>245.1171168270137</v>
+        <v>255.1960251556309</v>
       </c>
       <c r="F68">
-        <v>665.2079496887382</v>
+        <v>675.2868580173554</v>
       </c>
       <c r="G68">
         <v>4.21</v>
@@ -6863,28 +6863,28 @@
         <v>68.72</v>
       </c>
       <c r="M68">
-        <v>160.8051191347768</v>
+        <v>163.2415603337885</v>
       </c>
       <c r="N68">
-        <v>-92.08511913477676</v>
+        <v>-94.52156033378853</v>
       </c>
       <c r="O68">
         <v>-0</v>
       </c>
       <c r="P68">
-        <v>-92.08511913477676</v>
+        <v>-94.52156033378853</v>
       </c>
       <c r="Q68">
-        <v>-47.48511913477676</v>
+        <v>-49.92156033378853</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1130225317008728</v>
+        <v>0.1150595781160507</v>
       </c>
       <c r="T68">
-        <v>1.310292264082467</v>
+        <v>1.349998090266785</v>
       </c>
       <c r="U68">
         <v>0.2417366166625341</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4273495792282782</v>
+        <v>0.420971227299498</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1999331939421946</v>
+        <v>0.2018925601088199</v>
       </c>
       <c r="C69">
-        <v>-477.3635406550403</v>
+        <v>-489.8740531536441</v>
       </c>
       <c r="D69">
-        <v>193.7133173623151</v>
+        <v>191.2817131923286</v>
       </c>
       <c r="E69">
-        <v>255.1960251556309</v>
+        <v>265.2749334842482</v>
       </c>
       <c r="F69">
-        <v>675.2868580173554</v>
+        <v>685.3657663459727</v>
       </c>
       <c r="G69">
         <v>4.21</v>
@@ -6945,28 +6945,28 @@
         <v>68.72</v>
       </c>
       <c r="M69">
-        <v>163.2415603337885</v>
+        <v>165.6780015328003</v>
       </c>
       <c r="N69">
-        <v>-94.52156033378853</v>
+        <v>-96.95800153280032</v>
       </c>
       <c r="O69">
         <v>-0</v>
       </c>
       <c r="P69">
-        <v>-94.52156033378853</v>
+        <v>-96.95800153280032</v>
       </c>
       <c r="Q69">
-        <v>-49.92156033378853</v>
+        <v>-52.35800153280032</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1150595781160507</v>
+        <v>0.1172239399321773</v>
       </c>
       <c r="T69">
-        <v>1.349998090266785</v>
+        <v>1.392185530587622</v>
       </c>
       <c r="U69">
         <v>0.2417366166625341</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.420971227299498</v>
+        <v>0.4147804739568582</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2018925601088199</v>
+        <v>0.2038519262754453</v>
       </c>
       <c r="C70">
-        <v>-489.8740531536441</v>
+        <v>-502.3242765681023</v>
       </c>
       <c r="D70">
-        <v>191.2817131923286</v>
+        <v>188.9103981064877</v>
       </c>
       <c r="E70">
-        <v>265.2749334842482</v>
+        <v>275.3538418128654</v>
       </c>
       <c r="F70">
-        <v>685.3657663459727</v>
+        <v>695.4446746745899</v>
       </c>
       <c r="G70">
         <v>4.21</v>
@@ -7027,28 +7027,28 @@
         <v>68.72</v>
       </c>
       <c r="M70">
-        <v>165.6780015328003</v>
+        <v>168.1144427318121</v>
       </c>
       <c r="N70">
-        <v>-96.95800153280032</v>
+        <v>-99.39444273181209</v>
       </c>
       <c r="O70">
         <v>-0</v>
       </c>
       <c r="P70">
-        <v>-96.95800153280032</v>
+        <v>-99.39444273181209</v>
       </c>
       <c r="Q70">
-        <v>-52.35800153280032</v>
+        <v>-54.79444273181209</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1172239399321773</v>
+        <v>0.1195279379945056</v>
       </c>
       <c r="T70">
-        <v>1.392185530587622</v>
+        <v>1.437094741251739</v>
       </c>
       <c r="U70">
         <v>0.2417366166625341</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4147804739568582</v>
+        <v>0.4087691627400921</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2038519262754453</v>
+        <v>0.2058112924420706</v>
       </c>
       <c r="C71">
-        <v>-502.3242765681023</v>
+        <v>-514.7164256494468</v>
       </c>
       <c r="D71">
-        <v>188.9103981064877</v>
+        <v>186.5971573537603</v>
       </c>
       <c r="E71">
-        <v>275.3538418128654</v>
+        <v>285.4327501414826</v>
       </c>
       <c r="F71">
-        <v>695.4446746745899</v>
+        <v>705.5235830032071</v>
       </c>
       <c r="G71">
         <v>4.21</v>
@@ -7109,28 +7109,28 @@
         <v>68.72</v>
       </c>
       <c r="M71">
-        <v>168.1144427318121</v>
+        <v>170.5508839308238</v>
       </c>
       <c r="N71">
-        <v>-99.39444273181209</v>
+        <v>-101.8308839308238</v>
       </c>
       <c r="O71">
         <v>-0</v>
       </c>
       <c r="P71">
-        <v>-99.39444273181209</v>
+        <v>-101.8308839308238</v>
       </c>
       <c r="Q71">
-        <v>-54.79444273181209</v>
+        <v>-57.23088393082383</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1195279379945056</v>
+        <v>0.1219855359276558</v>
       </c>
       <c r="T71">
-        <v>1.437094741251739</v>
+        <v>1.484997899293463</v>
       </c>
       <c r="U71">
         <v>0.2417366166625341</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4087691627400921</v>
+        <v>0.4029296032723766</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2058112924420706</v>
+        <v>0.207770658608696</v>
       </c>
       <c r="C72">
-        <v>-514.7164256494468</v>
+        <v>-527.0526079809483</v>
       </c>
       <c r="D72">
-        <v>186.5971573537603</v>
+        <v>184.3398833508762</v>
       </c>
       <c r="E72">
-        <v>285.4327501414826</v>
+        <v>295.5116584701</v>
       </c>
       <c r="F72">
-        <v>705.5235830032071</v>
+        <v>715.6024913318245</v>
       </c>
       <c r="G72">
         <v>4.21</v>
@@ -7191,28 +7191,28 @@
         <v>68.72</v>
       </c>
       <c r="M72">
-        <v>170.5508839308238</v>
+        <v>172.9873251298356</v>
       </c>
       <c r="N72">
-        <v>-101.8308839308238</v>
+        <v>-104.2673251298356</v>
       </c>
       <c r="O72">
         <v>-0</v>
       </c>
       <c r="P72">
-        <v>-101.8308839308238</v>
+        <v>-104.2673251298356</v>
       </c>
       <c r="Q72">
-        <v>-57.23088393082383</v>
+        <v>-59.66732512983562</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1219855359276558</v>
+        <v>0.1246126233734371</v>
       </c>
       <c r="T72">
-        <v>1.484997899293463</v>
+        <v>1.536204723407031</v>
       </c>
       <c r="U72">
         <v>0.2417366166625341</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4029296032723766</v>
+        <v>0.3972545384375543</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.207770658608696</v>
+        <v>0.2097300247753213</v>
       </c>
       <c r="C73">
-        <v>-527.0526079809482</v>
+        <v>-539.3348303827036</v>
       </c>
       <c r="D73">
-        <v>184.3398833508762</v>
+        <v>182.136569277738</v>
       </c>
       <c r="E73">
-        <v>295.5116584700999</v>
+        <v>305.5905667987171</v>
       </c>
       <c r="F73">
-        <v>715.6024913318244</v>
+        <v>725.6813996604416</v>
       </c>
       <c r="G73">
         <v>4.21</v>
@@ -7273,28 +7273,28 @@
         <v>68.72</v>
       </c>
       <c r="M73">
-        <v>172.9873251298356</v>
+        <v>175.4237663288474</v>
       </c>
       <c r="N73">
-        <v>-104.2673251298356</v>
+        <v>-106.7037663288474</v>
       </c>
       <c r="O73">
         <v>-0</v>
       </c>
       <c r="P73">
-        <v>-104.2673251298356</v>
+        <v>-106.7037663288474</v>
       </c>
       <c r="Q73">
-        <v>-59.6673251298356</v>
+        <v>-62.10376632884736</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1246126233734371</v>
+        <v>0.1274273599224884</v>
       </c>
       <c r="T73">
-        <v>1.536204723407031</v>
+        <v>1.591069177814425</v>
       </c>
       <c r="U73">
         <v>0.2417366166625341</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3972545384375544</v>
+        <v>0.3917371142925884</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2097300247753213</v>
+        <v>0.2116893909419466</v>
       </c>
       <c r="C74">
-        <v>-539.3348303827036</v>
+        <v>-551.5650048623486</v>
       </c>
       <c r="D74">
-        <v>182.136569277738</v>
+        <v>179.9853031267102</v>
       </c>
       <c r="E74">
-        <v>305.5905667987171</v>
+        <v>315.6694751273343</v>
       </c>
       <c r="F74">
-        <v>725.6813996604416</v>
+        <v>735.7603079890588</v>
       </c>
       <c r="G74">
         <v>4.21</v>
@@ -7355,28 +7355,28 @@
         <v>68.72</v>
       </c>
       <c r="M74">
-        <v>175.4237663288474</v>
+        <v>177.8602075278591</v>
       </c>
       <c r="N74">
-        <v>-106.7037663288474</v>
+        <v>-109.1402075278591</v>
       </c>
       <c r="O74">
         <v>-0</v>
       </c>
       <c r="P74">
-        <v>-106.7037663288474</v>
+        <v>-109.1402075278591</v>
       </c>
       <c r="Q74">
-        <v>-62.10376632884736</v>
+        <v>-64.54020752785914</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1274273599224884</v>
+        <v>0.1304505954751731</v>
       </c>
       <c r="T74">
-        <v>1.591069177814425</v>
+        <v>1.649997665881625</v>
       </c>
       <c r="U74">
         <v>0.2417366166625341</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3917371142925884</v>
+        <v>0.3863708524529639</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2116893909419466</v>
+        <v>0.213648757108572</v>
       </c>
       <c r="C75">
-        <v>-551.5650048623486</v>
+        <v>-563.7449541489765</v>
       </c>
       <c r="D75">
-        <v>179.9853031267102</v>
+        <v>177.8842621686996</v>
       </c>
       <c r="E75">
-        <v>315.6694751273343</v>
+        <v>325.7483834559516</v>
       </c>
       <c r="F75">
-        <v>735.7603079890588</v>
+        <v>745.8392163176761</v>
       </c>
       <c r="G75">
         <v>4.21</v>
@@ -7437,28 +7437,28 @@
         <v>68.72</v>
       </c>
       <c r="M75">
-        <v>177.8602075278591</v>
+        <v>180.2966487268709</v>
       </c>
       <c r="N75">
-        <v>-109.1402075278591</v>
+        <v>-111.5766487268709</v>
       </c>
       <c r="O75">
         <v>-0</v>
       </c>
       <c r="P75">
-        <v>-109.1402075278591</v>
+        <v>-111.5766487268709</v>
       </c>
       <c r="Q75">
-        <v>-64.54020752785914</v>
+        <v>-66.97664872687093</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1304505954751731</v>
+        <v>0.1337063876088336</v>
       </c>
       <c r="T75">
-        <v>1.649997665881625</v>
+        <v>1.71345911456938</v>
       </c>
       <c r="U75">
         <v>0.2417366166625341</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3863708524529639</v>
+        <v>0.381149624717113</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.213648757108572</v>
+        <v>0.2156081232751973</v>
       </c>
       <c r="C76">
-        <v>-563.7449541489765</v>
+        <v>-575.8764168439334</v>
       </c>
       <c r="D76">
-        <v>177.8842621686996</v>
+        <v>175.8317078023599</v>
       </c>
       <c r="E76">
-        <v>325.7483834559516</v>
+        <v>335.8272917845688</v>
       </c>
       <c r="F76">
-        <v>745.8392163176761</v>
+        <v>755.9181246462933</v>
       </c>
       <c r="G76">
         <v>4.21</v>
@@ -7519,28 +7519,28 @@
         <v>68.72</v>
       </c>
       <c r="M76">
-        <v>180.2966487268709</v>
+        <v>182.7330899258827</v>
       </c>
       <c r="N76">
-        <v>-111.5766487268709</v>
+        <v>-114.0130899258827</v>
       </c>
       <c r="O76">
         <v>-0</v>
       </c>
       <c r="P76">
-        <v>-111.5766487268709</v>
+        <v>-114.0130899258827</v>
       </c>
       <c r="Q76">
-        <v>-66.97664872687093</v>
+        <v>-69.4130899258827</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1337063876088336</v>
+        <v>0.137222643113187</v>
       </c>
       <c r="T76">
-        <v>1.71345911456938</v>
+        <v>1.781997479152156</v>
       </c>
       <c r="U76">
         <v>0.2417366166625341</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.381149624717113</v>
+        <v>0.3760676297208848</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2156081232751973</v>
+        <v>0.2175674894418227</v>
       </c>
       <c r="C77">
-        <v>-575.8764168439334</v>
+        <v>-587.9610522190799</v>
       </c>
       <c r="D77">
-        <v>175.8317078023599</v>
+        <v>173.8259807558306</v>
       </c>
       <c r="E77">
-        <v>335.8272917845688</v>
+        <v>345.9062001131861</v>
       </c>
       <c r="F77">
-        <v>755.9181246462933</v>
+        <v>765.9970329749106</v>
       </c>
       <c r="G77">
         <v>4.21</v>
@@ -7601,28 +7601,28 @@
         <v>68.72</v>
       </c>
       <c r="M77">
-        <v>182.7330899258827</v>
+        <v>185.1695311248944</v>
       </c>
       <c r="N77">
-        <v>-114.0130899258827</v>
+        <v>-116.4495311248944</v>
       </c>
       <c r="O77">
         <v>-0</v>
       </c>
       <c r="P77">
-        <v>-114.0130899258827</v>
+        <v>-116.4495311248944</v>
       </c>
       <c r="Q77">
-        <v>-69.4130899258827</v>
+        <v>-71.84953112489444</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.137222643113187</v>
+        <v>0.1410319199095698</v>
       </c>
       <c r="T77">
-        <v>1.781997479152156</v>
+        <v>1.856247374116829</v>
       </c>
       <c r="U77">
         <v>0.2417366166625341</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3760676297208848</v>
+        <v>0.3711193714350838</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2175674894418227</v>
+        <v>0.219526855608448</v>
       </c>
       <c r="C78">
-        <v>-587.9610522190799</v>
+        <v>-600.0004446903509</v>
       </c>
       <c r="D78">
-        <v>173.8259807558306</v>
+        <v>171.8654966131769</v>
       </c>
       <c r="E78">
-        <v>345.9062001131861</v>
+        <v>355.9851084418034</v>
       </c>
       <c r="F78">
-        <v>765.9970329749106</v>
+        <v>776.0759413035279</v>
       </c>
       <c r="G78">
         <v>4.21</v>
@@ -7683,28 +7683,28 @@
         <v>68.72</v>
       </c>
       <c r="M78">
-        <v>185.1695311248944</v>
+        <v>187.6059723239062</v>
       </c>
       <c r="N78">
-        <v>-116.4495311248944</v>
+        <v>-118.8859723239062</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>-116.4495311248944</v>
+        <v>-118.8859723239062</v>
       </c>
       <c r="Q78">
-        <v>-71.84953112489444</v>
+        <v>-74.28597232390624</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1410319199095698</v>
+        <v>0.1451724381665076</v>
       </c>
       <c r="T78">
-        <v>1.856247374116829</v>
+        <v>1.936953781687125</v>
       </c>
       <c r="U78">
         <v>0.2417366166625341</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3711193714350838</v>
+        <v>0.3662996393385242</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.219526855608448</v>
+        <v>0.2214862217750734</v>
       </c>
       <c r="C79">
-        <v>-600.0004446903509</v>
+        <v>-611.9961079919634</v>
       </c>
       <c r="D79">
-        <v>171.8654966131769</v>
+        <v>169.9487416401817</v>
       </c>
       <c r="E79">
-        <v>355.9851084418034</v>
+        <v>366.0640167704206</v>
       </c>
       <c r="F79">
-        <v>776.0759413035279</v>
+        <v>786.1548496321451</v>
       </c>
       <c r="G79">
         <v>4.21</v>
@@ -7765,28 +7765,28 @@
         <v>68.72</v>
       </c>
       <c r="M79">
-        <v>187.6059723239062</v>
+        <v>190.042413522918</v>
       </c>
       <c r="N79">
-        <v>-118.8859723239062</v>
+        <v>-121.322413522918</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>-118.8859723239062</v>
+        <v>-121.322413522918</v>
       </c>
       <c r="Q79">
-        <v>-74.28597232390624</v>
+        <v>-76.722413522918</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1451724381665076</v>
+        <v>0.1496893671740761</v>
       </c>
       <c r="T79">
-        <v>1.936953781687125</v>
+        <v>2.024997135400177</v>
       </c>
       <c r="U79">
         <v>0.2417366166625341</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3662996393385242</v>
+        <v>0.3616034901162354</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2214862217750734</v>
+        <v>0.2234455879416987</v>
       </c>
       <c r="C80">
-        <v>-611.9961079919634</v>
+        <v>-623.9494890743853</v>
       </c>
       <c r="D80">
-        <v>169.9487416401817</v>
+        <v>168.074268886377</v>
       </c>
       <c r="E80">
-        <v>366.0640167704206</v>
+        <v>376.1429250990378</v>
       </c>
       <c r="F80">
-        <v>786.1548496321451</v>
+        <v>796.2337579607623</v>
       </c>
       <c r="G80">
         <v>4.21</v>
@@ -7847,28 +7847,28 @@
         <v>68.72</v>
       </c>
       <c r="M80">
-        <v>190.042413522918</v>
+        <v>192.4788547219298</v>
       </c>
       <c r="N80">
-        <v>-121.322413522918</v>
+        <v>-123.7588547219298</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-121.322413522918</v>
+        <v>-123.7588547219298</v>
       </c>
       <c r="Q80">
-        <v>-76.722413522918</v>
+        <v>-79.15885472192977</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1496893671740761</v>
+        <v>0.1546364798966512</v>
       </c>
       <c r="T80">
-        <v>2.024997135400177</v>
+        <v>2.121425570419233</v>
       </c>
       <c r="U80">
         <v>0.2417366166625341</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3616034901162354</v>
+        <v>0.3570262307476755</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2234455879416987</v>
+        <v>0.225404954108324</v>
       </c>
       <c r="C81">
-        <v>-623.9494890743853</v>
+        <v>-635.8619717471581</v>
       </c>
       <c r="D81">
-        <v>168.074268886377</v>
+        <v>166.2406945422215</v>
       </c>
       <c r="E81">
-        <v>376.1429250990378</v>
+        <v>386.2218334276552</v>
       </c>
       <c r="F81">
-        <v>796.2337579607623</v>
+        <v>806.3126662893796</v>
       </c>
       <c r="G81">
         <v>4.21</v>
@@ -7929,28 +7929,28 @@
         <v>68.72</v>
       </c>
       <c r="M81">
-        <v>192.4788547219298</v>
+        <v>194.9152959209416</v>
       </c>
       <c r="N81">
-        <v>-123.7588547219298</v>
+        <v>-126.1952959209416</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-123.7588547219298</v>
+        <v>-126.1952959209416</v>
       </c>
       <c r="Q81">
-        <v>-79.15885472192977</v>
+        <v>-81.59529592094157</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1546364798966512</v>
+        <v>0.1600783038914838</v>
       </c>
       <c r="T81">
-        <v>2.121425570419233</v>
+        <v>2.227496848940195</v>
       </c>
       <c r="U81">
         <v>0.2417366166625341</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3570262307476755</v>
+        <v>0.3525634028633294</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.225404954108324</v>
+        <v>0.2273643202749494</v>
       </c>
       <c r="C82">
-        <v>-635.8619717471581</v>
+        <v>-647.7348800858493</v>
       </c>
       <c r="D82">
-        <v>166.2406945422215</v>
+        <v>164.4466945321475</v>
       </c>
       <c r="E82">
-        <v>386.2218334276552</v>
+        <v>396.3007417562724</v>
       </c>
       <c r="F82">
-        <v>806.3126662893796</v>
+        <v>816.3915746179969</v>
       </c>
       <c r="G82">
         <v>4.21</v>
@@ -8011,28 +8011,28 @@
         <v>68.72</v>
       </c>
       <c r="M82">
-        <v>194.9152959209416</v>
+        <v>197.3517371199533</v>
       </c>
       <c r="N82">
-        <v>-126.1952959209416</v>
+        <v>-128.6317371199533</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-126.1952959209416</v>
+        <v>-128.6317371199533</v>
       </c>
       <c r="Q82">
-        <v>-81.59529592094157</v>
+        <v>-84.03173711995331</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1600783038914838</v>
+        <v>0.1660929514647198</v>
       </c>
       <c r="T82">
-        <v>2.227496848940195</v>
+        <v>2.344733525200205</v>
       </c>
       <c r="U82">
         <v>0.2417366166625341</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3525634028633294</v>
+        <v>0.3482107682600786</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2273643202749494</v>
+        <v>0.2293236864415747</v>
       </c>
       <c r="C83">
-        <v>-647.7348800858493</v>
+        <v>-659.5694816207614</v>
       </c>
       <c r="D83">
-        <v>164.4466945321475</v>
+        <v>162.6910013258527</v>
       </c>
       <c r="E83">
-        <v>396.3007417562724</v>
+        <v>406.3796500848896</v>
       </c>
       <c r="F83">
-        <v>816.3915746179969</v>
+        <v>826.4704829466141</v>
       </c>
       <c r="G83">
         <v>4.21</v>
@@ -8093,28 +8093,28 @@
         <v>68.72</v>
       </c>
       <c r="M83">
-        <v>197.3517371199533</v>
+        <v>199.7881783189651</v>
       </c>
       <c r="N83">
-        <v>-128.6317371199533</v>
+        <v>-131.0681783189651</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-128.6317371199533</v>
+        <v>-131.0681783189651</v>
       </c>
       <c r="Q83">
-        <v>-84.03173711995331</v>
+        <v>-86.46817831896507</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1660929514647198</v>
+        <v>0.1727758932127597</v>
       </c>
       <c r="T83">
-        <v>2.344733525200205</v>
+        <v>2.474996498822439</v>
       </c>
       <c r="U83">
         <v>0.2417366166625341</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3482107682600786</v>
+        <v>0.343964295476419</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2293236864415747</v>
+        <v>0.2312830526082001</v>
       </c>
       <c r="C84">
-        <v>-659.5694816207614</v>
+        <v>-671.3669903235359</v>
       </c>
       <c r="D84">
-        <v>162.6910013258527</v>
+        <v>160.9724009516954</v>
       </c>
       <c r="E84">
-        <v>406.3796500848896</v>
+        <v>416.4585584135069</v>
       </c>
       <c r="F84">
-        <v>826.4704829466141</v>
+        <v>836.5493912752314</v>
       </c>
       <c r="G84">
         <v>4.21</v>
@@ -8175,28 +8175,28 @@
         <v>68.72</v>
       </c>
       <c r="M84">
-        <v>199.7881783189651</v>
+        <v>202.2246195179769</v>
       </c>
       <c r="N84">
-        <v>-131.0681783189651</v>
+        <v>-133.5046195179769</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-131.0681783189651</v>
+        <v>-133.5046195179769</v>
       </c>
       <c r="Q84">
-        <v>-86.46817831896507</v>
+        <v>-88.90461951797687</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1727758932127597</v>
+        <v>0.1802450634017456</v>
       </c>
       <c r="T84">
-        <v>2.474996498822439</v>
+        <v>2.620584528164936</v>
       </c>
       <c r="U84">
         <v>0.2417366166625341</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.343964295476419</v>
+        <v>0.3398201473381489</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2312830526082001</v>
+        <v>0.2332424187748254</v>
       </c>
       <c r="C85">
-        <v>-671.3669903235359</v>
+        <v>-683.1285694064401</v>
       </c>
       <c r="D85">
-        <v>160.9724009516954</v>
+        <v>159.2897301974086</v>
       </c>
       <c r="E85">
-        <v>416.4585584135069</v>
+        <v>426.5374667421241</v>
       </c>
       <c r="F85">
-        <v>836.5493912752314</v>
+        <v>846.6282996038486</v>
       </c>
       <c r="G85">
         <v>4.21</v>
@@ -8257,28 +8257,28 @@
         <v>68.72</v>
       </c>
       <c r="M85">
-        <v>202.2246195179769</v>
+        <v>204.6610607169886</v>
       </c>
       <c r="N85">
-        <v>-133.5046195179769</v>
+        <v>-135.9410607169886</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-133.5046195179769</v>
+        <v>-135.9410607169886</v>
       </c>
       <c r="Q85">
-        <v>-88.90461951797687</v>
+        <v>-91.34106071698864</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1802450634017456</v>
+        <v>0.1886478798643547</v>
       </c>
       <c r="T85">
-        <v>2.620584528164936</v>
+        <v>2.784371061175245</v>
       </c>
       <c r="U85">
         <v>0.2417366166625341</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3398201473381489</v>
+        <v>0.3357746693936471</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2332424187748254</v>
+        <v>0.2352017849414507</v>
       </c>
       <c r="C86">
-        <v>-683.12856940644</v>
+        <v>-694.855333947902</v>
       </c>
       <c r="D86">
-        <v>159.2897301974086</v>
+        <v>157.6418739845637</v>
       </c>
       <c r="E86">
-        <v>426.537466742124</v>
+        <v>436.6163750707412</v>
       </c>
       <c r="F86">
-        <v>846.6282996038485</v>
+        <v>856.7072079324657</v>
       </c>
       <c r="G86">
         <v>4.21</v>
@@ -8339,28 +8339,28 @@
         <v>68.72</v>
       </c>
       <c r="M86">
-        <v>204.6610607169886</v>
+        <v>207.0975019160004</v>
       </c>
       <c r="N86">
-        <v>-135.9410607169886</v>
+        <v>-138.3775019160004</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-135.9410607169886</v>
+        <v>-138.3775019160004</v>
       </c>
       <c r="Q86">
-        <v>-91.34106071698861</v>
+        <v>-93.77750191600038</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1886478798643547</v>
+        <v>0.1981710718553117</v>
       </c>
       <c r="T86">
-        <v>2.784371061175243</v>
+        <v>2.969995798586926</v>
       </c>
       <c r="U86">
         <v>0.2417366166625341</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3357746693936472</v>
+        <v>0.3318243791654866</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2352017849414507</v>
+        <v>0.2371611511080761</v>
       </c>
       <c r="C87">
-        <v>-694.855333947902</v>
+        <v>-706.5483533567476</v>
       </c>
       <c r="D87">
-        <v>157.6418739845637</v>
+        <v>156.0277629043354</v>
       </c>
       <c r="E87">
-        <v>436.6163750707412</v>
+        <v>446.6952833993586</v>
       </c>
       <c r="F87">
-        <v>856.7072079324657</v>
+        <v>866.7861162610831</v>
       </c>
       <c r="G87">
         <v>4.21</v>
@@ -8421,28 +8421,28 @@
         <v>68.72</v>
       </c>
       <c r="M87">
-        <v>207.0975019160004</v>
+        <v>209.5339431150122</v>
       </c>
       <c r="N87">
-        <v>-138.3775019160004</v>
+        <v>-140.8139431150122</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-138.3775019160004</v>
+        <v>-140.8139431150122</v>
       </c>
       <c r="Q87">
-        <v>-93.77750191600038</v>
+        <v>-96.21394311501217</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1981710718553117</v>
+        <v>0.2090547198449768</v>
       </c>
       <c r="T87">
-        <v>2.969995798586926</v>
+        <v>3.182138355628849</v>
       </c>
       <c r="U87">
         <v>0.2417366166625341</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3318243791654866</v>
+        <v>0.3279659561519344</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2371611511080761</v>
+        <v>0.2391205172747014</v>
       </c>
       <c r="C88">
-        <v>-706.5483533567476</v>
+        <v>-718.20865368658</v>
       </c>
       <c r="D88">
-        <v>156.0277629043354</v>
+        <v>154.4463709031203</v>
       </c>
       <c r="E88">
-        <v>446.6952833993586</v>
+        <v>456.7741917279758</v>
       </c>
       <c r="F88">
-        <v>866.7861162610831</v>
+        <v>876.8650245897003</v>
       </c>
       <c r="G88">
         <v>4.21</v>
@@ -8503,28 +8503,28 @@
         <v>68.72</v>
       </c>
       <c r="M88">
-        <v>209.5339431150122</v>
+        <v>211.9703843140239</v>
       </c>
       <c r="N88">
-        <v>-140.8139431150122</v>
+        <v>-143.2503843140239</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-140.8139431150122</v>
+        <v>-143.2503843140239</v>
       </c>
       <c r="Q88">
-        <v>-96.21394311501217</v>
+        <v>-98.65038431402391</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2090547198449768</v>
+        <v>0.2216127752176673</v>
       </c>
       <c r="T88">
-        <v>3.182138355628849</v>
+        <v>3.426918229138761</v>
       </c>
       <c r="U88">
         <v>0.2417366166625341</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3279659561519344</v>
+        <v>0.3241962325180042</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2391205172747014</v>
+        <v>0.2410798834413267</v>
       </c>
       <c r="C89">
-        <v>-718.20865368658</v>
+        <v>-729.8372198108327</v>
       </c>
       <c r="D89">
-        <v>154.4463709031203</v>
+        <v>152.8967131074848</v>
       </c>
       <c r="E89">
-        <v>456.7741917279758</v>
+        <v>466.853100056593</v>
       </c>
       <c r="F89">
-        <v>876.8650245897003</v>
+        <v>886.9439329183175</v>
       </c>
       <c r="G89">
         <v>4.21</v>
@@ -8585,28 +8585,28 @@
         <v>68.72</v>
       </c>
       <c r="M89">
-        <v>211.9703843140239</v>
+        <v>214.4068255130357</v>
       </c>
       <c r="N89">
-        <v>-143.2503843140239</v>
+        <v>-145.6868255130357</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-143.2503843140239</v>
+        <v>-145.6868255130357</v>
       </c>
       <c r="Q89">
-        <v>-98.65038431402391</v>
+        <v>-101.0868255130357</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2216127752176673</v>
+        <v>0.2362638398191396</v>
       </c>
       <c r="T89">
-        <v>3.426918229138761</v>
+        <v>3.712494748233658</v>
       </c>
       <c r="U89">
         <v>0.2417366166625341</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3241962325180042</v>
+        <v>0.3205121844212087</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2410798834413267</v>
+        <v>0.2430392496079521</v>
       </c>
       <c r="C90">
-        <v>-729.8372198108327</v>
+        <v>-741.4349974681788</v>
       </c>
       <c r="D90">
-        <v>152.8967131074848</v>
+        <v>151.3778437787558</v>
       </c>
       <c r="E90">
-        <v>466.853100056593</v>
+        <v>476.9320083852102</v>
       </c>
       <c r="F90">
-        <v>886.9439329183175</v>
+        <v>897.0228412469347</v>
       </c>
       <c r="G90">
         <v>4.21</v>
@@ -8667,28 +8667,28 @@
         <v>68.72</v>
       </c>
       <c r="M90">
-        <v>214.4068255130357</v>
+        <v>216.8432667120474</v>
       </c>
       <c r="N90">
-        <v>-145.6868255130357</v>
+        <v>-148.1232667120474</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-145.6868255130357</v>
+        <v>-148.1232667120474</v>
       </c>
       <c r="Q90">
-        <v>-101.0868255130357</v>
+        <v>-103.5232667120474</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2362638398191396</v>
+        <v>0.2535787343481523</v>
       </c>
       <c r="T90">
-        <v>3.712494748233658</v>
+        <v>4.049994270800354</v>
       </c>
       <c r="U90">
         <v>0.2417366166625341</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3205121844212087</v>
+        <v>0.316910923922094</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2430392496079521</v>
+        <v>0.2449986157745774</v>
       </c>
       <c r="C91">
-        <v>-741.4349974681788</v>
+        <v>-753.0028951872267</v>
       </c>
       <c r="D91">
-        <v>151.3778437787558</v>
+        <v>149.8888543883253</v>
       </c>
       <c r="E91">
-        <v>476.9320083852102</v>
+        <v>487.0109167138276</v>
       </c>
       <c r="F91">
-        <v>897.0228412469347</v>
+        <v>907.101749575552</v>
       </c>
       <c r="G91">
         <v>4.21</v>
@@ -8749,28 +8749,28 @@
         <v>68.72</v>
       </c>
       <c r="M91">
-        <v>216.8432667120474</v>
+        <v>219.2797079110592</v>
       </c>
       <c r="N91">
-        <v>-148.1232667120474</v>
+        <v>-150.5597079110592</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-148.1232667120474</v>
+        <v>-150.5597079110592</v>
       </c>
       <c r="Q91">
-        <v>-103.5232667120474</v>
+        <v>-105.9597079110592</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2535787343481523</v>
+        <v>0.2743566077829675</v>
       </c>
       <c r="T91">
-        <v>4.049994270800354</v>
+        <v>4.45499369788039</v>
       </c>
       <c r="U91">
         <v>0.2417366166625341</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.316910923922094</v>
+        <v>0.3133896914340707</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2449986157745774</v>
+        <v>0.2469579819412028</v>
       </c>
       <c r="C92">
-        <v>-753.0028951872267</v>
+        <v>-764.5417860987302</v>
       </c>
       <c r="D92">
-        <v>149.8888543883253</v>
+        <v>148.4288718054391</v>
       </c>
       <c r="E92">
-        <v>487.0109167138276</v>
+        <v>497.0898250424448</v>
       </c>
       <c r="F92">
-        <v>907.101749575552</v>
+        <v>917.1806579041693</v>
       </c>
       <c r="G92">
         <v>4.21</v>
@@ -8831,28 +8831,28 @@
         <v>68.72</v>
       </c>
       <c r="M92">
-        <v>219.2797079110592</v>
+        <v>221.716149110071</v>
       </c>
       <c r="N92">
-        <v>-150.5597079110592</v>
+        <v>-152.996149110071</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-150.5597079110592</v>
+        <v>-152.996149110071</v>
       </c>
       <c r="Q92">
-        <v>-105.9597079110592</v>
+        <v>-108.396149110071</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2743566077829675</v>
+        <v>0.2997517864255195</v>
       </c>
       <c r="T92">
-        <v>4.45499369788039</v>
+        <v>4.949992997644878</v>
       </c>
       <c r="U92">
         <v>0.2417366166625341</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3133896914340707</v>
+        <v>0.3099458486710589</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2469579819412028</v>
+        <v>0.2489173481078281</v>
       </c>
       <c r="C93">
-        <v>-764.5417860987302</v>
+        <v>-776.0525096429122</v>
       </c>
       <c r="D93">
-        <v>148.4288718054391</v>
+        <v>146.9970565898743</v>
       </c>
       <c r="E93">
-        <v>497.0898250424448</v>
+        <v>507.168733371062</v>
       </c>
       <c r="F93">
-        <v>917.1806579041693</v>
+        <v>927.2595662327865</v>
       </c>
       <c r="G93">
         <v>4.21</v>
@@ -8913,28 +8913,28 @@
         <v>68.72</v>
       </c>
       <c r="M93">
-        <v>221.716149110071</v>
+        <v>224.1525903090827</v>
       </c>
       <c r="N93">
-        <v>-152.996149110071</v>
+        <v>-155.4325903090827</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-152.996149110071</v>
+        <v>-155.4325903090827</v>
       </c>
       <c r="Q93">
-        <v>-108.396149110071</v>
+        <v>-110.8325903090827</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2997517864255195</v>
+        <v>0.3314957597287095</v>
       </c>
       <c r="T93">
-        <v>4.949992997644878</v>
+        <v>5.568742122350489</v>
       </c>
       <c r="U93">
         <v>0.2417366166625341</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3099458486710589</v>
+        <v>0.3065768720550692</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2489173481078281</v>
+        <v>0.2508767142744535</v>
       </c>
       <c r="C94">
-        <v>-776.0525096429122</v>
+        <v>-787.5358731789123</v>
       </c>
       <c r="D94">
-        <v>146.9970565898743</v>
+        <v>145.5926013824915</v>
       </c>
       <c r="E94">
-        <v>507.168733371062</v>
+        <v>517.2476416996793</v>
       </c>
       <c r="F94">
-        <v>927.2595662327865</v>
+        <v>937.3384745614038</v>
       </c>
       <c r="G94">
         <v>4.21</v>
@@ -8995,28 +8995,28 @@
         <v>68.72</v>
       </c>
       <c r="M94">
-        <v>224.1525903090827</v>
+        <v>226.5890315080945</v>
       </c>
       <c r="N94">
-        <v>-155.4325903090827</v>
+        <v>-157.8690315080945</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-155.4325903090827</v>
+        <v>-157.8690315080945</v>
       </c>
       <c r="Q94">
-        <v>-110.8325903090827</v>
+        <v>-113.2690315080945</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3314957597287095</v>
+        <v>0.3723094396899537</v>
       </c>
       <c r="T94">
-        <v>5.568742122350489</v>
+        <v>6.364276711257703</v>
       </c>
       <c r="U94">
         <v>0.2417366166625341</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3065768720550692</v>
+        <v>0.3032803465491006</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2508767142744535</v>
+        <v>0.2528360804410788</v>
       </c>
       <c r="C95">
-        <v>-787.5358731789123</v>
+        <v>-798.9926535028459</v>
       </c>
       <c r="D95">
-        <v>145.5926013824915</v>
+        <v>144.2147293871751</v>
       </c>
       <c r="E95">
-        <v>517.2476416996793</v>
+        <v>527.3265500282965</v>
       </c>
       <c r="F95">
-        <v>937.3384745614038</v>
+        <v>947.417382890021</v>
       </c>
       <c r="G95">
         <v>4.21</v>
@@ -9077,28 +9077,28 @@
         <v>68.72</v>
       </c>
       <c r="M95">
-        <v>226.5890315080945</v>
+        <v>229.0254727071063</v>
       </c>
       <c r="N95">
-        <v>-157.8690315080945</v>
+        <v>-160.3054727071063</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-157.8690315080945</v>
+        <v>-160.3054727071063</v>
       </c>
       <c r="Q95">
-        <v>-113.2690315080945</v>
+        <v>-115.7054727071063</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3723094396899537</v>
+        <v>0.4267276796382795</v>
       </c>
       <c r="T95">
-        <v>6.364276711257703</v>
+        <v>7.424989496467322</v>
       </c>
       <c r="U95">
         <v>0.2417366166625341</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3032803465491006</v>
+        <v>0.3000539598836847</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2528360804410788</v>
+        <v>0.2547954466077041</v>
       </c>
       <c r="C96">
-        <v>-798.9926535028459</v>
+        <v>-810.4235982804707</v>
       </c>
       <c r="D96">
-        <v>144.2147293871751</v>
+        <v>142.8626929381674</v>
       </c>
       <c r="E96">
-        <v>527.3265500282965</v>
+        <v>537.4054583569138</v>
       </c>
       <c r="F96">
-        <v>947.417382890021</v>
+        <v>957.4962912186382</v>
       </c>
       <c r="G96">
         <v>4.21</v>
@@ -9159,28 +9159,28 @@
         <v>68.72</v>
       </c>
       <c r="M96">
-        <v>229.0254727071063</v>
+        <v>231.4619139061181</v>
       </c>
       <c r="N96">
-        <v>-160.3054727071063</v>
+        <v>-162.7419139061181</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-160.3054727071063</v>
+        <v>-162.7419139061181</v>
       </c>
       <c r="Q96">
-        <v>-115.7054727071063</v>
+        <v>-118.1419139061181</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4267276796382795</v>
+        <v>0.5029132155659356</v>
       </c>
       <c r="T96">
-        <v>7.424989496467322</v>
+        <v>8.90998739576079</v>
       </c>
       <c r="U96">
         <v>0.2417366166625341</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3000539598836847</v>
+        <v>0.296895497148067</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2547954466077041</v>
+        <v>0.2567548127743295</v>
       </c>
       <c r="C97">
-        <v>-810.4235982804707</v>
+        <v>-821.8294274000135</v>
       </c>
       <c r="D97">
-        <v>142.8626929381674</v>
+        <v>141.535772147242</v>
       </c>
       <c r="E97">
-        <v>537.4054583569138</v>
+        <v>547.4843666855311</v>
       </c>
       <c r="F97">
-        <v>957.4962912186382</v>
+        <v>967.5751995472556</v>
       </c>
       <c r="G97">
         <v>4.21</v>
@@ -9241,28 +9241,28 @@
         <v>68.72</v>
       </c>
       <c r="M97">
-        <v>231.4619139061181</v>
+        <v>233.8983551051299</v>
       </c>
       <c r="N97">
-        <v>-162.7419139061181</v>
+        <v>-165.1783551051299</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-162.7419139061181</v>
+        <v>-165.1783551051299</v>
       </c>
       <c r="Q97">
-        <v>-118.1419139061181</v>
+        <v>-120.5783551051299</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5029132155659356</v>
+        <v>0.6171915194574197</v>
       </c>
       <c r="T97">
-        <v>8.90998739576079</v>
+        <v>11.13748424470099</v>
       </c>
       <c r="U97">
         <v>0.2417366166625341</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.296895497148067</v>
+        <v>0.2938028357194412</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2567548127743295</v>
+        <v>0.2587141789409548</v>
       </c>
       <c r="C98">
-        <v>-821.8294274000134</v>
+        <v>-833.2108342502975</v>
       </c>
       <c r="D98">
-        <v>141.535772147242</v>
+        <v>140.2332736255752</v>
       </c>
       <c r="E98">
-        <v>547.484366685531</v>
+        <v>557.5632750141482</v>
       </c>
       <c r="F98">
-        <v>967.5751995472555</v>
+        <v>977.6541078758727</v>
       </c>
       <c r="G98">
         <v>4.21</v>
@@ -9323,28 +9323,28 @@
         <v>68.72</v>
       </c>
       <c r="M98">
-        <v>233.8983551051298</v>
+        <v>236.3347963041416</v>
       </c>
       <c r="N98">
-        <v>-165.1783551051298</v>
+        <v>-167.6147963041416</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-165.1783551051298</v>
+        <v>-167.6147963041416</v>
       </c>
       <c r="Q98">
-        <v>-120.5783551051298</v>
+        <v>-123.0147963041416</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6171915194574181</v>
+        <v>0.8076553592765576</v>
       </c>
       <c r="T98">
-        <v>11.13748424470096</v>
+        <v>14.84997899293462</v>
       </c>
       <c r="U98">
         <v>0.2417366166625341</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2938028357194413</v>
+        <v>0.2907739405058388</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2587141789409548</v>
+        <v>0.2606735451075802</v>
       </c>
       <c r="C99">
-        <v>-833.2108342502975</v>
+        <v>-844.5684869289439</v>
       </c>
       <c r="D99">
-        <v>140.2332736255752</v>
+        <v>138.954529275546</v>
       </c>
       <c r="E99">
-        <v>557.5632750141482</v>
+        <v>567.6421833427654</v>
       </c>
       <c r="F99">
-        <v>977.6541078758727</v>
+        <v>987.7330162044899</v>
       </c>
       <c r="G99">
         <v>4.21</v>
@@ -9405,28 +9405,28 @@
         <v>68.72</v>
       </c>
       <c r="M99">
-        <v>236.3347963041416</v>
+        <v>238.7712375031533</v>
       </c>
       <c r="N99">
-        <v>-167.6147963041416</v>
+        <v>-170.0512375031533</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-167.6147963041416</v>
+        <v>-170.0512375031533</v>
       </c>
       <c r="Q99">
-        <v>-123.0147963041416</v>
+        <v>-125.4512375031534</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8076553592765576</v>
+        <v>1.188583038914836</v>
       </c>
       <c r="T99">
-        <v>14.84997899293462</v>
+        <v>22.27496848940192</v>
       </c>
       <c r="U99">
         <v>0.2417366166625341</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2907739405058388</v>
+        <v>0.2878068594802691</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2606735451075802</v>
+        <v>0.2626329112742055</v>
       </c>
       <c r="C100">
-        <v>-844.5684869289439</v>
+        <v>-855.9030293850649</v>
       </c>
       <c r="D100">
-        <v>138.954529275546</v>
+        <v>137.6988951480424</v>
       </c>
       <c r="E100">
-        <v>567.6421833427654</v>
+        <v>577.7210916713827</v>
       </c>
       <c r="F100">
-        <v>987.7330162044899</v>
+        <v>997.8119245331072</v>
       </c>
       <c r="G100">
         <v>4.21</v>
@@ -9487,28 +9487,28 @@
         <v>68.72</v>
       </c>
       <c r="M100">
-        <v>238.7712375031533</v>
+        <v>241.2076787021651</v>
       </c>
       <c r="N100">
-        <v>-170.0512375031533</v>
+        <v>-172.4876787021651</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-170.0512375031533</v>
+        <v>-172.4876787021651</v>
       </c>
       <c r="Q100">
-        <v>-125.4512375031534</v>
+        <v>-127.8876787021651</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.188583038914836</v>
+        <v>2.331366077829673</v>
       </c>
       <c r="T100">
-        <v>22.27496848940192</v>
+        <v>44.54993697880385</v>
       </c>
       <c r="U100">
         <v>0.2417366166625341</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2878068594802691</v>
+        <v>0.2848997194855188</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2626329112742055</v>
-      </c>
-      <c r="C101">
-        <v>-855.9030293850649</v>
-      </c>
-      <c r="D101">
-        <v>137.6988951480424</v>
-      </c>
-      <c r="E101">
-        <v>577.7210916713827</v>
-      </c>
-      <c r="F101">
-        <v>997.8119245331072</v>
-      </c>
-      <c r="G101">
-        <v>4.21</v>
-      </c>
-      <c r="H101">
-        <v>587.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>113.32</v>
-      </c>
-      <c r="K101">
-        <v>44.6</v>
-      </c>
-      <c r="L101">
-        <v>68.72</v>
-      </c>
-      <c r="M101">
-        <v>241.2076787021651</v>
-      </c>
-      <c r="N101">
-        <v>-172.4876787021651</v>
-      </c>
-      <c r="O101">
-        <v>-0</v>
-      </c>
-      <c r="P101">
-        <v>-172.4876787021651</v>
-      </c>
-      <c r="Q101">
-        <v>-127.8876787021651</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.331366077829673</v>
-      </c>
-      <c r="T101">
-        <v>44.54993697880385</v>
-      </c>
-      <c r="U101">
-        <v>0.2417366166625341</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.2417366166625341</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2848997194855188</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
